--- a/base.xlsx
+++ b/base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6385D764-1F65-4BAB-93F3-6D3799AA857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53826844-B9EF-4E14-A752-FC92D3F63242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">mcc!$A$1:$F$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">mcc!$A$1:$F$185</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="427">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -1315,6 +1315,9 @@
   </si>
   <si>
     <t>LM-34B</t>
+  </si>
+  <si>
+    <t>x-1111</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1381,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1401,6 +1404,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1408,7 +1422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1438,6 +1452,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1457,9 +1472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1497,7 +1512,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1603,7 +1618,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1745,7 +1760,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1753,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -5104,6 +5119,26 @@
         <v>422</v>
       </c>
     </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="B168">
+        <v>12512</v>
+      </c>
+      <c r="C168" s="6">
+        <v>1212</v>
+      </c>
+      <c r="D168" s="7">
+        <v>1212</v>
+      </c>
+      <c r="E168" s="7">
+        <v>2121</v>
+      </c>
+      <c r="F168" s="7">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53826844-B9EF-4E14-A752-FC92D3F63242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE236AD5-C272-4007-BB6C-0A64F30DCB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">mcc!$A$1:$F$185</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">mcc!$A$1:$F$191</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="670">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -1317,14 +1317,827 @@
     <t>LM-34B</t>
   </si>
   <si>
-    <t>x-1111</t>
+    <t>MH-2101</t>
+  </si>
+  <si>
+    <t>MH-2102</t>
+  </si>
+  <si>
+    <t>MH-2103</t>
+  </si>
+  <si>
+    <t>MH-2104</t>
+  </si>
+  <si>
+    <t>MH-2105</t>
+  </si>
+  <si>
+    <t>MP-2201B</t>
+  </si>
+  <si>
+    <t>MP-2201C</t>
+  </si>
+  <si>
+    <t>MP-2210B</t>
+  </si>
+  <si>
+    <t>MP-2210C</t>
+  </si>
+  <si>
+    <t>MP-2720A</t>
+  </si>
+  <si>
+    <t>MP-2720B</t>
+  </si>
+  <si>
+    <t>Вентилятор искуственной тяги</t>
+  </si>
+  <si>
+    <t>Насос В циркуляций закалочного масла</t>
+  </si>
+  <si>
+    <t>Насос С циркуляций закалочного масла</t>
+  </si>
+  <si>
+    <t>Насос В циркуляций закалочной воды</t>
+  </si>
+  <si>
+    <t>Насос С циркуляций закалочной воды</t>
+  </si>
+  <si>
+    <t>Насос А орошения колонны разделения С3 фракций</t>
+  </si>
+  <si>
+    <t>Насос В орошения колонны разделения С3 фракций</t>
+  </si>
+  <si>
+    <t>A20-MS-201-A</t>
+  </si>
+  <si>
+    <t>A20-MS-201-B</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>8A</t>
+  </si>
+  <si>
+    <t>7A</t>
+  </si>
+  <si>
+    <t>6B</t>
+  </si>
+  <si>
+    <t>HM-51A-1</t>
+  </si>
+  <si>
+    <t>HM-51A-2</t>
+  </si>
+  <si>
+    <t>HM-51A-3</t>
+  </si>
+  <si>
+    <t>HM-61A</t>
+  </si>
+  <si>
+    <t>A20-PC-301-A</t>
+  </si>
+  <si>
+    <t>A20-PC-302-A</t>
+  </si>
+  <si>
+    <t>A20-EP-301</t>
+  </si>
+  <si>
+    <t>A20-PC-301-B</t>
+  </si>
+  <si>
+    <t>A20-PC-302-B</t>
+  </si>
+  <si>
+    <t>A20-PC-301-A               23-CP-003</t>
+  </si>
+  <si>
+    <t>MCC-2AF-4</t>
+  </si>
+  <si>
+    <t>MCC-3AF-7</t>
+  </si>
+  <si>
+    <t>MCC-1AF-4</t>
+  </si>
+  <si>
+    <t>MCC-2AF-3</t>
+  </si>
+  <si>
+    <t>MCC-1AR-7</t>
+  </si>
+  <si>
+    <t>MCC-1AR-4</t>
+  </si>
+  <si>
+    <t>MCC-3AR-4</t>
+  </si>
+  <si>
+    <t>MCC-1AR-5</t>
+  </si>
+  <si>
+    <t>MCC-1BF-4</t>
+  </si>
+  <si>
+    <t>MCC-2AF-6</t>
+  </si>
+  <si>
+    <t>MCC-3AF-5</t>
+  </si>
+  <si>
+    <t>MCC-3AR-5</t>
+  </si>
+  <si>
+    <t>MCC-2BR-5</t>
+  </si>
+  <si>
+    <t>MCC-2BR-4</t>
+  </si>
+  <si>
+    <t>MCC-1BR-7</t>
+  </si>
+  <si>
+    <t>MCC-1AR-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-2AR-2</t>
+  </si>
+  <si>
+    <t>MCC-2AF-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-1AR-2</t>
+  </si>
+  <si>
+    <t>MCC-2AR-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-1AF-2</t>
+  </si>
+  <si>
+    <t>MCC-2AF-2</t>
+  </si>
+  <si>
+    <t>MCC-2AR-5</t>
+  </si>
+  <si>
+    <t>MCC-1AF-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-2AF-5</t>
+  </si>
+  <si>
+    <t>MCC-2AR-4</t>
+  </si>
+  <si>
+    <t>MCC-2AR-6</t>
+  </si>
+  <si>
+    <t>MCC-3BR-2</t>
+  </si>
+  <si>
+    <t>MCC-1AF-5</t>
+  </si>
+  <si>
+    <t>MCC-1AR-6</t>
+  </si>
+  <si>
+    <t>MCC-2BR-1</t>
+  </si>
+  <si>
+    <t>MCC-2AR-7</t>
+  </si>
+  <si>
+    <t>MCC-1AF-6</t>
+  </si>
+  <si>
+    <t>MCC-1AR-8</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-2BF-2</t>
+  </si>
+  <si>
+    <t>MCC-1AF-3</t>
+  </si>
+  <si>
+    <t>MCC-2AR-3</t>
+  </si>
+  <si>
+    <t>MCC-3BF-2</t>
+  </si>
+  <si>
+    <t>MCC-1BR-3</t>
+  </si>
+  <si>
+    <t>MCC-1BR-4</t>
+  </si>
+  <si>
+    <t>MCC-2BR-3</t>
+  </si>
+  <si>
+    <t>MCC-3BR-3</t>
+  </si>
+  <si>
+    <t>MCC-1AR-3</t>
+  </si>
+  <si>
+    <t>MCC-1BR-2</t>
+  </si>
+  <si>
+    <t>MCC-3AF-2</t>
+  </si>
+  <si>
+    <t>MCC-1BR-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-1BR-8</t>
+  </si>
+  <si>
+    <t>MCC-2BF-3</t>
+  </si>
+  <si>
+    <t>MCC-2BR-2</t>
+  </si>
+  <si>
+    <t>23-CP-003</t>
+  </si>
+  <si>
+    <t>A20-DCP-502</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-EPB-BAT-301</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-ETLL-402</t>
+  </si>
+  <si>
+    <t>A20-HP-501</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-HP-K2301</t>
+  </si>
+  <si>
+    <t>A20-HP-K2601</t>
+  </si>
+  <si>
+    <t>A20-HP-K2801</t>
+  </si>
+  <si>
+    <t>A20-MVP-401</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-UPSD-601-A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-UPSD-601-B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A20-VSDS-01-A             MP-2202A</t>
+  </si>
+  <si>
+    <t>A20-VSDS-01-B              MP-2202B</t>
+  </si>
+  <si>
+    <t>HO-2301</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HO-2601</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-23001</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-23004</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-23005</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-23025</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-26002</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-26003</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-26004</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-26035</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-28014</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-28015</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-28016</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>HV-28017</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-H1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-H2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-KM1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-PM1</t>
+  </si>
+  <si>
+    <t>K-2301-PM2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-PM4</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-PM5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2301-PM8</t>
+  </si>
+  <si>
+    <t>K-2301-PM9</t>
+  </si>
+  <si>
+    <t>K-2301-PM10</t>
+  </si>
+  <si>
+    <t>K-2601-H1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2601-H2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2601-PM1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2601-PM2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2601-PM4</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2601-PM5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-2801-PM2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ME-2720</t>
+  </si>
+  <si>
+    <t>MP-2103A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2103B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2110A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2110B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2115A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2115B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2150A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2150B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2202A-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2202B-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2203A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2203B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2204A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2204B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2211A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2211B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2212A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2212B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2213A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2213B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2301A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2301B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2302A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2302B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2306A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2306B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2307A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2307B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2311A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2311B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGC CONDENSER TUBE CLEANING SYSTEM(LOCAL PANEL)</t>
+  </si>
+  <si>
+    <t>ЭКСПАНДЕР-КОМПРЕССОРА КАБИНЕТ AMB</t>
+  </si>
+  <si>
+    <t>BATTERY FOR 400V EMERGENCY GENERATOR</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSFORMER 400/400-230V - 200KVA</t>
+  </si>
+  <si>
+    <t>EXPANDER-COMPRESSOR SEAL GAS HEATER CABINET</t>
+  </si>
+  <si>
+    <t>CGC SEAL GAS HEATER PANEL</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2C SEAL GAS HEATER PANEL</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C3C SEAL GAS HEATER PANEL</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOV POWER DISTRIBUTION BOARD</t>
+  </si>
+  <si>
+    <t>DC CHARGER (EMERGENCY)</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC CHARGER</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>VVVF PANEL (TAR PRODUCT PUMP A)</t>
+  </si>
+  <si>
+    <t>VVVF PANEL (TAR PRODUCT PUMP B)</t>
+  </si>
+  <si>
+    <t>CGC SHELTER OVERHEAD CRANE</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2C/C3C COMPRESSOR SHELTER OVERHEAD CRANE</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOV (BUTTERFLY)</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOV (GATE)</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGC OIL HEATER A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGC OIL HEATER B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Двигатель ускорителя уплотнительного газа для компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Главный масляной насос компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос валоповоротного устройства компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Аварийный масляный насос компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос охлаждающего масла компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Avto cleaning</t>
+  </si>
+  <si>
+    <t>Actuator collector</t>
+  </si>
+  <si>
+    <t>Actuator screen</t>
+  </si>
+  <si>
+    <t>C2C/C3C OIL HEATER A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2C/C3C OIL HEATER B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Главный масляной насос компрессоров C2/C3 фракций</t>
+  </si>
+  <si>
+    <t>Насос валоповоротного устройства компрессора С2 фракций</t>
+  </si>
+  <si>
+    <t>Аварийный масляный насос компрессоров C2/C3 фракций</t>
+  </si>
+  <si>
+    <t>Насос валоповоротного устройства компрессора С3 фракций</t>
+  </si>
+  <si>
+    <t>Панель управления Автоматическая система очистки</t>
+  </si>
+  <si>
+    <t>Насос A промывки жидкого сырья</t>
+  </si>
+  <si>
+    <t>Насос B промывки жидкого сырья</t>
+  </si>
+  <si>
+    <t>Насос A рециркуляции реактора гидрирования С4 фракций</t>
+  </si>
+  <si>
+    <t>Насос B рециркуляции реактора гидрирования С4 фракций</t>
+  </si>
+  <si>
+    <t>Насос А впрыска ДМДС</t>
+  </si>
+  <si>
+    <t>Насос B впрыска ДМДС</t>
+  </si>
+  <si>
+    <t>Насос A конденсата нагревателя сырья реактора гидрирования С4 фракций</t>
+  </si>
+  <si>
+    <t>Насос B конденсата нагревателя сырья реактора гидрирования С4 фракций</t>
+  </si>
+  <si>
+    <t>Система уплотнений B План54</t>
+  </si>
+  <si>
+    <t>Насос А топливного масла</t>
+  </si>
+  <si>
+    <t>Насос B топливного масла</t>
+  </si>
+  <si>
+    <t>Насос А разжижителя</t>
+  </si>
+  <si>
+    <t>Насос B разжижителя</t>
+  </si>
+  <si>
+    <t>Насос A кубового продукта отпарной колонны технологического конденсата</t>
+  </si>
+  <si>
+    <t>Насос В кубового продукта отпарной колонны технологического конденсата</t>
+  </si>
+  <si>
+    <t>Насос А чистого технологического конденсата</t>
+  </si>
+  <si>
+    <t>Насос B чистого технологического конденсата</t>
+  </si>
+  <si>
+    <t>Насос A орошения тяжелого дистиллята</t>
+  </si>
+  <si>
+    <t>Насос В орошения тяжелого дистиллята</t>
+  </si>
+  <si>
+    <t>Насос А конденсата компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос B конденсата компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос А сепаратора на всасе 1 ступени компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос B сепаратора на всасе 1 ступени компрессора пирогаза</t>
+  </si>
+  <si>
+    <t>Насос A впрыска промывочного масла</t>
+  </si>
+  <si>
+    <t>Насос В впрыска промывочного масла</t>
+  </si>
+  <si>
+    <t>Насос А подпитки щелочи</t>
+  </si>
+  <si>
+    <t>Насос B подпитки щелочи</t>
+  </si>
+  <si>
+    <t>Насос А кубового продукта отпарной колонны дистиллята</t>
+  </si>
+  <si>
+    <t>Насос B кубового продукта отпарной колонны дистиллята</t>
+  </si>
+  <si>
+    <t>LF-02A-1</t>
+  </si>
+  <si>
+    <t>LM-01B-1</t>
+  </si>
+  <si>
+    <t>LM-01B-2</t>
+  </si>
+  <si>
+    <t>LM-01B-5</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>LM-12B-1</t>
+  </si>
+  <si>
+    <t>LM-44B-4</t>
+  </si>
+  <si>
+    <t>LM-32B-1</t>
+  </si>
+  <si>
+    <t>LM-32B-4</t>
+  </si>
+  <si>
+    <t>LM-44B-3</t>
+  </si>
+  <si>
+    <t>LM-44B-1</t>
+  </si>
+  <si>
+    <t>LM-01B-4</t>
+  </si>
+  <si>
+    <t>LM-32B-6</t>
+  </si>
+  <si>
+    <t>LM-44B-5</t>
+  </si>
+  <si>
+    <t>LM-22B-1</t>
+  </si>
+  <si>
+    <t>200KVA</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1366,8 +2179,59 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1377,6 +2241,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1405,24 +2275,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1452,11 +2327,53 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{A2B79AB5-A776-46DB-90D8-9CC280B1FFA3}"/>
+    <cellStyle name="표준 2" xfId="2" xr:uid="{4809AEED-97A9-46D9-98DA-7BAC10EEA86F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1768,8 +2685,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F168"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F253"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
@@ -1778,7 +2695,7 @@
     <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
         <v>366</v>
       </c>
@@ -1798,7 +2715,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1818,7 +2735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1838,7 +2755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1858,7 +2775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1878,7 +2795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1898,7 +2815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1918,7 +2835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1938,7 +2855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1958,7 +2875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1978,7 +2895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1998,7 +2915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -2018,7 +2935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -2038,7 +2955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -2058,7 +2975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2078,7 +2995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2098,7 +3015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
@@ -2118,7 +3035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
@@ -2138,7 +3055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -2158,7 +3075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -2178,7 +3095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -2198,7 +3115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
@@ -2218,7 +3135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -2238,7 +3155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
@@ -2258,7 +3175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
@@ -2278,7 +3195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
@@ -2298,7 +3215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -2318,7 +3235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>67</v>
       </c>
@@ -2338,7 +3255,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>71</v>
       </c>
@@ -2358,7 +3275,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
         <v>74</v>
       </c>
@@ -2378,7 +3295,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
         <v>76</v>
       </c>
@@ -2398,7 +3315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
         <v>78</v>
       </c>
@@ -2418,7 +3335,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -2438,7 +3355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
@@ -2458,7 +3375,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
@@ -2478,7 +3395,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
         <v>90</v>
       </c>
@@ -2498,7 +3415,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
         <v>93</v>
       </c>
@@ -2518,7 +3435,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>96</v>
       </c>
@@ -2538,7 +3455,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
         <v>99</v>
       </c>
@@ -2558,7 +3475,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
@@ -2578,7 +3495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
         <v>105</v>
       </c>
@@ -2598,7 +3515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
         <v>108</v>
       </c>
@@ -2618,7 +3535,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
         <v>111</v>
       </c>
@@ -2638,7 +3555,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
         <v>114</v>
       </c>
@@ -2658,7 +3575,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
         <v>118</v>
       </c>
@@ -2678,7 +3595,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
         <v>120</v>
       </c>
@@ -2698,7 +3615,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
         <v>123</v>
       </c>
@@ -2718,7 +3635,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>125</v>
       </c>
@@ -2738,7 +3655,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
         <v>129</v>
       </c>
@@ -2758,7 +3675,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
         <v>132</v>
       </c>
@@ -2778,7 +3695,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
         <v>135</v>
       </c>
@@ -2798,7 +3715,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -2818,7 +3735,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
         <v>142</v>
       </c>
@@ -2838,7 +3755,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" s="2" t="s">
         <v>144</v>
       </c>
@@ -2858,7 +3775,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
@@ -2878,7 +3795,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
         <v>149</v>
       </c>
@@ -2898,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -2918,7 +3835,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
         <v>155</v>
       </c>
@@ -2938,7 +3855,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
@@ -2958,7 +3875,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
         <v>161</v>
       </c>
@@ -2978,7 +3895,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
         <v>164</v>
       </c>
@@ -2998,7 +3915,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" s="4" t="s">
         <v>167</v>
       </c>
@@ -3018,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
         <v>170</v>
       </c>
@@ -3038,7 +3955,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>173</v>
       </c>
@@ -3058,7 +3975,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
         <v>176</v>
       </c>
@@ -3078,7 +3995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
         <v>179</v>
       </c>
@@ -3098,7 +4015,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
         <v>182</v>
       </c>
@@ -3118,7 +4035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
         <v>185</v>
       </c>
@@ -3138,7 +4055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
         <v>188</v>
       </c>
@@ -3158,7 +4075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
         <v>191</v>
       </c>
@@ -3178,7 +4095,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
         <v>194</v>
       </c>
@@ -3198,7 +4115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
         <v>197</v>
       </c>
@@ -3218,7 +4135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
         <v>200</v>
       </c>
@@ -3238,7 +4155,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
         <v>203</v>
       </c>
@@ -3258,7 +4175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
         <v>206</v>
       </c>
@@ -3279,7 +4196,7 @@
         <v>LF-02A</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
         <v>209</v>
       </c>
@@ -3299,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
         <v>212</v>
       </c>
@@ -3319,7 +4236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
         <v>215</v>
       </c>
@@ -3339,7 +4256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
         <v>217</v>
       </c>
@@ -3359,7 +4276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>219</v>
       </c>
@@ -3379,7 +4296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
         <v>219</v>
       </c>
@@ -3399,7 +4316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" s="5" t="s">
         <v>222</v>
       </c>
@@ -3419,7 +4336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
         <v>222</v>
       </c>
@@ -3439,7 +4356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
         <v>225</v>
       </c>
@@ -3459,7 +4376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
         <v>225</v>
       </c>
@@ -3479,7 +4396,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
         <v>230</v>
       </c>
@@ -3499,7 +4416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
         <v>232</v>
       </c>
@@ -3519,7 +4436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
         <v>234</v>
       </c>
@@ -3539,7 +4456,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>236</v>
       </c>
@@ -3559,7 +4476,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
         <v>238</v>
       </c>
@@ -3579,7 +4496,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
         <v>240</v>
       </c>
@@ -3599,7 +4516,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
         <v>242</v>
       </c>
@@ -3619,7 +4536,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
         <v>245</v>
       </c>
@@ -3639,7 +4556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
         <v>247</v>
       </c>
@@ -3659,7 +4576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
         <v>249</v>
       </c>
@@ -3679,7 +4596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
         <v>251</v>
       </c>
@@ -3699,7 +4616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>251</v>
       </c>
@@ -3719,7 +4636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
         <v>253</v>
       </c>
@@ -3739,7 +4656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
         <v>255</v>
       </c>
@@ -3759,7 +4676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
         <v>257</v>
       </c>
@@ -3779,7 +4696,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
         <v>259</v>
       </c>
@@ -3799,7 +4716,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>261</v>
       </c>
@@ -3819,7 +4736,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>263</v>
       </c>
@@ -3839,7 +4756,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
         <v>265</v>
       </c>
@@ -3859,7 +4776,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
         <v>267</v>
       </c>
@@ -3879,7 +4796,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
         <v>269</v>
       </c>
@@ -3899,7 +4816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
         <v>272</v>
       </c>
@@ -3919,7 +4836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
         <v>275</v>
       </c>
@@ -3939,7 +4856,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
         <v>279</v>
       </c>
@@ -3959,7 +4876,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
         <v>282</v>
       </c>
@@ -3979,7 +4896,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
         <v>285</v>
       </c>
@@ -3999,7 +4916,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
         <v>288</v>
       </c>
@@ -4019,7 +4936,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>291</v>
       </c>
@@ -4039,7 +4956,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>294</v>
       </c>
@@ -4059,7 +4976,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>297</v>
       </c>
@@ -4079,7 +4996,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>300</v>
       </c>
@@ -4099,7 +5016,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>303</v>
       </c>
@@ -4119,7 +5036,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>306</v>
       </c>
@@ -4139,7 +5056,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>309</v>
       </c>
@@ -4159,7 +5076,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>312</v>
       </c>
@@ -4179,7 +5096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>315</v>
       </c>
@@ -4199,7 +5116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
         <v>318</v>
       </c>
@@ -4219,7 +5136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
         <v>321</v>
       </c>
@@ -4239,7 +5156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
         <v>324</v>
       </c>
@@ -4259,7 +5176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
         <v>328</v>
       </c>
@@ -4279,7 +5196,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -4299,7 +5216,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
         <v>335</v>
       </c>
@@ -4319,7 +5236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
         <v>338</v>
       </c>
@@ -4339,7 +5256,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
         <v>341</v>
       </c>
@@ -4359,7 +5276,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
         <v>344</v>
       </c>
@@ -4379,7 +5296,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
         <v>346</v>
       </c>
@@ -4399,7 +5316,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +5336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
         <v>350</v>
       </c>
@@ -4439,7 +5356,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
         <v>353</v>
       </c>
@@ -4459,7 +5376,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
         <v>355</v>
       </c>
@@ -4479,7 +5396,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
         <v>357</v>
       </c>
@@ -4499,7 +5416,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
         <v>359</v>
       </c>
@@ -4519,7 +5436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
         <v>361</v>
       </c>
@@ -4539,7 +5456,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
         <v>363</v>
       </c>
@@ -4559,7 +5476,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
         <v>372</v>
       </c>
@@ -4579,7 +5496,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
         <v>374</v>
       </c>
@@ -4599,7 +5516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
         <v>376</v>
       </c>
@@ -4619,7 +5536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
         <v>378</v>
       </c>
@@ -4639,7 +5556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" s="9" t="s">
         <v>372</v>
       </c>
@@ -4659,7 +5576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
         <v>380</v>
       </c>
@@ -4679,7 +5596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
         <v>382</v>
       </c>
@@ -4699,7 +5616,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" s="2" t="s">
         <v>384</v>
       </c>
@@ -4719,7 +5636,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" s="2" t="s">
         <v>386</v>
       </c>
@@ -4739,7 +5656,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
         <v>388</v>
       </c>
@@ -4759,7 +5676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
         <v>389</v>
       </c>
@@ -4779,7 +5696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
         <v>391</v>
       </c>
@@ -4799,7 +5716,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
         <v>392</v>
       </c>
@@ -4819,7 +5736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" s="2" t="s">
         <v>393</v>
       </c>
@@ -4839,7 +5756,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" s="2" t="s">
         <v>395</v>
       </c>
@@ -4859,7 +5776,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
         <v>397</v>
       </c>
@@ -4879,7 +5796,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" s="2" t="s">
         <v>399</v>
       </c>
@@ -4899,7 +5816,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" s="5" t="s">
         <v>401</v>
       </c>
@@ -4919,7 +5836,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" s="2" t="s">
         <v>403</v>
       </c>
@@ -4939,7 +5856,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6">
       <c r="A159" s="10" t="s">
         <v>405</v>
       </c>
@@ -4959,7 +5876,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" s="2" t="s">
         <v>406</v>
       </c>
@@ -4979,7 +5896,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
         <v>408</v>
       </c>
@@ -4999,7 +5916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" s="2" t="s">
         <v>410</v>
       </c>
@@ -5019,7 +5936,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
         <v>217</v>
       </c>
@@ -5039,7 +5956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" s="2" t="s">
         <v>230</v>
       </c>
@@ -5059,7 +5976,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
         <v>412</v>
       </c>
@@ -5079,7 +5996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" s="2" t="s">
         <v>414</v>
       </c>
@@ -5099,7 +6016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
         <v>416</v>
       </c>
@@ -5119,24 +6036,1724 @@
         <v>422</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" ht="15.75">
       <c r="A168" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="B168">
-        <v>12512</v>
-      </c>
-      <c r="C168" s="6">
-        <v>1212</v>
-      </c>
-      <c r="D168" s="7">
-        <v>1212</v>
-      </c>
-      <c r="E168" s="7">
-        <v>2121</v>
-      </c>
-      <c r="F168" s="7">
-        <v>212</v>
+      <c r="B168" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E168" s="13">
+        <v>250</v>
+      </c>
+      <c r="F168" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="15.75">
+      <c r="A169" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="E169" s="13">
+        <v>250</v>
+      </c>
+      <c r="F169" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="15.75">
+      <c r="A170" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="E170" s="13">
+        <v>250</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="15.75">
+      <c r="A171" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="E171" s="13">
+        <v>250</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="15.75">
+      <c r="A172" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="E172" s="13">
+        <v>250</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="15.75">
+      <c r="A173" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="E173" s="13">
+        <v>380</v>
+      </c>
+      <c r="F173" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="15.75">
+      <c r="A174" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="E174" s="13">
+        <v>380</v>
+      </c>
+      <c r="F174" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="15.75">
+      <c r="A175" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="E175" s="13">
+        <v>320</v>
+      </c>
+      <c r="F175" s="13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="15.75">
+      <c r="A176" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E176" s="13">
+        <v>320</v>
+      </c>
+      <c r="F176" s="13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="15.75">
+      <c r="A177" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E177" s="13">
+        <v>180</v>
+      </c>
+      <c r="F177" s="13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15.75">
+      <c r="A178" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="E178" s="13">
+        <v>180</v>
+      </c>
+      <c r="F178" s="13" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="15.75">
+      <c r="A179" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C179" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D179" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E179" s="23">
+        <v>3.3</v>
+      </c>
+      <c r="F179" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="15.75">
+      <c r="A180" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D180" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="E180" s="23">
+        <v>5</v>
+      </c>
+      <c r="F180" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="15.75">
+      <c r="A181" s="18" t="s">
+        <v>518</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D181" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="E181" s="23">
+        <v>71.44</v>
+      </c>
+      <c r="F181" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="15.75">
+      <c r="A182" s="18" t="s">
+        <v>519</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D182" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>669</v>
+      </c>
+      <c r="F182" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="15.75">
+      <c r="A183" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C183" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D183" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="E183" s="23">
+        <v>22.4</v>
+      </c>
+      <c r="F183" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="15.75">
+      <c r="A184" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D184" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="E184" s="23">
+        <v>25</v>
+      </c>
+      <c r="F184" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="15.75">
+      <c r="A185" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C185" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D185" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E185" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="F185" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="15.75">
+      <c r="A186" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C186" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D186" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E186" s="23">
+        <v>4</v>
+      </c>
+      <c r="F186" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="15.75">
+      <c r="A187" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D187" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="E187" s="23">
+        <v>20.23</v>
+      </c>
+      <c r="F187" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="15.75">
+      <c r="A188" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C188" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D188" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="E188" s="23">
+        <v>30</v>
+      </c>
+      <c r="F188" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="15.75">
+      <c r="A189" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C189" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D189" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="E189" s="23">
+        <v>30</v>
+      </c>
+      <c r="F189" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="31.5">
+      <c r="A190" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="B190" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="C190" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D190" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="E190" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F190" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="31.5">
+      <c r="A191" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="B191" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="C191" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D191" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="E191" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F191" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="15.75">
+      <c r="A192" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C192" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D192" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="E192" s="23">
+        <v>15</v>
+      </c>
+      <c r="F192" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="15.75">
+      <c r="A193" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C193" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D193" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="E193" s="23">
+        <v>15</v>
+      </c>
+      <c r="F193" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="15.75">
+      <c r="A194" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C194" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D194" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="E194" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F194" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="15.75">
+      <c r="A195" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C195" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D195" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="E195" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F195" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="15.75">
+      <c r="A196" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C196" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D196" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="E196" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F196" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="15.75">
+      <c r="A197" s="18" t="s">
+        <v>534</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C197" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D197" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="E197" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F197" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="15.75">
+      <c r="A198" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C198" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D198" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="E198" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F198" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="15.75">
+      <c r="A199" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C199" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D199" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="E199" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F199" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="15.75">
+      <c r="A200" s="18" t="s">
+        <v>537</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C200" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D200" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="E200" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F200" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="15.75">
+      <c r="A201" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C201" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D201" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="E201" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F201" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="15.75">
+      <c r="A202" s="18" t="s">
+        <v>539</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C202" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D202" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="E202" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F202" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="15.75">
+      <c r="A203" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C203" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D203" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="E203" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F203" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="15.75">
+      <c r="A204" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C204" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D204" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="E204" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F204" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="15.75">
+      <c r="A205" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C205" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D205" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E205" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F205" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="15.75">
+      <c r="A206" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C206" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D206" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E206" s="23">
+        <v>30</v>
+      </c>
+      <c r="F206" s="23" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="15.75">
+      <c r="A207" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C207" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D207" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="E207" s="23">
+        <v>30</v>
+      </c>
+      <c r="F207" s="23" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="15.75">
+      <c r="A208" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C208" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D208" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="E208" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F208" s="23" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="15.75">
+      <c r="A209" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C209" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D209" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="E209" s="23">
+        <v>37</v>
+      </c>
+      <c r="F209" s="23" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="15.75">
+      <c r="A210" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C210" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D210" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="E210" s="23">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F210" s="23" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="15.75">
+      <c r="A211" s="18" t="s">
+        <v>548</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C211" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D211" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="E211" s="23">
+        <v>37</v>
+      </c>
+      <c r="F211" s="23" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="15.75">
+      <c r="A212" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C212" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D212" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="E212" s="23">
+        <v>4</v>
+      </c>
+      <c r="F212" s="23" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="30">
+      <c r="A213" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="B213" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="C213" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D213" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E213" s="24">
+        <v>3</v>
+      </c>
+      <c r="F213" s="23" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="30">
+      <c r="A214" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="B214" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="C214" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D214" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E214" s="23">
+        <v>0.06</v>
+      </c>
+      <c r="F214" s="23" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="30">
+      <c r="A215" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="B215" s="22" t="s">
+        <v>617</v>
+      </c>
+      <c r="C215" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D215" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E215" s="23">
+        <v>0.06</v>
+      </c>
+      <c r="F215" s="23" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="15.75">
+      <c r="A216" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C216" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D216" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="E216" s="23">
+        <v>30</v>
+      </c>
+      <c r="F216" s="23" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="15.75">
+      <c r="A217" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C217" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D217" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E217" s="23">
+        <v>30</v>
+      </c>
+      <c r="F217" s="23" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="15.75">
+      <c r="A218" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C218" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D218" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="E218" s="23">
+        <v>37</v>
+      </c>
+      <c r="F218" s="23" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="15.75">
+      <c r="A219" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C219" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D219" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E219" s="23">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F219" s="23" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="15.75">
+      <c r="A220" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C220" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D220" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="E220" s="23">
+        <v>37</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="15.75">
+      <c r="A221" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C221" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D221" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="E221" s="23">
+        <v>4</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="15.75">
+      <c r="A222" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C222" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D222" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="E222" s="23">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F222" s="23" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="15.75">
+      <c r="A223" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C223" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D223" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="E223" s="23">
+        <v>15</v>
+      </c>
+      <c r="F223" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="15.75">
+      <c r="A224" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C224" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D224" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="E224" s="23">
+        <v>4</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="15.75">
+      <c r="A225" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C225" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D225" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="E225" s="23">
+        <v>4</v>
+      </c>
+      <c r="F225" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="15.75">
+      <c r="A226" s="18" t="s">
+        <v>563</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C226" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D226" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="E226" s="23">
+        <v>132</v>
+      </c>
+      <c r="F226" s="23" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="15.75">
+      <c r="A227" s="18" t="s">
+        <v>564</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C227" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D227" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="E227" s="23">
+        <v>132</v>
+      </c>
+      <c r="F227" s="23" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="15.75">
+      <c r="A228" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C228" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D228" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="E228" s="23">
+        <v>11</v>
+      </c>
+      <c r="F228" s="23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="15.75">
+      <c r="A229" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C229" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D229" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="E229" s="23">
+        <v>11</v>
+      </c>
+      <c r="F229" s="23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="15.75">
+      <c r="A230" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C230" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D230" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="E230" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="F230" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="15.75">
+      <c r="A231" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D231" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="E231" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="F231" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="15.75">
+      <c r="A232" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C232" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D232" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="E232" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F232" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="15.75">
+      <c r="A233" s="18" t="s">
+        <v>570</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C233" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D233" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E233" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F233" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="15.75">
+      <c r="A234" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C234" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D234" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="E234" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F234" s="23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="15.75">
+      <c r="A235" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C235" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D235" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E235" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F235" s="23" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="15.75">
+      <c r="A236" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C236" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D236" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="E236" s="23">
+        <v>15</v>
+      </c>
+      <c r="F236" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="15.75">
+      <c r="A237" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C237" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D237" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="E237" s="23">
+        <v>15</v>
+      </c>
+      <c r="F237" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="15.75">
+      <c r="A238" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C238" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D238" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="E238" s="23">
+        <v>75</v>
+      </c>
+      <c r="F238" s="23" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="15.75">
+      <c r="A239" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C239" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D239" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="E239" s="23">
+        <v>75</v>
+      </c>
+      <c r="F239" s="23" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="15.75">
+      <c r="A240" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C240" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D240" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E240" s="23">
+        <v>37</v>
+      </c>
+      <c r="F240" s="23" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="15.75">
+      <c r="A241" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C241" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D241" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="E241" s="23">
+        <v>37</v>
+      </c>
+      <c r="F241" s="23" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="15.75">
+      <c r="A242" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C242" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D242" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="E242" s="23">
+        <v>22</v>
+      </c>
+      <c r="F242" s="23" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="15.75">
+      <c r="A243" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C243" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D243" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="E243" s="23">
+        <v>22</v>
+      </c>
+      <c r="F243" s="23" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="15.75">
+      <c r="A244" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C244" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D244" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="E244" s="23">
+        <v>75</v>
+      </c>
+      <c r="F244" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="15.75">
+      <c r="A245" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C245" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D245" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="E245" s="23">
+        <v>75</v>
+      </c>
+      <c r="F245" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="15.75">
+      <c r="A246" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C246" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D246" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E246" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F246" s="23" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="15.75">
+      <c r="A247" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C247" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D247" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="E247" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F247" s="23" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="15.75">
+      <c r="A248" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C248" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D248" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="E248" s="23">
+        <v>75</v>
+      </c>
+      <c r="F248" s="23" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="15.75">
+      <c r="A249" s="18" t="s">
+        <v>586</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C249" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D249" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="E249" s="23">
+        <v>75</v>
+      </c>
+      <c r="F249" s="23" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="15.75">
+      <c r="A250" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C250" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D250" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="E250" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F250" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="15.75">
+      <c r="A251" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C251" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D251" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="E251" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F251" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="15.75">
+      <c r="A252" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C252" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D252" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="E252" s="23">
+        <v>22</v>
+      </c>
+      <c r="F252" s="23" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="15.75">
+      <c r="A253" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C253" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D253" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="E253" s="23">
+        <v>22</v>
+      </c>
+      <c r="F253" s="23" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE236AD5-C272-4007-BB6C-0A64F30DCB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01AB0F3-B3CD-44CE-8A0F-145E087AD062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="859">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -2131,6 +2131,644 @@
   <si>
     <t>200KVA</t>
     <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2320A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2320B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2321</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2322</t>
+  </si>
+  <si>
+    <t>MP-2323A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2323B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2324A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2324B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2325A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2325B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2326A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2326B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2327A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2327B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2328A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2328B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2329</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2340A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2340B</t>
+  </si>
+  <si>
+    <t>MP-2411A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2411B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2420A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2420B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2422A</t>
+  </si>
+  <si>
+    <t>MP-2422B</t>
+  </si>
+  <si>
+    <t>MP-2510A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2510B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2601A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2601B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2610A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2610B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2611A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2611B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2620A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2620B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2624A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2624B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2625A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2625B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2710A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2710B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2721A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2721B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2801A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2801B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2802</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2901A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2901B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2903A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2903B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2904</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2906A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2906B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP-2908</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-2201A-E2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-2201A-M1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-2210A-E2</t>
+  </si>
+  <si>
+    <t>P-2210A-M1</t>
+  </si>
+  <si>
+    <t>X-2201A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2201B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2201C</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2201D</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2202A</t>
+  </si>
+  <si>
+    <t>X-2202B</t>
+  </si>
+  <si>
+    <t>X-2320A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2320B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2320C</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2330-MP1A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2330-MP1B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2401A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2401B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2402A</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>X-2402B</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Насос А слабой щелочи</t>
+  </si>
+  <si>
+    <t>Насос B слабой щелочи</t>
+  </si>
+  <si>
+    <t>Насос средней щелочи</t>
+  </si>
+  <si>
+    <t>Насос крепкой щелочи</t>
+  </si>
+  <si>
+    <t>Насос А промывочной воды колонны щелочной промывки</t>
+  </si>
+  <si>
+    <t>Насос B промывочной воды колонны щелочной промывки</t>
+  </si>
+  <si>
+    <t>Насос А отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос B отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос А отстойника щелочи</t>
+  </si>
+  <si>
+    <t>Насос B отстойника щелочи</t>
+  </si>
+  <si>
+    <t>Сырьевой насос А отпарной колонны отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Сырьевой насос B отпарной колонны отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос А циркуляции дистиллята сепаратора снятой щелочи</t>
+  </si>
+  <si>
+    <t>Насос B циркуляции дистиллята сепаратора снятой щелочи</t>
+  </si>
+  <si>
+    <t>Насос А перекачки отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос B перекачки отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос снятого масла с резервуара хранения отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос А серной кислоты</t>
+  </si>
+  <si>
+    <t>Насос B серной кислоты</t>
+  </si>
+  <si>
+    <t>Насос А конденсата ребойлера депропанизатора</t>
+  </si>
+  <si>
+    <t>Насос B конденсата ребойлера депропанизатора</t>
+  </si>
+  <si>
+    <t>Насос A орошения дебутанизатора</t>
+  </si>
+  <si>
+    <t>Насос В орошения дебутанизатора</t>
+  </si>
+  <si>
+    <t>Насос А кубового продукта дебутанизатора</t>
+  </si>
+  <si>
+    <t>Насос B кубового продукта дебутанизатора</t>
+  </si>
+  <si>
+    <t>Насос А орошения деметанизатора</t>
+  </si>
+  <si>
+    <t>Насос B орошения деметанизатора</t>
+  </si>
+  <si>
+    <t>Насос А конденсата компрессора С2 фракций</t>
+  </si>
+  <si>
+    <t>Насос B конденсата компрессора С2 фракций</t>
+  </si>
+  <si>
+    <t>Насос А орошения деэтанизатора</t>
+  </si>
+  <si>
+    <t>Насос B орошения деэтанизатора</t>
+  </si>
+  <si>
+    <t>Насос А кубового продукта деэтанизатора</t>
+  </si>
+  <si>
+    <t>Насос B кубового продукта деэтанизатора</t>
+  </si>
+  <si>
+    <t>Насос А рециркуляции этана</t>
+  </si>
+  <si>
+    <t>Насос B рециркуляции этана</t>
+  </si>
+  <si>
+    <t>Насос A этиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос В этиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос А конденсата испарителя этиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос B конденсата испарителя этиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос А рециркуляции реактора МАПД</t>
+  </si>
+  <si>
+    <t>Насос B рециркуляции реактора МАПД</t>
+  </si>
+  <si>
+    <t>Насос A пропиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос в пропиленового продукта</t>
+  </si>
+  <si>
+    <t>Насос А конденсата компрессора С3 фракций</t>
+  </si>
+  <si>
+    <t>Насос B конденсата компрессора С3 фракций</t>
+  </si>
+  <si>
+    <t>Насос откачки хладагента С3 фракций</t>
+  </si>
+  <si>
+    <t>Насос A испарительного барабана подозрительного конденсата</t>
+  </si>
+  <si>
+    <t>Насос в испарительного барабана подозрительного конденсата</t>
+  </si>
+  <si>
+    <t>Насос A испарительного барабана очищенного конденсата ATM</t>
+  </si>
+  <si>
+    <t>Насос В испарительного барабана очищенного конденсата ATM</t>
+  </si>
+  <si>
+    <t>Нагнетательный насос коллектора закалочного масла</t>
+  </si>
+  <si>
+    <t>Насос А отработанной воды</t>
+  </si>
+  <si>
+    <t>Насос B отработанной воды</t>
+  </si>
+  <si>
+    <t>Насос коллектора теплых углеводородов</t>
+  </si>
+  <si>
+    <t>QUENCH OIL CIRCULATION LUBE OIL SYSTEM A HEATER</t>
+  </si>
+  <si>
+    <t>Двигатель А системы смазочного масла насоса циркуляции закалочного масло</t>
+  </si>
+  <si>
+    <t>QUENCH WATER CIRCULATION LUBE OIL SYSTEM A HEATER</t>
+  </si>
+  <si>
+    <t>Двигатель А системы смазочного масла насоса циркуляции закалочного воды</t>
+  </si>
+  <si>
+    <t>Дозирующий насос А системы вспрыска амина в закалочную воду/технологический конденсат</t>
+  </si>
+  <si>
+    <t>Дозирующий насос В системы вспрыска амина в закалочную воду/технологический конденсат</t>
+  </si>
+  <si>
+    <t>Дозирующий насос С системы вспрыска амина в закалочную воду/технологический конденсат</t>
+  </si>
+  <si>
+    <t>Дозирующий насос D системы вспрыска амина в закалочную воду/технологический конденсат</t>
+  </si>
+  <si>
+    <t>Дозирующий насос A системы впрыска деэмульгатора</t>
+  </si>
+  <si>
+    <t>Дозирующий насос В системы впрыска деэмульгатора</t>
+  </si>
+  <si>
+    <t>Дозирующий насос А системы впрыска стабилизатора щелочи</t>
+  </si>
+  <si>
+    <t>Дозирующий насос B системы впрыска стабилизатора щелочи</t>
+  </si>
+  <si>
+    <t>Дозирующий насос С системы впрыска стабилизатора щелочи</t>
+  </si>
+  <si>
+    <t>Насос A рециркуляции отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Насос В рециркуляции отработанной щелочи</t>
+  </si>
+  <si>
+    <t>Дозирующий насос A системы впрыска ингибитора полимеризации в депропанизаторе</t>
+  </si>
+  <si>
+    <t>Дозирующий насос В системы впрыска ингибитора полимеризации в депропанизаторе</t>
+  </si>
+  <si>
+    <t>Дозирующий насос А системы впрыска стабилизатора пиролизного дистиллята</t>
+  </si>
+  <si>
+    <t>Дозирующий насос B системы впрыска стабилизатора пиролизного дистиллята</t>
+  </si>
+  <si>
+    <t>MCC-3BR-4</t>
+  </si>
+  <si>
+    <t>MCC-1BF-2</t>
+  </si>
+  <si>
+    <t>MCC-2BF-4</t>
+  </si>
+  <si>
+    <t>MCC-3BF-4</t>
+  </si>
+  <si>
+    <t>MCC-1BR-5</t>
+  </si>
+  <si>
+    <t>MCC-3BR-5</t>
+  </si>
+  <si>
+    <t>MCC-3BR-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-1BF-5</t>
+  </si>
+  <si>
+    <t>MCC-2BF-6</t>
+  </si>
+  <si>
+    <t>MCC-3AF-6</t>
+  </si>
+  <si>
+    <t>MCC-1BF-7</t>
+  </si>
+  <si>
+    <t>MCC-1BR-6</t>
+  </si>
+  <si>
+    <t>MCC-2BR-6</t>
+  </si>
+  <si>
+    <t>MCC-3BR-6</t>
+  </si>
+  <si>
+    <t>MCC-2AF-7</t>
+  </si>
+  <si>
+    <t>MCC-3AF-4</t>
+  </si>
+  <si>
+    <t>MCC-3BF-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-3AR-2</t>
+  </si>
+  <si>
+    <t>MCC-2BF-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-3AR-6</t>
+  </si>
+  <si>
+    <t>MCC-2BR-7</t>
+  </si>
+  <si>
+    <t>MCC-2BR-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-1BF-3</t>
+  </si>
+  <si>
+    <t>MCC-3AF-3</t>
+  </si>
+  <si>
+    <t>MCC-1BR-9</t>
+  </si>
+  <si>
+    <t>MCC-2BF-5</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-3BF-3</t>
+  </si>
+  <si>
+    <t>MCC-1BF-6</t>
+  </si>
+  <si>
+    <t>MCC-1BF-1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCC-2BR-9</t>
+  </si>
+  <si>
+    <t>MCC-3AR-8</t>
+  </si>
+  <si>
+    <t>MCC-1AR-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCC-2BF-5 </t>
+  </si>
+  <si>
+    <t>MCC-3BF-5</t>
+  </si>
+  <si>
+    <t>LM-32B-5</t>
+  </si>
+  <si>
+    <t>LM-22B-2</t>
+  </si>
+  <si>
+    <t>LM-32B-3</t>
+  </si>
+  <si>
+    <t>LM-22B-4</t>
+  </si>
+  <si>
+    <t>LM-12B-2</t>
+  </si>
+  <si>
+    <t>LM-32B-2</t>
+  </si>
+  <si>
+    <t>LM-22B-3</t>
+  </si>
+  <si>
+    <t>LM-44B-2</t>
+  </si>
+  <si>
+    <t>LM-01B-3</t>
   </si>
 </sst>
 </file>
@@ -2251,7 +2889,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2287,6 +2925,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2297,7 +2959,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2367,6 +3029,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2685,7 +3362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7756,6 +8433,1466 @@
         <v>668</v>
       </c>
     </row>
+    <row r="254" spans="1:6" ht="15.75">
+      <c r="A254" s="19" t="s">
+        <v>670</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C254" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D254" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="E254" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F254" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="15.75">
+      <c r="A255" s="19" t="s">
+        <v>671</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C255" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D255" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="E255" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F255" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="15.75">
+      <c r="A256" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C256" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D256" s="17" t="s">
+        <v>817</v>
+      </c>
+      <c r="E256" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F256" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="15.75">
+      <c r="A257" s="19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C257" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D257" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="E257" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F257" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="15.75">
+      <c r="A258" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C258" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D258" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="E258" s="23">
+        <v>4</v>
+      </c>
+      <c r="F258" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="15.75">
+      <c r="A259" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C259" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D259" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E259" s="23">
+        <v>4</v>
+      </c>
+      <c r="F259" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="15.75">
+      <c r="A260" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C260" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D260" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="E260" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F260" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="15.75">
+      <c r="A261" s="19" t="s">
+        <v>677</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="C261" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D261" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="E261" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F261" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="15.75">
+      <c r="A262" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C262" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D262" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="E262" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F262" s="23" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="15.75">
+      <c r="A263" s="19" t="s">
+        <v>679</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C263" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D263" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="E263" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F263" s="23" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="15.75">
+      <c r="A264" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C264" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D264" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="E264" s="23">
+        <v>4</v>
+      </c>
+      <c r="F264" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="15.75">
+      <c r="A265" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C265" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D265" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="E265" s="23">
+        <v>4</v>
+      </c>
+      <c r="F265" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="15.75">
+      <c r="A266" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="C266" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D266" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="E266" s="23">
+        <v>30</v>
+      </c>
+      <c r="F266" s="23" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="15.75">
+      <c r="A267" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C267" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D267" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="E267" s="23">
+        <v>30</v>
+      </c>
+      <c r="F267" s="23" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="15.75">
+      <c r="A268" s="18" t="s">
+        <v>684</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C268" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D268" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="E268" s="23">
+        <v>22</v>
+      </c>
+      <c r="F268" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="15.75">
+      <c r="A269" s="18" t="s">
+        <v>685</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C269" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D269" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="E269" s="23">
+        <v>15</v>
+      </c>
+      <c r="F269" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="15.75">
+      <c r="A270" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C270" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D270" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="E270" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F270" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="15.75">
+      <c r="A271" s="18" t="s">
+        <v>687</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C271" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D271" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="E271" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F271" s="23" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="15.75">
+      <c r="A272" s="18" t="s">
+        <v>688</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C272" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D272" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="E272" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="F272" s="23" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="15.75">
+      <c r="A273" s="19" t="s">
+        <v>689</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="C273" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D273" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="E273" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F273" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="15.75">
+      <c r="A274" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C274" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D274" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="E274" s="23">
+        <v>5.5</v>
+      </c>
+      <c r="F274" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="15.75">
+      <c r="A275" s="18" t="s">
+        <v>691</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C275" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D275" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="E275" s="23">
+        <v>75</v>
+      </c>
+      <c r="F275" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="15.75">
+      <c r="A276" s="18" t="s">
+        <v>692</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C276" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D276" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="E276" s="23">
+        <v>75</v>
+      </c>
+      <c r="F276" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="15.75">
+      <c r="A277" s="19" t="s">
+        <v>693</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C277" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D277" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="E277" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="F277" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="15.75">
+      <c r="A278" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C278" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D278" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="E278" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="F278" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="15.75">
+      <c r="A279" s="19" t="s">
+        <v>695</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C279" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D279" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="E279" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="F279" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="15.75">
+      <c r="A280" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C280" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D280" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="E280" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="F280" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="15.75">
+      <c r="A281" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C281" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D281" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="E281" s="23">
+        <v>55</v>
+      </c>
+      <c r="F281" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="15.75">
+      <c r="A282" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C282" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D282" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="E282" s="23">
+        <v>55</v>
+      </c>
+      <c r="F282" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="15.75">
+      <c r="A283" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C283" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D283" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="E283" s="23">
+        <v>11</v>
+      </c>
+      <c r="F283" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="15.75">
+      <c r="A284" s="18" t="s">
+        <v>700</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C284" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D284" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="E284" s="23">
+        <v>11</v>
+      </c>
+      <c r="F284" s="23" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="15.75">
+      <c r="A285" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C285" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D285" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="E285" s="23">
+        <v>90</v>
+      </c>
+      <c r="F285" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="15.75">
+      <c r="A286" s="18" t="s">
+        <v>702</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C286" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D286" s="17" t="s">
+        <v>817</v>
+      </c>
+      <c r="E286" s="23">
+        <v>90</v>
+      </c>
+      <c r="F286" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="15.75">
+      <c r="A287" s="19" t="s">
+        <v>703</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C287" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D287" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="E287" s="23">
+        <v>37</v>
+      </c>
+      <c r="F287" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="15.75">
+      <c r="A288" s="19" t="s">
+        <v>704</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C288" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D288" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="E288" s="23">
+        <v>37</v>
+      </c>
+      <c r="F288" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="15.75">
+      <c r="A289" s="18" t="s">
+        <v>705</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C289" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D289" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="E289" s="23">
+        <v>45</v>
+      </c>
+      <c r="F289" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="15.75">
+      <c r="A290" s="18" t="s">
+        <v>706</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C290" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D290" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="E290" s="23">
+        <v>45</v>
+      </c>
+      <c r="F290" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="15.75">
+      <c r="A291" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C291" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D291" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="E291" s="23">
+        <v>4</v>
+      </c>
+      <c r="F291" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="15.75">
+      <c r="A292" s="18" t="s">
+        <v>708</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C292" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D292" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="E292" s="23">
+        <v>4</v>
+      </c>
+      <c r="F292" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="15.75">
+      <c r="A293" s="18" t="s">
+        <v>709</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C293" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D293" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="E293" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="F293" s="23" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="15.75">
+      <c r="A294" s="18" t="s">
+        <v>710</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C294" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D294" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="E294" s="23">
+        <v>18.5</v>
+      </c>
+      <c r="F294" s="23" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="15.75">
+      <c r="A295" s="18" t="s">
+        <v>711</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C295" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D295" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="E295" s="23">
+        <v>55</v>
+      </c>
+      <c r="F295" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="15.75">
+      <c r="A296" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C296" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D296" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="E296" s="23">
+        <v>55</v>
+      </c>
+      <c r="F296" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="15.75">
+      <c r="A297" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C297" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D297" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="E297" s="23">
+        <v>55</v>
+      </c>
+      <c r="F297" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="15.75">
+      <c r="A298" s="18" t="s">
+        <v>714</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C298" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D298" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="E298" s="23">
+        <v>55</v>
+      </c>
+      <c r="F298" s="23" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="15.75">
+      <c r="A299" s="19" t="s">
+        <v>715</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C299" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D299" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="E299" s="23">
+        <v>132</v>
+      </c>
+      <c r="F299" s="23" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="15.75">
+      <c r="A300" s="18" t="s">
+        <v>716</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C300" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D300" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E300" s="23">
+        <v>30</v>
+      </c>
+      <c r="F300" s="23" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="15.75">
+      <c r="A301" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C301" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D301" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="E301" s="23">
+        <v>30</v>
+      </c>
+      <c r="F301" s="23" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="15.75">
+      <c r="A302" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C302" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D302" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="E302" s="23">
+        <v>55</v>
+      </c>
+      <c r="F302" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="15.75">
+      <c r="A303" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C303" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D303" s="17" t="s">
+        <v>839</v>
+      </c>
+      <c r="E303" s="23">
+        <v>55</v>
+      </c>
+      <c r="F303" s="23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="15.75">
+      <c r="A304" s="19" t="s">
+        <v>720</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C304" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D304" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="E304" s="23">
+        <v>37</v>
+      </c>
+      <c r="F304" s="23" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="15.75">
+      <c r="A305" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C305" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D305" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="E305" s="23">
+        <v>30</v>
+      </c>
+      <c r="F305" s="23" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="15.75">
+      <c r="A306" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C306" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D306" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="E306" s="23">
+        <v>30</v>
+      </c>
+      <c r="F306" s="23" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="15.75">
+      <c r="A307" s="18" t="s">
+        <v>723</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C307" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D307" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="E307" s="23">
+        <v>11</v>
+      </c>
+      <c r="F307" s="23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="15.75">
+      <c r="A308" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C308" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D308" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="E308" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F308" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="15.75">
+      <c r="A309" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C309" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D309" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="E309" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F309" s="23" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="15.75">
+      <c r="A310" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C310" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D310" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="E310" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="F310" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="15.75">
+      <c r="A311" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C311" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D311" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="E311" s="23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F311" s="23" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="15.75">
+      <c r="A312" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C312" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D312" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="E312" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F312" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="15.75">
+      <c r="A313" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C313" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D313" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="E313" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F313" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="15.75">
+      <c r="A314" s="19" t="s">
+        <v>730</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C314" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D314" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="E314" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F314" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="15.75">
+      <c r="A315" s="19" t="s">
+        <v>731</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C315" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D315" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="E315" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F315" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="15.75">
+      <c r="A316" s="18" t="s">
+        <v>732</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C316" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D316" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="E316" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F316" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="15.75">
+      <c r="A317" s="20" t="s">
+        <v>733</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C317" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D317" s="17" t="s">
+        <v>846</v>
+      </c>
+      <c r="E317" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F317" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="15.75">
+      <c r="A318" s="19" t="s">
+        <v>734</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C318" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D318" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="E318" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F318" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="15.75">
+      <c r="A319" s="19" t="s">
+        <v>735</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C319" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D319" s="17" t="s">
+        <v>847</v>
+      </c>
+      <c r="E319" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F319" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="15.75">
+      <c r="A320" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C320" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="D320" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="E320" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F320" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="15.75">
+      <c r="A321" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C321" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D321" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="E321" s="23">
+        <v>11</v>
+      </c>
+      <c r="F321" s="23" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="15.75">
+      <c r="A322" s="18" t="s">
+        <v>738</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C322" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D322" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="E322" s="23">
+        <v>11</v>
+      </c>
+      <c r="F322" s="23" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="15.75">
+      <c r="A323" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C323" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D323" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E323" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F323" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="15.75">
+      <c r="A324" s="18" t="s">
+        <v>740</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C324" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D324" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="E324" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F324" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="15.75">
+      <c r="A325" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C325" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="D325" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="E325" s="29">
+        <v>0.4</v>
+      </c>
+      <c r="F325" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="15.75">
+      <c r="A326" s="19" t="s">
+        <v>742</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C326" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D326" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="E326" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="F326" s="23" t="s">
+        <v>659</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01AB0F3-B3CD-44CE-8A0F-145E087AD062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCDB3AC-44CD-48E5-8631-E97B7399062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="1589">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -2769,13 +2769,2203 @@
   </si>
   <si>
     <t>LM-01B-3</t>
+  </si>
+  <si>
+    <t>MP-3105A</t>
+  </si>
+  <si>
+    <t>AT FEED PUMP</t>
+  </si>
+  <si>
+    <t>A30-PC-301-A</t>
+  </si>
+  <si>
+    <t>MP-3105B</t>
+  </si>
+  <si>
+    <t>A30-PC-301-B</t>
+  </si>
+  <si>
+    <t>MP-3105C</t>
+  </si>
+  <si>
+    <t>MP-3106</t>
+  </si>
+  <si>
+    <t>CATALYST TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3108A</t>
+  </si>
+  <si>
+    <t>CATALYST FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3108B</t>
+  </si>
+  <si>
+    <t>MP-3108C</t>
+  </si>
+  <si>
+    <t>MP-3108D</t>
+  </si>
+  <si>
+    <t>MP-3202A</t>
+  </si>
+  <si>
+    <t>1ST SLURRY TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3202B</t>
+  </si>
+  <si>
+    <t>MP-3205A</t>
+  </si>
+  <si>
+    <t>1ST CONDENSATE RECYCLE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3205B</t>
+  </si>
+  <si>
+    <t>MP-3206</t>
+  </si>
+  <si>
+    <t>1ST JACKET WATER RECYCLE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3207A</t>
+  </si>
+  <si>
+    <t>2ND CONDENSATE RECYCLE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3207B</t>
+  </si>
+  <si>
+    <t>MP-3208</t>
+  </si>
+  <si>
+    <t>2ND JACKET WATER RECYCLE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3209A</t>
+  </si>
+  <si>
+    <t>BUTENE FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3209B</t>
+  </si>
+  <si>
+    <t>MP-3213A</t>
+  </si>
+  <si>
+    <t>SLURRY COOLER JACKET PUMP</t>
+  </si>
+  <si>
+    <t>MP-3213B</t>
+  </si>
+  <si>
+    <t>MP-3214A</t>
+  </si>
+  <si>
+    <t>1ST REACTOR A SLURRY COOLER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3214B</t>
+  </si>
+  <si>
+    <t>1ST REACTOR B SLURRY COOLER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3215A</t>
+  </si>
+  <si>
+    <t>2ND REACTOR A SLURRY COOLER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3215B</t>
+  </si>
+  <si>
+    <t>2ND REACTOR B SLURRY COOLER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3223</t>
+  </si>
+  <si>
+    <t>AUXILIARY LUBE OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3303</t>
+  </si>
+  <si>
+    <t>MP-3306A</t>
+  </si>
+  <si>
+    <t>CENTRIFUGE TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3306B</t>
+  </si>
+  <si>
+    <t>MP-3317A</t>
+  </si>
+  <si>
+    <t>CENTRIFUGE - LO PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3317B</t>
+  </si>
+  <si>
+    <t>MP-3320A</t>
+  </si>
+  <si>
+    <t>DC HEXANE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3320B</t>
+  </si>
+  <si>
+    <t>MP-3321A</t>
+  </si>
+  <si>
+    <t>DC HEXANE TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3321B</t>
+  </si>
+  <si>
+    <t>MP-3401A</t>
+  </si>
+  <si>
+    <t>SCRUBBER BOTTOM RECYCLE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3401B</t>
+  </si>
+  <si>
+    <t>MP-3402A</t>
+  </si>
+  <si>
+    <t>PCW CIRCULATION PUMP</t>
+  </si>
+  <si>
+    <t>A30-PC-302-A</t>
+  </si>
+  <si>
+    <t>MP-3402B</t>
+  </si>
+  <si>
+    <t>A30-PC-302-B</t>
+  </si>
+  <si>
+    <t>MP-3405A</t>
+  </si>
+  <si>
+    <t>WSB FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3405B</t>
+  </si>
+  <si>
+    <t>MP-3406</t>
+  </si>
+  <si>
+    <t>HEXANE TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3407A</t>
+  </si>
+  <si>
+    <t>LUBE OIL PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3407B</t>
+  </si>
+  <si>
+    <t>MP-3410A</t>
+  </si>
+  <si>
+    <t>LUBE OIL RETURN PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3410B</t>
+  </si>
+  <si>
+    <t>MP-3411A</t>
+  </si>
+  <si>
+    <t>BCW PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3411B</t>
+  </si>
+  <si>
+    <t>MP-3412A</t>
+  </si>
+  <si>
+    <t>SCREEN CHANGER HYDRAULIC OIL PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3412B</t>
+  </si>
+  <si>
+    <t>HYDRAULIC OIL PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3413A</t>
+  </si>
+  <si>
+    <t>VARIATOR LUBE OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3413B</t>
+  </si>
+  <si>
+    <t>MP-3414A</t>
+  </si>
+  <si>
+    <t>MAIN LUBE OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3414B</t>
+  </si>
+  <si>
+    <t>MP-3420A</t>
+  </si>
+  <si>
+    <t>LUBE OIL PUMP MOTOR FOR MIXER MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3420B</t>
+  </si>
+  <si>
+    <t>MP-3449A</t>
+  </si>
+  <si>
+    <t>HOT OIL PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3449B</t>
+  </si>
+  <si>
+    <t>MP-3491A</t>
+  </si>
+  <si>
+    <t>PCW W.W PUMP</t>
+  </si>
+  <si>
+    <t>MP-3491B</t>
+  </si>
+  <si>
+    <t>MP-3701A</t>
+  </si>
+  <si>
+    <t>HEXANE STRIPPER FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3701B</t>
+  </si>
+  <si>
+    <t>MP-3702</t>
+  </si>
+  <si>
+    <t>WASHING WATER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3703A</t>
+  </si>
+  <si>
+    <t>HEXANE DEHYDRATOR FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3703B</t>
+  </si>
+  <si>
+    <t>MP-3704A</t>
+  </si>
+  <si>
+    <t>HEXANE DEHYDRATOR BOTTOM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3704B</t>
+  </si>
+  <si>
+    <t>MP-3706A</t>
+  </si>
+  <si>
+    <t>PURE HEXANE PUMP</t>
+  </si>
+  <si>
+    <t>A30-EP-301</t>
+  </si>
+  <si>
+    <t>MP-3706B</t>
+  </si>
+  <si>
+    <t>MP-3707A</t>
+  </si>
+  <si>
+    <t>STRIPPER BOTTOM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3707B</t>
+  </si>
+  <si>
+    <t>MP-3709</t>
+  </si>
+  <si>
+    <t>FOULD HEXANE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3710A</t>
+  </si>
+  <si>
+    <t>CRUDE HEXANE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3710B</t>
+  </si>
+  <si>
+    <t>MP-3711A</t>
+  </si>
+  <si>
+    <t>1ST FLASH FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3711B</t>
+  </si>
+  <si>
+    <t>MP-3712A</t>
+  </si>
+  <si>
+    <t>AUX. LUBE OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3712B</t>
+  </si>
+  <si>
+    <t>MP-3713A</t>
+  </si>
+  <si>
+    <t>LOW POLYMER TRANSFER PUMPS</t>
+  </si>
+  <si>
+    <t>A30-VSDS-305</t>
+  </si>
+  <si>
+    <t>MP-3713B</t>
+  </si>
+  <si>
+    <t>MP-3714A</t>
+  </si>
+  <si>
+    <t>RECOVERED HEXANE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3714B</t>
+  </si>
+  <si>
+    <t>MP-3716A</t>
+  </si>
+  <si>
+    <t>LP STORAGE BOTTOM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3716B</t>
+  </si>
+  <si>
+    <t>MP-3717</t>
+  </si>
+  <si>
+    <t>PCW RETURN PUMP</t>
+  </si>
+  <si>
+    <t>MP-3720A</t>
+  </si>
+  <si>
+    <t>VACUUM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3720B</t>
+  </si>
+  <si>
+    <t>MP-3721</t>
+  </si>
+  <si>
+    <t>OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3740</t>
+  </si>
+  <si>
+    <t>V-3740 BOTTOM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3741</t>
+  </si>
+  <si>
+    <t>HEAVY HEXANE PURIFICATION COLUMN BOTTOM PUMP</t>
+  </si>
+  <si>
+    <t>MP-3742</t>
+  </si>
+  <si>
+    <t>HEAVY HEXANE PURIFICATION COLUMN REFLUX PUMP</t>
+  </si>
+  <si>
+    <t>MP-3802</t>
+  </si>
+  <si>
+    <t>MP-3806A</t>
+  </si>
+  <si>
+    <t>CAUSTIC SODA FEED PUMP</t>
+  </si>
+  <si>
+    <t>MP-3806B</t>
+  </si>
+  <si>
+    <t>MP-3811A</t>
+  </si>
+  <si>
+    <t>HP SEAL OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3811B</t>
+  </si>
+  <si>
+    <t>MP-3812A</t>
+  </si>
+  <si>
+    <t>LP SEAL OIL PUMP</t>
+  </si>
+  <si>
+    <t>MP-3812B</t>
+  </si>
+  <si>
+    <t>MP-3813</t>
+  </si>
+  <si>
+    <t>SEAL OIL MAKE UP PUMP</t>
+  </si>
+  <si>
+    <t>MP-3820A</t>
+  </si>
+  <si>
+    <t>LO PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MP-3820B</t>
+  </si>
+  <si>
+    <t>MP-3821A</t>
+  </si>
+  <si>
+    <t>BRINE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3821B</t>
+  </si>
+  <si>
+    <t>MP-3823A</t>
+  </si>
+  <si>
+    <t>PONTENTIALLY CONTAMINATED WATER PIT PUMP</t>
+  </si>
+  <si>
+    <t>MP-3823B</t>
+  </si>
+  <si>
+    <t>MP-3851A</t>
+  </si>
+  <si>
+    <t>STEAM CONDENSATE TRANSFER PUMP</t>
+  </si>
+  <si>
+    <t>MP-3851B</t>
+  </si>
+  <si>
+    <t>MP-3852A</t>
+  </si>
+  <si>
+    <t>STEAM CONDENSATE PUMP FOR  TRAIN # 1</t>
+  </si>
+  <si>
+    <t>MP-3852B</t>
+  </si>
+  <si>
+    <t>MP-3881</t>
+  </si>
+  <si>
+    <t>FLARE CONDENSATE PUMP</t>
+  </si>
+  <si>
+    <t>MP-3883</t>
+  </si>
+  <si>
+    <t>MP-4105A</t>
+  </si>
+  <si>
+    <t>A30-PC-303-A</t>
+  </si>
+  <si>
+    <t>MP-4105B</t>
+  </si>
+  <si>
+    <t>A30-PC-303-B</t>
+  </si>
+  <si>
+    <t>MP-4105C</t>
+  </si>
+  <si>
+    <t>MP-4106</t>
+  </si>
+  <si>
+    <t>MP-4108A</t>
+  </si>
+  <si>
+    <t>MP-4108B</t>
+  </si>
+  <si>
+    <t>MP-4108C</t>
+  </si>
+  <si>
+    <t>MP-4108D</t>
+  </si>
+  <si>
+    <t>MP-4202A</t>
+  </si>
+  <si>
+    <t>MP-4202B</t>
+  </si>
+  <si>
+    <t>MP-4205A</t>
+  </si>
+  <si>
+    <t>MP-4205B</t>
+  </si>
+  <si>
+    <t>MP-4206</t>
+  </si>
+  <si>
+    <t>MP-4207A</t>
+  </si>
+  <si>
+    <t>MP-4207B</t>
+  </si>
+  <si>
+    <t>MP-4208</t>
+  </si>
+  <si>
+    <t>MP-4209A</t>
+  </si>
+  <si>
+    <t>MP-4209B</t>
+  </si>
+  <si>
+    <t>MP-4213A</t>
+  </si>
+  <si>
+    <t>MP-4213B</t>
+  </si>
+  <si>
+    <t>MP-4214A</t>
+  </si>
+  <si>
+    <t>MP-4214B</t>
+  </si>
+  <si>
+    <t>MP-4215A</t>
+  </si>
+  <si>
+    <t>MP-4215B</t>
+  </si>
+  <si>
+    <t>MP-4223</t>
+  </si>
+  <si>
+    <t>MP-4303</t>
+  </si>
+  <si>
+    <t>MP-4306A</t>
+  </si>
+  <si>
+    <t>MP-4306B</t>
+  </si>
+  <si>
+    <t>MP-4317A</t>
+  </si>
+  <si>
+    <t>MP-4317B</t>
+  </si>
+  <si>
+    <t>MP-4320A</t>
+  </si>
+  <si>
+    <t>MP-4320B</t>
+  </si>
+  <si>
+    <t>MP-4321A</t>
+  </si>
+  <si>
+    <t>MP-4321B</t>
+  </si>
+  <si>
+    <t>MP-4401A</t>
+  </si>
+  <si>
+    <t>MP-4401B</t>
+  </si>
+  <si>
+    <t>MP-4402A</t>
+  </si>
+  <si>
+    <t>A30-PC-304-B</t>
+  </si>
+  <si>
+    <t>MP-4402B</t>
+  </si>
+  <si>
+    <t>A30-PC-304-A</t>
+  </si>
+  <si>
+    <t>MP-4405A</t>
+  </si>
+  <si>
+    <t>MP-4405B</t>
+  </si>
+  <si>
+    <t>MP-4406</t>
+  </si>
+  <si>
+    <t>MP-4407A</t>
+  </si>
+  <si>
+    <t>MP-4407B</t>
+  </si>
+  <si>
+    <t>MP-4410A</t>
+  </si>
+  <si>
+    <t>MP-4410B</t>
+  </si>
+  <si>
+    <t>MP-4411A</t>
+  </si>
+  <si>
+    <t>MP-4411B</t>
+  </si>
+  <si>
+    <t>MP-4412A</t>
+  </si>
+  <si>
+    <t>MP-4412B</t>
+  </si>
+  <si>
+    <t>MP-4413A</t>
+  </si>
+  <si>
+    <t>MP-4413B</t>
+  </si>
+  <si>
+    <t>MP-4414A</t>
+  </si>
+  <si>
+    <t>MP-4414B</t>
+  </si>
+  <si>
+    <t>MP-4420A</t>
+  </si>
+  <si>
+    <t>MP-4420B</t>
+  </si>
+  <si>
+    <t>MP-4449A</t>
+  </si>
+  <si>
+    <t>MP-4449B</t>
+  </si>
+  <si>
+    <t>MP-4491A</t>
+  </si>
+  <si>
+    <t>MP-4491B</t>
+  </si>
+  <si>
+    <t>MP-4811A</t>
+  </si>
+  <si>
+    <t>MP-4811B</t>
+  </si>
+  <si>
+    <t>MP-4812A</t>
+  </si>
+  <si>
+    <t>MP-4812B</t>
+  </si>
+  <si>
+    <t>MP-4813</t>
+  </si>
+  <si>
+    <t>MP-4852A</t>
+  </si>
+  <si>
+    <t>STEAM CONDENSATE PUMP FOR  TRAIN # 2</t>
+  </si>
+  <si>
+    <t>MP-4852B</t>
+  </si>
+  <si>
+    <t>AR05-7</t>
+  </si>
+  <si>
+    <t>BR04-6</t>
+  </si>
+  <si>
+    <t>BR01-8</t>
+  </si>
+  <si>
+    <t>AR06-7</t>
+  </si>
+  <si>
+    <t>AR08-3</t>
+  </si>
+  <si>
+    <t>BR03-3</t>
+  </si>
+  <si>
+    <t>BR03-4</t>
+  </si>
+  <si>
+    <t>AR08-4</t>
+  </si>
+  <si>
+    <t>BR06-5</t>
+  </si>
+  <si>
+    <t>AF08-6</t>
+  </si>
+  <si>
+    <t>BR07-1</t>
+  </si>
+  <si>
+    <t>AF08-5</t>
+  </si>
+  <si>
+    <t>AF01-3</t>
+  </si>
+  <si>
+    <t>BR03-7</t>
+  </si>
+  <si>
+    <t>AF08-4</t>
+  </si>
+  <si>
+    <t>AF02-3</t>
+  </si>
+  <si>
+    <t>BF02-1</t>
+  </si>
+  <si>
+    <t>AF01-1</t>
+  </si>
+  <si>
+    <t>BF08-4</t>
+  </si>
+  <si>
+    <t>AF05-4</t>
+  </si>
+  <si>
+    <t>AF03-4</t>
+  </si>
+  <si>
+    <t>BF05-4</t>
+  </si>
+  <si>
+    <t>BF02-4</t>
+  </si>
+  <si>
+    <t>AF01-4</t>
+  </si>
+  <si>
+    <t>AR02-4</t>
+  </si>
+  <si>
+    <t>BR01-7</t>
+  </si>
+  <si>
+    <t>BF02-3</t>
+  </si>
+  <si>
+    <t>AF03-3</t>
+  </si>
+  <si>
+    <t>BR04-4</t>
+  </si>
+  <si>
+    <t>AR02-6</t>
+  </si>
+  <si>
+    <t>AF04-4</t>
+  </si>
+  <si>
+    <t>BF06-4</t>
+  </si>
+  <si>
+    <t>AF04-3</t>
+  </si>
+  <si>
+    <t>BF06-3</t>
+  </si>
+  <si>
+    <t>AF01-2</t>
+  </si>
+  <si>
+    <t>BF02-2</t>
+  </si>
+  <si>
+    <t>BF05-2</t>
+  </si>
+  <si>
+    <t>AR06-4</t>
+  </si>
+  <si>
+    <t>BR04-5</t>
+  </si>
+  <si>
+    <t>BR01-6</t>
+  </si>
+  <si>
+    <t>AR06-3</t>
+  </si>
+  <si>
+    <t>BR07-6</t>
+  </si>
+  <si>
+    <t>BR05-3</t>
+  </si>
+  <si>
+    <t>AR04-3</t>
+  </si>
+  <si>
+    <t>AR07-1</t>
+  </si>
+  <si>
+    <t>BR07-5</t>
+  </si>
+  <si>
+    <t>AR07-2</t>
+  </si>
+  <si>
+    <t>BR03-5</t>
+  </si>
+  <si>
+    <t>AR06-8</t>
+  </si>
+  <si>
+    <t>AF04-1</t>
+  </si>
+  <si>
+    <t>BF06-1</t>
+  </si>
+  <si>
+    <t>AR03-2</t>
+  </si>
+  <si>
+    <t>BR06-4</t>
+  </si>
+  <si>
+    <t>AR07-3</t>
+  </si>
+  <si>
+    <t>AF03-2</t>
+  </si>
+  <si>
+    <t>AF03-5</t>
+  </si>
+  <si>
+    <t>BF03-3</t>
+  </si>
+  <si>
+    <t>AR04-5</t>
+  </si>
+  <si>
+    <t>AF07-5</t>
+  </si>
+  <si>
+    <t>AR03-6</t>
+  </si>
+  <si>
+    <t>AF02-4</t>
+  </si>
+  <si>
+    <t>BR02-3</t>
+  </si>
+  <si>
+    <t>AF02-2</t>
+  </si>
+  <si>
+    <t>AF02-5</t>
+  </si>
+  <si>
+    <t>AF06-3</t>
+  </si>
+  <si>
+    <t>BR02-4</t>
+  </si>
+  <si>
+    <t>AR02-2</t>
+  </si>
+  <si>
+    <t>AF05-3</t>
+  </si>
+  <si>
+    <t>AF07-2</t>
+  </si>
+  <si>
+    <t>BR07-4</t>
+  </si>
+  <si>
+    <t>BR02-5</t>
+  </si>
+  <si>
+    <t>AR02-5</t>
+  </si>
+  <si>
+    <t>BR01-5</t>
+  </si>
+  <si>
+    <t>AR03-3</t>
+  </si>
+  <si>
+    <t>BF08-8</t>
+  </si>
+  <si>
+    <t>AF08-7</t>
+  </si>
+  <si>
+    <t>AR04-4</t>
+  </si>
+  <si>
+    <t>AR03-4</t>
+  </si>
+  <si>
+    <t>AF05-2</t>
+  </si>
+  <si>
+    <t>BR05-5</t>
+  </si>
+  <si>
+    <t>BR03-6</t>
+  </si>
+  <si>
+    <t>AF07-3</t>
+  </si>
+  <si>
+    <t>BR06-2</t>
+  </si>
+  <si>
+    <t>BR04-1</t>
+  </si>
+  <si>
+    <t>AF02-1</t>
+  </si>
+  <si>
+    <t>BF03-1</t>
+  </si>
+  <si>
+    <t>AR01-5</t>
+  </si>
+  <si>
+    <t>AF05-5</t>
+  </si>
+  <si>
+    <t>BF05-1</t>
+  </si>
+  <si>
+    <t>BF04-3</t>
+  </si>
+  <si>
+    <t>BR07-3</t>
+  </si>
+  <si>
+    <t>AF06-2</t>
+  </si>
+  <si>
+    <t>BR04-7</t>
+  </si>
+  <si>
+    <t>BF01-2</t>
+  </si>
+  <si>
+    <t>AR05-8</t>
+  </si>
+  <si>
+    <t>BF03-4</t>
+  </si>
+  <si>
+    <t>BF01-4</t>
+  </si>
+  <si>
+    <t>BF07-5</t>
+  </si>
+  <si>
+    <t>AF04-5</t>
+  </si>
+  <si>
+    <t>BF04-6</t>
+  </si>
+  <si>
+    <t>AR07-4</t>
+  </si>
+  <si>
+    <t>BR05-7</t>
+  </si>
+  <si>
+    <t>BF03-2</t>
+  </si>
+  <si>
+    <t>BF02-5</t>
+  </si>
+  <si>
+    <t>AF01-5</t>
+  </si>
+  <si>
+    <t>BR05-6</t>
+  </si>
+  <si>
+    <t>AR05-6</t>
+  </si>
+  <si>
+    <t>AR03-5</t>
+  </si>
+  <si>
+    <t>BR03-2</t>
+  </si>
+  <si>
+    <t>BR02-6</t>
+  </si>
+  <si>
+    <t>AR01-2</t>
+  </si>
+  <si>
+    <t>AR04-6</t>
+  </si>
+  <si>
+    <t>BF06-2</t>
+  </si>
+  <si>
+    <t>MOP-3105A</t>
+  </si>
+  <si>
+    <t>AT FEED PUMP STROKE ACTUATOR</t>
+  </si>
+  <si>
+    <t>MOP-3105B</t>
+  </si>
+  <si>
+    <t>MOP-3105C</t>
+  </si>
+  <si>
+    <t>MOP-3106</t>
+  </si>
+  <si>
+    <t>CATALYST TRANSFER PUMP STROKE ACTUATOR</t>
+  </si>
+  <si>
+    <t>MOP-3108A</t>
+  </si>
+  <si>
+    <t>CATALYST FEED PUMP STROKE ACTUATOR</t>
+  </si>
+  <si>
+    <t>MOP-3108B</t>
+  </si>
+  <si>
+    <t>MOP-3108C</t>
+  </si>
+  <si>
+    <t>MOP-3108D</t>
+  </si>
+  <si>
+    <t>MOP-3405A</t>
+  </si>
+  <si>
+    <t>WSB FEED PUMP STROKE ACTUATOR</t>
+  </si>
+  <si>
+    <t>MOP-3405B</t>
+  </si>
+  <si>
+    <t>MOP-3806A</t>
+  </si>
+  <si>
+    <t>CAUSTIC SODA FEED PUMP STROKE ACTUATOR</t>
+  </si>
+  <si>
+    <t>MOP-3806B</t>
+  </si>
+  <si>
+    <t>MOP-4105A</t>
+  </si>
+  <si>
+    <t>MOP-4105B</t>
+  </si>
+  <si>
+    <t>MOP-4105C</t>
+  </si>
+  <si>
+    <t>MOP-4106</t>
+  </si>
+  <si>
+    <t>MOP-4108A</t>
+  </si>
+  <si>
+    <t>MOP-4108B</t>
+  </si>
+  <si>
+    <t>MOP-4108C</t>
+  </si>
+  <si>
+    <t>MOP-4108D</t>
+  </si>
+  <si>
+    <t>MOP-4405A</t>
+  </si>
+  <si>
+    <t>MOP-4405B</t>
+  </si>
+  <si>
+    <t>BR06-3</t>
+  </si>
+  <si>
+    <t>BR05-4</t>
+  </si>
+  <si>
+    <t>AR05-3</t>
+  </si>
+  <si>
+    <t>BR04-2</t>
+  </si>
+  <si>
+    <t>AR05-4</t>
+  </si>
+  <si>
+    <t>AF06-5</t>
+  </si>
+  <si>
+    <t>BR04-3</t>
+  </si>
+  <si>
+    <t>BR01-4</t>
+  </si>
+  <si>
+    <t>BR05-2</t>
+  </si>
+  <si>
+    <t>BR01-3</t>
+  </si>
+  <si>
+    <t>AR05-5</t>
+  </si>
+  <si>
+    <t>BR02-2</t>
+  </si>
+  <si>
+    <t>AR04-2</t>
+  </si>
+  <si>
+    <t>AR08-6</t>
+  </si>
+  <si>
+    <t>MK-3201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1ST RECYCLE GAS BLOWER </t>
+  </si>
+  <si>
+    <t>A30-MS-201-6A</t>
+  </si>
+  <si>
+    <t>MK-3202</t>
+  </si>
+  <si>
+    <t>2ND RECYCLE GAS BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-7A</t>
+  </si>
+  <si>
+    <t>MK-3222</t>
+  </si>
+  <si>
+    <t>FLASH GAS COMPRESSOR</t>
+  </si>
+  <si>
+    <t>MK-3302</t>
+  </si>
+  <si>
+    <t>OFF GAS COMPRESSOR</t>
+  </si>
+  <si>
+    <t>MK-3401A</t>
+  </si>
+  <si>
+    <t>DRYER GAS BLOWER</t>
+  </si>
+  <si>
+    <t>MK-3401B</t>
+  </si>
+  <si>
+    <t>MK-3402A</t>
+  </si>
+  <si>
+    <t>POWDER TRANSFER BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-11A</t>
+  </si>
+  <si>
+    <t>MK-3402A-1</t>
+  </si>
+  <si>
+    <t>BLOWER ACOUSTIC FAN</t>
+  </si>
+  <si>
+    <t>MK-3402A-2</t>
+  </si>
+  <si>
+    <t>MK-3402B</t>
+  </si>
+  <si>
+    <t>A30-MS-201-13A</t>
+  </si>
+  <si>
+    <t>MK-3402B-1</t>
+  </si>
+  <si>
+    <t>MK-3402B-2</t>
+  </si>
+  <si>
+    <t>MK-3403A</t>
+  </si>
+  <si>
+    <t>PELLET TRANSFER BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-12A</t>
+  </si>
+  <si>
+    <t>MK-3403A-1</t>
+  </si>
+  <si>
+    <t>MK-3403B</t>
+  </si>
+  <si>
+    <t>A30-MS-201-14A</t>
+  </si>
+  <si>
+    <t>MK-3403B-1</t>
+  </si>
+  <si>
+    <t>MK-3406</t>
+  </si>
+  <si>
+    <t>PELLET BLENDING BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-15A</t>
+  </si>
+  <si>
+    <t>MK-3406-1</t>
+  </si>
+  <si>
+    <t>MK-3407</t>
+  </si>
+  <si>
+    <t>BLENDED PELLET TRANSFER BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-16A</t>
+  </si>
+  <si>
+    <t>MK-3407-1</t>
+  </si>
+  <si>
+    <t>MK-3408</t>
+  </si>
+  <si>
+    <t>WET AIR EXHAUST FAN</t>
+  </si>
+  <si>
+    <t>MK-3409</t>
+  </si>
+  <si>
+    <t>PELLET COMMON BLOWER</t>
+  </si>
+  <si>
+    <t>A30-MS-201-17A</t>
+  </si>
+  <si>
+    <t>MK-3409-1</t>
+  </si>
+  <si>
+    <t>MK-3420-4</t>
+  </si>
+  <si>
+    <t>EXTERNAL FAN MOTOR FOR GEAR PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>VSDS-MEX-3420-4</t>
+  </si>
+  <si>
+    <t>MK-3451</t>
+  </si>
+  <si>
+    <t>MOTOR FAN</t>
+  </si>
+  <si>
+    <t>MK-3457</t>
+  </si>
+  <si>
+    <t>ELUTRIATOR FAN</t>
+  </si>
+  <si>
+    <t>MK-3720A</t>
+  </si>
+  <si>
+    <t>VENT GAS BLOWER</t>
+  </si>
+  <si>
+    <t>MK-3720B</t>
+  </si>
+  <si>
+    <t>MK-3801</t>
+  </si>
+  <si>
+    <t>REACTIVATION GAS BLOWER</t>
+  </si>
+  <si>
+    <t>MK-3821</t>
+  </si>
+  <si>
+    <t>MAIN MOTOR - REFRIGERATOR PACKAGE</t>
+  </si>
+  <si>
+    <t>A30-MS-201-8A</t>
+  </si>
+  <si>
+    <t>MK-3881</t>
+  </si>
+  <si>
+    <t>FLARE GAS COMPRESSOR</t>
+  </si>
+  <si>
+    <t>MK-4201</t>
+  </si>
+  <si>
+    <t>A30-MS-201-6B</t>
+  </si>
+  <si>
+    <t>MK-4202</t>
+  </si>
+  <si>
+    <t>A30-MS-201-7B</t>
+  </si>
+  <si>
+    <t>MK-4222</t>
+  </si>
+  <si>
+    <t>MK-4302</t>
+  </si>
+  <si>
+    <t>MK-4401A</t>
+  </si>
+  <si>
+    <t>MK-4401B</t>
+  </si>
+  <si>
+    <t>MK-4402A</t>
+  </si>
+  <si>
+    <t>A30-MS-201-12B</t>
+  </si>
+  <si>
+    <t>MK-4402A-1</t>
+  </si>
+  <si>
+    <t>MK-4402A-2</t>
+  </si>
+  <si>
+    <t>MK-4402B</t>
+  </si>
+  <si>
+    <t>A30-MS-201-10B</t>
+  </si>
+  <si>
+    <t>MK-4402B-1</t>
+  </si>
+  <si>
+    <t>MK-4402B-2</t>
+  </si>
+  <si>
+    <t>MK-4403A</t>
+  </si>
+  <si>
+    <t>A30-MS-201-13B</t>
+  </si>
+  <si>
+    <t>MK-4403A-1</t>
+  </si>
+  <si>
+    <t>MK-4403B</t>
+  </si>
+  <si>
+    <t>A30-MS-201-11B</t>
+  </si>
+  <si>
+    <t>MK-4403B-1</t>
+  </si>
+  <si>
+    <t>MK-4406</t>
+  </si>
+  <si>
+    <t>A30-MS-201-14B</t>
+  </si>
+  <si>
+    <t>MK-4406-1</t>
+  </si>
+  <si>
+    <t>MK-4407</t>
+  </si>
+  <si>
+    <t>A30-MS-201-15B</t>
+  </si>
+  <si>
+    <t>MK-4407-1</t>
+  </si>
+  <si>
+    <t>MK-4408</t>
+  </si>
+  <si>
+    <t>MK-4409</t>
+  </si>
+  <si>
+    <t>A30-MS-201-16B</t>
+  </si>
+  <si>
+    <t>MK-4409-1</t>
+  </si>
+  <si>
+    <t>MK-4420-4</t>
+  </si>
+  <si>
+    <t>VSDS-MEX-4420-4</t>
+  </si>
+  <si>
+    <t>MK-4451</t>
+  </si>
+  <si>
+    <t>MK-4457</t>
+  </si>
+  <si>
+    <t>BR06-6</t>
+  </si>
+  <si>
+    <t>BF08-2</t>
+  </si>
+  <si>
+    <t>AF08-3</t>
+  </si>
+  <si>
+    <t>AF06-7</t>
+  </si>
+  <si>
+    <t>BF08-1</t>
+  </si>
+  <si>
+    <t>AF06-6</t>
+  </si>
+  <si>
+    <t>BR08-4</t>
+  </si>
+  <si>
+    <t>AF05-1</t>
+  </si>
+  <si>
+    <t>BR08-3</t>
+  </si>
+  <si>
+    <t>AR01-4</t>
+  </si>
+  <si>
+    <t>AF07-4</t>
+  </si>
+  <si>
+    <t>BF01-3</t>
+  </si>
+  <si>
+    <t>BF07-3</t>
+  </si>
+  <si>
+    <t>BF04-5</t>
+  </si>
+  <si>
+    <t>BR07-2</t>
+  </si>
+  <si>
+    <t>AF05-6</t>
+  </si>
+  <si>
+    <t>BR08-6</t>
+  </si>
+  <si>
+    <t>AR08-11</t>
+  </si>
+  <si>
+    <t>MAG-3104</t>
+  </si>
+  <si>
+    <t>AT PREPERATION DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3106A</t>
+  </si>
+  <si>
+    <t>CATALYST PREPARATION DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>A30-VSDS-301</t>
+  </si>
+  <si>
+    <t>MAG-3106B</t>
+  </si>
+  <si>
+    <t>A30-VSDS-302</t>
+  </si>
+  <si>
+    <t>MAG-3107</t>
+  </si>
+  <si>
+    <t>MAG-3109</t>
+  </si>
+  <si>
+    <t>CATALYST CHARGE DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3201</t>
+  </si>
+  <si>
+    <t>1ST POLYMERIZER AGITATOR</t>
+  </si>
+  <si>
+    <t>A30-MS-201-9A</t>
+  </si>
+  <si>
+    <t>MAG-3202</t>
+  </si>
+  <si>
+    <t>1ST SLURRY DILUTION DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3204</t>
+  </si>
+  <si>
+    <t>1ST FLASH DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3205</t>
+  </si>
+  <si>
+    <t>2ND POLYMERIZER AGITATOR</t>
+  </si>
+  <si>
+    <t>A30-MS-201-10A</t>
+  </si>
+  <si>
+    <t>MAG-3206</t>
+  </si>
+  <si>
+    <t>2ND SLURRY DILUTION DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3306</t>
+  </si>
+  <si>
+    <t>2ND FLASH DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3310</t>
+  </si>
+  <si>
+    <t>MOTHER LIQUOR DRUM AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3416</t>
+  </si>
+  <si>
+    <t>STABILIZER HOPPER AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3426</t>
+  </si>
+  <si>
+    <t>STABILIZER MIXER AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-3701A</t>
+  </si>
+  <si>
+    <t>CRUDE HEXANE TANK MIXER</t>
+  </si>
+  <si>
+    <t>MAG-3701B</t>
+  </si>
+  <si>
+    <t>MAG-3802</t>
+  </si>
+  <si>
+    <t>HEXANE STRIPPER AGITATOR</t>
+  </si>
+  <si>
+    <t>MAG-4104</t>
+  </si>
+  <si>
+    <t>MAG-4106A</t>
+  </si>
+  <si>
+    <t>A30-VSDS-303</t>
+  </si>
+  <si>
+    <t>MAG-4106B</t>
+  </si>
+  <si>
+    <t>A30-VSDS-304</t>
+  </si>
+  <si>
+    <t>MAG-4107</t>
+  </si>
+  <si>
+    <t>MAG-4109</t>
+  </si>
+  <si>
+    <t>MAG-4201</t>
+  </si>
+  <si>
+    <t>A30-MS-201-8B</t>
+  </si>
+  <si>
+    <t>MAG-4202</t>
+  </si>
+  <si>
+    <t>MAG-4204</t>
+  </si>
+  <si>
+    <t>MAG-4205</t>
+  </si>
+  <si>
+    <t>A30-MS-201-9B</t>
+  </si>
+  <si>
+    <t>MAG-4206</t>
+  </si>
+  <si>
+    <t>MAG-4306</t>
+  </si>
+  <si>
+    <t>MAG-4310</t>
+  </si>
+  <si>
+    <t>MAG-4416</t>
+  </si>
+  <si>
+    <t>MAG-4426</t>
+  </si>
+  <si>
+    <t>AF03-1</t>
+  </si>
+  <si>
+    <t>BF08-3</t>
+  </si>
+  <si>
+    <t>BR02-7</t>
+  </si>
+  <si>
+    <t>AR09-7</t>
+  </si>
+  <si>
+    <t>AF04-2</t>
+  </si>
+  <si>
+    <t>AF06-4</t>
+  </si>
+  <si>
+    <t>AF05-7</t>
+  </si>
+  <si>
+    <t>BF05-3</t>
+  </si>
+  <si>
+    <t>BF04-4</t>
+  </si>
+  <si>
+    <t>BF07-2</t>
+  </si>
+  <si>
+    <t>MEX-3420</t>
+  </si>
+  <si>
+    <t>EXTRUDER - MAIN MOTOR TRAIN-1</t>
+  </si>
+  <si>
+    <t>A30-MS-101</t>
+  </si>
+  <si>
+    <t>MEX-3420-1</t>
+  </si>
+  <si>
+    <t>BARRING MOTOR</t>
+  </si>
+  <si>
+    <t>MEX-3420-4</t>
+  </si>
+  <si>
+    <t>GEAR PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MEX-3420-6</t>
+  </si>
+  <si>
+    <t>PELLETIZER MOTOR</t>
+  </si>
+  <si>
+    <t>VSDS-MEX-3420-6</t>
+  </si>
+  <si>
+    <t>MEX-4420</t>
+  </si>
+  <si>
+    <t>EXTRUDER - MAIN MOTOR TRAIN -2</t>
+  </si>
+  <si>
+    <t>A30-MS-102</t>
+  </si>
+  <si>
+    <t>MEX-4420-1</t>
+  </si>
+  <si>
+    <t>MEX-4420-4</t>
+  </si>
+  <si>
+    <t>MEX-4420-6</t>
+  </si>
+  <si>
+    <t>VSDS-MEX-4420-6</t>
+  </si>
+  <si>
+    <t>MM-3303</t>
+  </si>
+  <si>
+    <t>CENTRIFUGE - MAIN MOTOR</t>
+  </si>
+  <si>
+    <t>A30-MS-201-18A</t>
+  </si>
+  <si>
+    <t>MM-3313</t>
+  </si>
+  <si>
+    <t>WET CAKE FEEDER</t>
+  </si>
+  <si>
+    <t>MM-3401</t>
+  </si>
+  <si>
+    <t>DRYER</t>
+  </si>
+  <si>
+    <t>VSDS-MM-3401</t>
+  </si>
+  <si>
+    <t>MM-3404</t>
+  </si>
+  <si>
+    <t>PELLET DRYER</t>
+  </si>
+  <si>
+    <t>MM-3414</t>
+  </si>
+  <si>
+    <t>SCREW FEEDER</t>
+  </si>
+  <si>
+    <t>MM-3424</t>
+  </si>
+  <si>
+    <t>MM-3434</t>
+  </si>
+  <si>
+    <t>PELLET VIBRATING CLASSIFIER</t>
+  </si>
+  <si>
+    <t>MM-4303</t>
+  </si>
+  <si>
+    <t>CENTRIFUGE MAIN MOTOR</t>
+  </si>
+  <si>
+    <t>A30-MS-201-17B</t>
+  </si>
+  <si>
+    <t>MM-4313</t>
+  </si>
+  <si>
+    <t>MM-4401</t>
+  </si>
+  <si>
+    <t>VSDS-MM-4401</t>
+  </si>
+  <si>
+    <t>MM-4404</t>
+  </si>
+  <si>
+    <t>MM-4414</t>
+  </si>
+  <si>
+    <t>MM-4419-02</t>
+  </si>
+  <si>
+    <t>POWDER VIBRATING SCREEN</t>
+  </si>
+  <si>
+    <t>MM-4424</t>
+  </si>
+  <si>
+    <t>MM-4434</t>
+  </si>
+  <si>
+    <t>AR06-2</t>
+  </si>
+  <si>
+    <t>AR01-6</t>
+  </si>
+  <si>
+    <t>BR08-2</t>
+  </si>
+  <si>
+    <t>BR03-1</t>
+  </si>
+  <si>
+    <t>MME-3427</t>
+  </si>
+  <si>
+    <t>STB DUST COLLECTOR</t>
+  </si>
+  <si>
+    <t>MME-3704</t>
+  </si>
+  <si>
+    <t>NaOH CONTACTOR</t>
+  </si>
+  <si>
+    <t>MME-3705</t>
+  </si>
+  <si>
+    <t>HEXANE &amp; WATER CONTACTOR</t>
+  </si>
+  <si>
+    <t>MME-3710A</t>
+  </si>
+  <si>
+    <t>LMP FLAKER</t>
+  </si>
+  <si>
+    <t>MME-3710B</t>
+  </si>
+  <si>
+    <t>MME-3711A</t>
+  </si>
+  <si>
+    <t>FLAKE CRUSHER (PINE CRUSHER)</t>
+  </si>
+  <si>
+    <t>MME-3711B</t>
+  </si>
+  <si>
+    <t>MME-3717A</t>
+  </si>
+  <si>
+    <t>SEWING MACHINE WITH CONVEYOR</t>
+  </si>
+  <si>
+    <t>MME-3717B</t>
+  </si>
+  <si>
+    <t>MME-4419</t>
+  </si>
+  <si>
+    <t>MME-4427</t>
+  </si>
+  <si>
+    <t>MW-3411</t>
+  </si>
+  <si>
+    <t>STABILIZER MEASURING FEEDER</t>
+  </si>
+  <si>
+    <t>MW-3411-01</t>
+  </si>
+  <si>
+    <t>FEEDING ELEMENT MOTOR</t>
+  </si>
+  <si>
+    <t>MW-4411</t>
+  </si>
+  <si>
+    <t>MW-4411-01</t>
+  </si>
+  <si>
+    <t>MX-3420A</t>
+  </si>
+  <si>
+    <t>MIXTURE MOTOR JACKUP PUMP MOTOR</t>
+  </si>
+  <si>
+    <t>MX-3420B</t>
+  </si>
+  <si>
+    <t>MX-3711A-01A</t>
+  </si>
+  <si>
+    <t>CONVEYOR BELT</t>
+  </si>
+  <si>
+    <t>MX-3711A-01B</t>
+  </si>
+  <si>
+    <t>MX-3711A-02A</t>
+  </si>
+  <si>
+    <t>DE DUSTING SYSTEM</t>
+  </si>
+  <si>
+    <t>MX-3711A-02B</t>
+  </si>
+  <si>
+    <t>MX-3720-01A</t>
+  </si>
+  <si>
+    <t>COMBUSTION AIR FAN - INCINERATOR</t>
+  </si>
+  <si>
+    <t>VSDS-MX-3720-01A</t>
+  </si>
+  <si>
+    <t>MX-4420A</t>
+  </si>
+  <si>
+    <t>MX-4420B</t>
+  </si>
+  <si>
+    <t>MZ-4480</t>
+  </si>
+  <si>
+    <t>ELEVATOR</t>
+  </si>
+  <si>
+    <t>AR06-6</t>
+  </si>
+  <si>
+    <t>AR02-1</t>
+  </si>
+  <si>
+    <t>AR03-1</t>
+  </si>
+  <si>
+    <t>AR01-3</t>
+  </si>
+  <si>
+    <t>MRF-3401</t>
+  </si>
+  <si>
+    <t>POWDER ROTARY VALVE(M-3401)</t>
+  </si>
+  <si>
+    <t>MRF-3403</t>
+  </si>
+  <si>
+    <t>POWDER ROTARY VALVE</t>
+  </si>
+  <si>
+    <t>MRF-3437</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3409)</t>
+  </si>
+  <si>
+    <t>MRF-3451</t>
+  </si>
+  <si>
+    <t>ROTARY VALVE (RF-3451)</t>
+  </si>
+  <si>
+    <t>MRF-3451A</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3451A)</t>
+  </si>
+  <si>
+    <t>MRF-3451B</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3451B)</t>
+  </si>
+  <si>
+    <t>MRF-3451C</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3451C)</t>
+  </si>
+  <si>
+    <t>MRF-3451D</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3451D)</t>
+  </si>
+  <si>
+    <t>MRF-3451E</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3451E)</t>
+  </si>
+  <si>
+    <t>MRF-3451SA</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3452A)</t>
+  </si>
+  <si>
+    <t>MRF-3451SB</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3452B)</t>
+  </si>
+  <si>
+    <t>MRF-3455</t>
+  </si>
+  <si>
+    <t>ROTARY VALVE (RF-3455)</t>
+  </si>
+  <si>
+    <t>MRF-3465</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-3453)</t>
+  </si>
+  <si>
+    <t>MRF-4401</t>
+  </si>
+  <si>
+    <t>POWDER ROTARY VALVE(M-4401)</t>
+  </si>
+  <si>
+    <t>MRF-4403</t>
+  </si>
+  <si>
+    <t>MRF-4419</t>
+  </si>
+  <si>
+    <t>ROTARY FEEDER</t>
+  </si>
+  <si>
+    <t>MRF-4437</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4409)</t>
+  </si>
+  <si>
+    <t>MRF-4451</t>
+  </si>
+  <si>
+    <t>ROTARY VALVE (RF-4451)</t>
+  </si>
+  <si>
+    <t>MRF-4451A</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4451A)</t>
+  </si>
+  <si>
+    <t>MRF-4451B</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4451B)</t>
+  </si>
+  <si>
+    <t>MRF-4451C</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4451C)</t>
+  </si>
+  <si>
+    <t>MRF-4451D</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4451D)</t>
+  </si>
+  <si>
+    <t>MRF-4451E</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4451E)</t>
+  </si>
+  <si>
+    <t>MRF-4451SA</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4452A)</t>
+  </si>
+  <si>
+    <t>MRF-4451SB</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4452B)</t>
+  </si>
+  <si>
+    <t>MRF-4455</t>
+  </si>
+  <si>
+    <t>ROTARY VALVE (RF-4455)</t>
+  </si>
+  <si>
+    <t>MRF-4465</t>
+  </si>
+  <si>
+    <t>PELLET ROTARY VALVE(Z-4453)</t>
+  </si>
+  <si>
+    <t>AR06-5</t>
+  </si>
+  <si>
+    <t>AR03-7</t>
+  </si>
+  <si>
+    <t>BF01-1</t>
+  </si>
+  <si>
+    <t>AF03-7</t>
+  </si>
+  <si>
+    <t>AF03-6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2868,8 +5058,23 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2885,6 +5090,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2959,7 +5170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3044,6 +5255,57 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3362,7 +5624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F687"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -9893,6 +12155,6070 @@
         <v>659</v>
       </c>
     </row>
+    <row r="327" spans="1:6" ht="18.75">
+      <c r="A327" s="30" t="s">
+        <v>859</v>
+      </c>
+      <c r="B327" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C327" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D327" s="34" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E327" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="18.75">
+      <c r="A328" s="30" t="s">
+        <v>862</v>
+      </c>
+      <c r="B328" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C328" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D328" s="34" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E328" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="18.75">
+      <c r="A329" s="30" t="s">
+        <v>864</v>
+      </c>
+      <c r="B329" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C329" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D329" s="34" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E329" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="18.75">
+      <c r="A330" s="30" t="s">
+        <v>865</v>
+      </c>
+      <c r="B330" s="31" t="s">
+        <v>866</v>
+      </c>
+      <c r="C330" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D330" s="34" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E330" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="18.75">
+      <c r="A331" s="30" t="s">
+        <v>867</v>
+      </c>
+      <c r="B331" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C331" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D331" s="34" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E331" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="18.75">
+      <c r="A332" s="30" t="s">
+        <v>869</v>
+      </c>
+      <c r="B332" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C332" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D332" s="34" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E332" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="18.75">
+      <c r="A333" s="30" t="s">
+        <v>870</v>
+      </c>
+      <c r="B333" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C333" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D333" s="34" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E333" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="18.75">
+      <c r="A334" s="30" t="s">
+        <v>871</v>
+      </c>
+      <c r="B334" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C334" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D334" s="34" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E334" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="18.75">
+      <c r="A335" s="30" t="s">
+        <v>872</v>
+      </c>
+      <c r="B335" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="C335" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D335" s="34" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E335" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="18.75">
+      <c r="A336" s="30" t="s">
+        <v>874</v>
+      </c>
+      <c r="B336" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="C336" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="D336" s="34" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E336" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="18.75">
+      <c r="A337" s="30" t="s">
+        <v>875</v>
+      </c>
+      <c r="B337" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="C337" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D337" s="34" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E337" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="18.75">
+      <c r="A338" s="30" t="s">
+        <v>877</v>
+      </c>
+      <c r="B338" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="C338" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D338" s="34" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E338" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="18.75">
+      <c r="A339" s="30" t="s">
+        <v>878</v>
+      </c>
+      <c r="B339" s="31" t="s">
+        <v>879</v>
+      </c>
+      <c r="C339" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D339" s="34" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E339" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" ht="18.75">
+      <c r="A340" s="30" t="s">
+        <v>880</v>
+      </c>
+      <c r="B340" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="C340" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D340" s="34" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E340" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" ht="18.75">
+      <c r="A341" s="30" t="s">
+        <v>882</v>
+      </c>
+      <c r="B341" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="C341" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D341" s="34" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E341" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" ht="18.75">
+      <c r="A342" s="30" t="s">
+        <v>883</v>
+      </c>
+      <c r="B342" s="31" t="s">
+        <v>884</v>
+      </c>
+      <c r="C342" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D342" s="34" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E342" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" ht="18.75">
+      <c r="A343" s="30" t="s">
+        <v>885</v>
+      </c>
+      <c r="B343" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="C343" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D343" s="34" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E343" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" ht="18.75">
+      <c r="A344" s="30" t="s">
+        <v>887</v>
+      </c>
+      <c r="B344" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="C344" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D344" s="34" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E344" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="18.75">
+      <c r="A345" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B345" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C345" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D345" s="34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E345" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="18.75">
+      <c r="A346" s="30" t="s">
+        <v>890</v>
+      </c>
+      <c r="B346" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C346" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D346" s="34" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E346" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="18.75">
+      <c r="A347" s="30" t="s">
+        <v>891</v>
+      </c>
+      <c r="B347" s="31" t="s">
+        <v>892</v>
+      </c>
+      <c r="C347" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="D347" s="34" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E347" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" ht="18.75">
+      <c r="A348" s="30" t="s">
+        <v>893</v>
+      </c>
+      <c r="B348" s="31" t="s">
+        <v>894</v>
+      </c>
+      <c r="C348" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D348" s="34" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E348" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="18.75">
+      <c r="A349" s="30" t="s">
+        <v>895</v>
+      </c>
+      <c r="B349" s="31" t="s">
+        <v>896</v>
+      </c>
+      <c r="C349" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D349" s="34" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E349" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="18.75">
+      <c r="A350" s="30" t="s">
+        <v>897</v>
+      </c>
+      <c r="B350" s="31" t="s">
+        <v>898</v>
+      </c>
+      <c r="C350" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="D350" s="34" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E350" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="18.75">
+      <c r="A351" s="30" t="s">
+        <v>899</v>
+      </c>
+      <c r="B351" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="C351" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D351" s="34" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E351" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="18.75">
+      <c r="A352" s="30" t="s">
+        <v>901</v>
+      </c>
+      <c r="B352" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="C352" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D352" s="34" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E352" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="18.75">
+      <c r="A353" s="30" t="s">
+        <v>902</v>
+      </c>
+      <c r="B353" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="C353" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D353" s="34" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E353" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="18.75">
+      <c r="A354" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="B354" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="C354" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D354" s="34" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E354" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="18.75">
+      <c r="A355" s="30" t="s">
+        <v>905</v>
+      </c>
+      <c r="B355" s="31" t="s">
+        <v>906</v>
+      </c>
+      <c r="C355" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D355" s="34" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E355" s="35">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="18.75">
+      <c r="A356" s="30" t="s">
+        <v>907</v>
+      </c>
+      <c r="B356" s="31" t="s">
+        <v>906</v>
+      </c>
+      <c r="C356" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D356" s="34" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E356" s="35">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="18.75">
+      <c r="A357" s="30" t="s">
+        <v>908</v>
+      </c>
+      <c r="B357" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="C357" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D357" s="34" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E357" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="18.75">
+      <c r="A358" s="30" t="s">
+        <v>910</v>
+      </c>
+      <c r="B358" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="C358" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D358" s="34" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E358" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="18.75">
+      <c r="A359" s="30" t="s">
+        <v>911</v>
+      </c>
+      <c r="B359" s="31" t="s">
+        <v>912</v>
+      </c>
+      <c r="C359" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D359" s="34" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E359" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="18.75">
+      <c r="A360" s="30" t="s">
+        <v>913</v>
+      </c>
+      <c r="B360" s="31" t="s">
+        <v>912</v>
+      </c>
+      <c r="C360" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D360" s="34" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E360" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="18.75">
+      <c r="A361" s="30" t="s">
+        <v>914</v>
+      </c>
+      <c r="B361" s="31" t="s">
+        <v>915</v>
+      </c>
+      <c r="C361" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D361" s="34" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E361" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="18.75">
+      <c r="A362" s="30" t="s">
+        <v>916</v>
+      </c>
+      <c r="B362" s="31" t="s">
+        <v>915</v>
+      </c>
+      <c r="C362" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D362" s="34" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E362" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="30" t="s">
+        <v>917</v>
+      </c>
+      <c r="B363" s="31" t="s">
+        <v>918</v>
+      </c>
+      <c r="C363" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D363" s="35" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E363" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="30" t="s">
+        <v>920</v>
+      </c>
+      <c r="B364" s="31" t="s">
+        <v>918</v>
+      </c>
+      <c r="C364" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D364" s="35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E364" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="18.75">
+      <c r="A365" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="B365" s="31" t="s">
+        <v>923</v>
+      </c>
+      <c r="C365" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D365" s="34" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E365" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" ht="18.75">
+      <c r="A366" s="30" t="s">
+        <v>924</v>
+      </c>
+      <c r="B366" s="31" t="s">
+        <v>923</v>
+      </c>
+      <c r="C366" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D366" s="34" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E366" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="18.75">
+      <c r="A367" s="30" t="s">
+        <v>925</v>
+      </c>
+      <c r="B367" s="31" t="s">
+        <v>926</v>
+      </c>
+      <c r="C367" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D367" s="34" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E367" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="B368" s="31" t="s">
+        <v>928</v>
+      </c>
+      <c r="C368" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D368" s="35" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E368" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="B369" s="31" t="s">
+        <v>928</v>
+      </c>
+      <c r="C369" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D369" s="35" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E369" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="B370" s="31" t="s">
+        <v>931</v>
+      </c>
+      <c r="C370" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D370" s="35" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E370" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="30" t="s">
+        <v>932</v>
+      </c>
+      <c r="B371" s="31" t="s">
+        <v>931</v>
+      </c>
+      <c r="C371" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D371" s="35" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E371" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="30" t="s">
+        <v>933</v>
+      </c>
+      <c r="B372" s="31" t="s">
+        <v>934</v>
+      </c>
+      <c r="C372" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D372" s="35" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E372" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="30" t="s">
+        <v>935</v>
+      </c>
+      <c r="B373" s="31" t="s">
+        <v>934</v>
+      </c>
+      <c r="C373" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D373" s="35" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E373" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="B374" s="31" t="s">
+        <v>937</v>
+      </c>
+      <c r="C374" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D374" s="35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E374" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="30" t="s">
+        <v>938</v>
+      </c>
+      <c r="B375" s="31" t="s">
+        <v>939</v>
+      </c>
+      <c r="C375" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D375" s="35" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E375" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="18.75">
+      <c r="A376" s="30" t="s">
+        <v>940</v>
+      </c>
+      <c r="B376" s="31" t="s">
+        <v>941</v>
+      </c>
+      <c r="C376" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D376" s="34" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E376" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="18.75">
+      <c r="A377" s="30" t="s">
+        <v>942</v>
+      </c>
+      <c r="B377" s="31" t="s">
+        <v>941</v>
+      </c>
+      <c r="C377" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="D377" s="34" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E377" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="18.75">
+      <c r="A378" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="B378" s="31" t="s">
+        <v>944</v>
+      </c>
+      <c r="C378" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="D378" s="34" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E378" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="18.75">
+      <c r="A379" s="30" t="s">
+        <v>945</v>
+      </c>
+      <c r="B379" s="31" t="s">
+        <v>944</v>
+      </c>
+      <c r="C379" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D379" s="34" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E379" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="30" t="s">
+        <v>946</v>
+      </c>
+      <c r="B380" s="31" t="s">
+        <v>947</v>
+      </c>
+      <c r="C380" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D380" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E380" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="30" t="s">
+        <v>948</v>
+      </c>
+      <c r="B381" s="31" t="s">
+        <v>947</v>
+      </c>
+      <c r="C381" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D381" s="35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E381" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="30" t="s">
+        <v>949</v>
+      </c>
+      <c r="B382" s="31" t="s">
+        <v>950</v>
+      </c>
+      <c r="C382" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D382" s="35" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E382" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="30" t="s">
+        <v>951</v>
+      </c>
+      <c r="B383" s="31" t="s">
+        <v>950</v>
+      </c>
+      <c r="C383" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D383" s="35" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E383" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" ht="18.75">
+      <c r="A384" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="B384" s="31" t="s">
+        <v>953</v>
+      </c>
+      <c r="C384" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D384" s="34" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E384" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="18.75">
+      <c r="A385" s="30" t="s">
+        <v>954</v>
+      </c>
+      <c r="B385" s="31" t="s">
+        <v>953</v>
+      </c>
+      <c r="C385" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D385" s="34" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E385" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="B386" s="31" t="s">
+        <v>956</v>
+      </c>
+      <c r="C386" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D386" s="35" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E386" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="30" t="s">
+        <v>957</v>
+      </c>
+      <c r="B387" s="31" t="s">
+        <v>956</v>
+      </c>
+      <c r="C387" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D387" s="35" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E387" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="30" t="s">
+        <v>958</v>
+      </c>
+      <c r="B388" s="31" t="s">
+        <v>959</v>
+      </c>
+      <c r="C388" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D388" s="35" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E388" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="30" t="s">
+        <v>960</v>
+      </c>
+      <c r="B389" s="31" t="s">
+        <v>961</v>
+      </c>
+      <c r="C389" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D389" s="35" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E389" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="30" t="s">
+        <v>962</v>
+      </c>
+      <c r="B390" s="31" t="s">
+        <v>961</v>
+      </c>
+      <c r="C390" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D390" s="35" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E390" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="30" t="s">
+        <v>963</v>
+      </c>
+      <c r="B391" s="31" t="s">
+        <v>964</v>
+      </c>
+      <c r="C391" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D391" s="35" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E391" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="30" t="s">
+        <v>965</v>
+      </c>
+      <c r="B392" s="31" t="s">
+        <v>964</v>
+      </c>
+      <c r="C392" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D392" s="35" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E392" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="30" t="s">
+        <v>966</v>
+      </c>
+      <c r="B393" s="31" t="s">
+        <v>967</v>
+      </c>
+      <c r="C393" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D393" s="35" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E393" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="30" t="s">
+        <v>969</v>
+      </c>
+      <c r="B394" s="31" t="s">
+        <v>967</v>
+      </c>
+      <c r="C394" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D394" s="35" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E394" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="B395" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="C395" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D395" s="35" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E395" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="30" t="s">
+        <v>972</v>
+      </c>
+      <c r="B396" s="31" t="s">
+        <v>971</v>
+      </c>
+      <c r="C396" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D396" s="35" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E396" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="30" t="s">
+        <v>973</v>
+      </c>
+      <c r="B397" s="31" t="s">
+        <v>974</v>
+      </c>
+      <c r="C397" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D397" s="35" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E397" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="30" t="s">
+        <v>975</v>
+      </c>
+      <c r="B398" s="31" t="s">
+        <v>976</v>
+      </c>
+      <c r="C398" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D398" s="35" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E398" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="30" t="s">
+        <v>977</v>
+      </c>
+      <c r="B399" s="31" t="s">
+        <v>976</v>
+      </c>
+      <c r="C399" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D399" s="35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E399" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="30" t="s">
+        <v>978</v>
+      </c>
+      <c r="B400" s="31" t="s">
+        <v>979</v>
+      </c>
+      <c r="C400" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D400" s="35" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E400" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="30" t="s">
+        <v>980</v>
+      </c>
+      <c r="B401" s="31" t="s">
+        <v>979</v>
+      </c>
+      <c r="C401" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D401" s="35" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E401" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="B402" s="31" t="s">
+        <v>982</v>
+      </c>
+      <c r="C402" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D402" s="35" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E402" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="30" t="s">
+        <v>983</v>
+      </c>
+      <c r="B403" s="31" t="s">
+        <v>982</v>
+      </c>
+      <c r="C403" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D403" s="35" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E403" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="B404" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="C404" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="D404" s="35" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E404" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="B405" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="C405" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="D405" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E405" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="B406" s="31" t="s">
+        <v>989</v>
+      </c>
+      <c r="C406" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D406" s="35" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E406" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="30" t="s">
+        <v>990</v>
+      </c>
+      <c r="B407" s="31" t="s">
+        <v>989</v>
+      </c>
+      <c r="C407" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D407" s="35" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E407" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="B408" s="32" t="s">
+        <v>992</v>
+      </c>
+      <c r="C408" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="D408" s="35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E408" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="B409" s="32" t="s">
+        <v>992</v>
+      </c>
+      <c r="C409" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="D409" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E409" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="B410" s="31" t="s">
+        <v>995</v>
+      </c>
+      <c r="C410" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D410" s="35" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E410" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="B411" s="31" t="s">
+        <v>997</v>
+      </c>
+      <c r="C411" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D411" s="35" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E411" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="B412" s="31" t="s">
+        <v>997</v>
+      </c>
+      <c r="C412" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D412" s="35" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E412" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="B413" s="31" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C413" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D413" s="35" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E413" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B414" s="31" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C414" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D414" s="35" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E414" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B415" s="31" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C415" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D415" s="35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E415" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B416" s="31" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C416" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D416" s="35" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E416" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B417" s="31" t="s">
+        <v>926</v>
+      </c>
+      <c r="C417" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D417" s="35" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E417" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B418" s="31" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C418" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D418" s="35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E418" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B419" s="31" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C419" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D419" s="35" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E419" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B420" s="31" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C420" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D420" s="35" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E420" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="30" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B421" s="31" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C421" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D421" s="35" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E421" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B422" s="31" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C422" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D422" s="35" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E422" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B423" s="31" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C423" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D423" s="35" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E423" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="30" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B424" s="31" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C424" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D424" s="35" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E424" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="30" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B425" s="31" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C425" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D425" s="35" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E425" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="30" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B426" s="31" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C426" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D426" s="35" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E426" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B427" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C427" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D427" s="35" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E427" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B428" s="31" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C428" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D428" s="35" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E428" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="30" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B429" s="31" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C429" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D429" s="35" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E429" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="30" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B430" s="31" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C430" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D430" s="35" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E430" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B431" s="31" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C431" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D431" s="35" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E431" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B432" s="31" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C432" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D432" s="35" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E432" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B433" s="31" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C433" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D433" s="35" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E433" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B434" s="31" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C434" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D434" s="35" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E434" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="30" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B435" s="31" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C435" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D435" s="35" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E435" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B436" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="C436" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D436" s="35" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E436" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B437" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C437" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D437" s="35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E437" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="30" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B438" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C438" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D438" s="35" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E438" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B439" s="31" t="s">
+        <v>860</v>
+      </c>
+      <c r="C439" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D439" s="35" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E439" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="30" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B440" s="31" t="s">
+        <v>866</v>
+      </c>
+      <c r="C440" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D440" s="35" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E440" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B441" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C441" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D441" s="35" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E441" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B442" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C442" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D442" s="35" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E442" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="30" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B443" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C443" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D443" s="35" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E443" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B444" s="31" t="s">
+        <v>868</v>
+      </c>
+      <c r="C444" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D444" s="35" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E444" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B445" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="C445" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D445" s="35" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E445" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B446" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="C446" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D446" s="35" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E446" s="35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="30" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B447" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="C447" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D447" s="35" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E447" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B448" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="C448" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D448" s="35" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E448" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B449" s="31" t="s">
+        <v>879</v>
+      </c>
+      <c r="C449" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D449" s="35" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E449" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B450" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="C450" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D450" s="35" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E450" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B451" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="C451" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D451" s="35" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E451" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B452" s="31" t="s">
+        <v>884</v>
+      </c>
+      <c r="C452" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D452" s="35" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E452" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B453" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="C453" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D453" s="35" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E453" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B454" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="C454" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D454" s="35" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E454" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B455" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C455" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D455" s="35" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E455" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B456" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C456" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D456" s="35" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E456" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="30" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B457" s="31" t="s">
+        <v>892</v>
+      </c>
+      <c r="C457" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D457" s="35" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E457" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="30" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B458" s="31" t="s">
+        <v>894</v>
+      </c>
+      <c r="C458" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D458" s="35" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E458" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="30" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B459" s="31" t="s">
+        <v>896</v>
+      </c>
+      <c r="C459" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D459" s="35" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E459" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="30" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B460" s="31" t="s">
+        <v>898</v>
+      </c>
+      <c r="C460" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D460" s="35" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E460" s="35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="30" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B461" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="C461" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D461" s="35" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E461" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="30" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B462" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="C462" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D462" s="35" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E462" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="30" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B463" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="C463" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D463" s="35" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E463" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="30" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B464" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="C464" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D464" s="35" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E464" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="30" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B465" s="31" t="s">
+        <v>906</v>
+      </c>
+      <c r="C465" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D465" s="35" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E465" s="35">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="30" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B466" s="31" t="s">
+        <v>906</v>
+      </c>
+      <c r="C466" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D466" s="35" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E466" s="35">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="30" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B467" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="C467" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D467" s="35" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E467" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="30" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B468" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="C468" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D468" s="35" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E468" s="35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="30" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B469" s="31" t="s">
+        <v>912</v>
+      </c>
+      <c r="C469" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D469" s="35" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E469" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="30" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B470" s="31" t="s">
+        <v>912</v>
+      </c>
+      <c r="C470" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D470" s="35" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E470" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="30" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B471" s="31" t="s">
+        <v>915</v>
+      </c>
+      <c r="C471" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D471" s="35" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E471" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="30" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B472" s="31" t="s">
+        <v>915</v>
+      </c>
+      <c r="C472" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D472" s="35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E472" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="30" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B473" s="31" t="s">
+        <v>918</v>
+      </c>
+      <c r="C473" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D473" s="35" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E473" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="30" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B474" s="31" t="s">
+        <v>918</v>
+      </c>
+      <c r="C474" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D474" s="35" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E474" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="30" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B475" s="31" t="s">
+        <v>923</v>
+      </c>
+      <c r="C475" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D475" s="35" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E475" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="30" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B476" s="31" t="s">
+        <v>923</v>
+      </c>
+      <c r="C476" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D476" s="35" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E476" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="30" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B477" s="31" t="s">
+        <v>926</v>
+      </c>
+      <c r="C477" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D477" s="35" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E477" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="30" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B478" s="31" t="s">
+        <v>928</v>
+      </c>
+      <c r="C478" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D478" s="35" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E478" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="30" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B479" s="31" t="s">
+        <v>928</v>
+      </c>
+      <c r="C479" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D479" s="35" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E479" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="30" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B480" s="31" t="s">
+        <v>931</v>
+      </c>
+      <c r="C480" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D480" s="35" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E480" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="30" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B481" s="31" t="s">
+        <v>931</v>
+      </c>
+      <c r="C481" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D481" s="35" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E481" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="30" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B482" s="31" t="s">
+        <v>934</v>
+      </c>
+      <c r="C482" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D482" s="35" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E482" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="30" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B483" s="31" t="s">
+        <v>934</v>
+      </c>
+      <c r="C483" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D483" s="35" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E483" s="35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="30" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B484" s="31" t="s">
+        <v>937</v>
+      </c>
+      <c r="C484" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D484" s="35" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E484" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="30" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B485" s="31" t="s">
+        <v>939</v>
+      </c>
+      <c r="C485" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D485" s="35" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E485" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="30" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B486" s="31" t="s">
+        <v>941</v>
+      </c>
+      <c r="C486" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D486" s="35" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E486" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487" s="30" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B487" s="31" t="s">
+        <v>941</v>
+      </c>
+      <c r="C487" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D487" s="35" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E487" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488" s="30" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B488" s="31" t="s">
+        <v>944</v>
+      </c>
+      <c r="C488" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D488" s="35" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E488" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489" s="30" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B489" s="31" t="s">
+        <v>944</v>
+      </c>
+      <c r="C489" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D489" s="35" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E489" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490" s="30" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B490" s="31" t="s">
+        <v>947</v>
+      </c>
+      <c r="C490" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D490" s="35" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E490" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491" s="30" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B491" s="31" t="s">
+        <v>947</v>
+      </c>
+      <c r="C491" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D491" s="35" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E491" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492" s="30" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B492" s="31" t="s">
+        <v>950</v>
+      </c>
+      <c r="C492" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D492" s="35" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E492" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493" s="30" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B493" s="31" t="s">
+        <v>950</v>
+      </c>
+      <c r="C493" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D493" s="35" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E493" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494" s="30" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B494" s="31" t="s">
+        <v>953</v>
+      </c>
+      <c r="C494" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D494" s="35" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E494" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495" s="30" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B495" s="31" t="s">
+        <v>953</v>
+      </c>
+      <c r="C495" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D495" s="35" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E495" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496" s="30" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B496" s="31" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C496" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D496" s="35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E496" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497" s="30" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B497" s="31" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C497" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D497" s="35" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E497" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498" s="30" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B498" s="31" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C498" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D498" s="35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E498" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" s="30" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B499" s="31" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C499" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D499" s="35" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E499" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" s="30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B500" s="31" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C500" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D500" s="35" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E500" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" s="30" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B501" s="31" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C501" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D501" s="35" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E501" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" s="30" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B502" s="31" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C502" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D502" s="35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E502" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="18.75">
+      <c r="A503" s="30" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B503" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C503" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D503" s="34" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E503" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="18.75">
+      <c r="A504" s="30" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B504" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C504" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D504" s="34" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E504" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" ht="18.75">
+      <c r="A505" s="30" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B505" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C505" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D505" s="34" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E505" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" ht="18.75">
+      <c r="A506" s="30" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B506" s="31" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C506" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D506" s="34" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E506" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" ht="18.75">
+      <c r="A507" s="30" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B507" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C507" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D507" s="34" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E507" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" ht="18.75">
+      <c r="A508" s="30" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B508" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C508" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D508" s="34" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E508" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" ht="18.75">
+      <c r="A509" s="30" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B509" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C509" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D509" s="34" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E509" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" ht="18.75">
+      <c r="A510" s="30" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B510" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C510" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D510" s="34" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E510" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="18.75">
+      <c r="A511" s="30" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B511" s="31" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C511" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D511" s="34" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E511" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" ht="18.75">
+      <c r="A512" s="30" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B512" s="31" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C512" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D512" s="34" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E512" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" s="30" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B513" s="31" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C513" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D513" s="35" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E513" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" s="30" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B514" s="31" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C514" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D514" s="35" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E514" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515" s="30" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B515" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C515" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D515" s="35" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E515" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516" s="30" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B516" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C516" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D516" s="35" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E516" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517" s="30" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B517" s="31" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C517" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D517" s="35" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E517" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518" s="30" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B518" s="31" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C518" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D518" s="35" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E518" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519" s="30" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B519" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C519" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D519" s="35" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E519" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520" s="30" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B520" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C520" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D520" s="35" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E520" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521" s="30" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B521" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C521" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D521" s="35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E521" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522" s="30" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B522" s="31" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C522" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D522" s="35" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E522" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523" s="30" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B523" s="31" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C523" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D523" s="35" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E523" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524" s="30" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B524" s="31" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C524" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D524" s="35" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E524" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525" s="36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B525" s="37" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C525" s="38" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D525" s="39"/>
+      <c r="E525" s="39">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526" s="36" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B526" s="37" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C526" s="38" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D526" s="39"/>
+      <c r="E526" s="39">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" ht="18.75">
+      <c r="A527" s="36" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B527" s="37" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C527" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D527" s="40" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E527" s="39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" ht="18.75">
+      <c r="A528" s="36" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B528" s="37" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C528" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D528" s="40" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E528" s="39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" ht="18.75">
+      <c r="A529" s="36" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B529" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C529" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D529" s="40" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E529" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" ht="18.75">
+      <c r="A530" s="36" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B530" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C530" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D530" s="40" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E530" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5">
+      <c r="A531" s="36" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B531" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C531" s="38" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D531" s="39"/>
+      <c r="E531" s="39">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" ht="18.75">
+      <c r="A532" s="36" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B532" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C532" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D532" s="40" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E532" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" ht="18.75">
+      <c r="A533" s="36" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B533" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C533" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D533" s="40" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E533" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5">
+      <c r="A534" s="36" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B534" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C534" s="38" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D534" s="39"/>
+      <c r="E534" s="39">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" ht="18.75">
+      <c r="A535" s="36" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B535" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C535" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D535" s="40" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E535" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" ht="18.75">
+      <c r="A536" s="36" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B536" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C536" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D536" s="40" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E536" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5">
+      <c r="A537" s="36" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B537" s="37" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C537" s="38" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D537" s="39"/>
+      <c r="E537" s="39">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" ht="18.75">
+      <c r="A538" s="36" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B538" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C538" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D538" s="40" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E538" s="39">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5">
+      <c r="A539" s="36" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B539" s="37" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C539" s="38" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D539" s="39"/>
+      <c r="E539" s="39">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" ht="18.75">
+      <c r="A540" s="36" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B540" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C540" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D540" s="40" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E540" s="39">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5">
+      <c r="A541" s="36" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B541" s="37" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C541" s="38" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D541" s="39"/>
+      <c r="E541" s="39">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" ht="18.75">
+      <c r="A542" s="36" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B542" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C542" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D542" s="40" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E542" s="39">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5">
+      <c r="A543" s="36" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B543" s="37" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C543" s="38" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D543" s="39"/>
+      <c r="E543" s="39">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" ht="18.75">
+      <c r="A544" s="36" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B544" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C544" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D544" s="40" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E544" s="39">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545" s="36" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B545" s="37" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C545" s="38" t="s">
+        <v>919</v>
+      </c>
+      <c r="D545" s="39" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E545" s="39">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" s="36" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B546" s="37" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C546" s="38" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D546" s="39"/>
+      <c r="E546" s="39">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" ht="18.75">
+      <c r="A547" s="36" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B547" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C547" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D547" s="40" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E547" s="39">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" s="36" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B548" s="37" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C548" s="38" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D548" s="39"/>
+      <c r="E548" s="39">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" ht="18.75">
+      <c r="A549" s="36" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B549" s="37" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C549" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D549" s="40" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E549" s="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" ht="18.75">
+      <c r="A550" s="36" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B550" s="37" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C550" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D550" s="40" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E550" s="39">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551" s="36" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B551" s="37" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C551" s="38" t="s">
+        <v>921</v>
+      </c>
+      <c r="D551" s="39" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E551" s="39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552" s="36" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B552" s="37" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C552" s="38" t="s">
+        <v>919</v>
+      </c>
+      <c r="D552" s="39" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E552" s="39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553" s="36" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B553" s="37" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C553" s="38" t="s">
+        <v>921</v>
+      </c>
+      <c r="D553" s="39" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E553" s="39">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554" s="36" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B554" s="37" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C554" s="38" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D554" s="39"/>
+      <c r="E554" s="39">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555" s="36" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B555" s="37" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C555" s="38" t="s">
+        <v>968</v>
+      </c>
+      <c r="D555" s="39" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E555" s="39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556" s="36" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B556" s="37" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C556" s="38" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D556" s="39"/>
+      <c r="E556" s="39">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557" s="36" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B557" s="37" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C557" s="38" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D557" s="39"/>
+      <c r="E557" s="39">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558" s="36" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B558" s="37" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C558" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D558" s="39" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E558" s="39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5">
+      <c r="A559" s="36" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B559" s="37" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C559" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D559" s="39" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E559" s="39">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5">
+      <c r="A560" s="36" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B560" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C560" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D560" s="39" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E560" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561" s="36" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B561" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C561" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D561" s="39" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E561" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5">
+      <c r="A562" s="36" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B562" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C562" s="38" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D562" s="39"/>
+      <c r="E562" s="39">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5">
+      <c r="A563" s="36" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B563" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C563" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D563" s="39" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E563" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5">
+      <c r="A564" s="36" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B564" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C564" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D564" s="39" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E564" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5">
+      <c r="A565" s="36" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B565" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C565" s="38" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D565" s="39"/>
+      <c r="E565" s="39">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5">
+      <c r="A566" s="36" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B566" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C566" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D566" s="39" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E566" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5">
+      <c r="A567" s="36" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B567" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C567" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D567" s="39" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E567" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" s="36" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B568" s="37" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C568" s="38" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D568" s="39"/>
+      <c r="E568" s="39">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569" s="36" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B569" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C569" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D569" s="39" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E569" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570" s="36" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B570" s="37" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C570" s="38" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D570" s="39"/>
+      <c r="E570" s="39">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5">
+      <c r="A571" s="36" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B571" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C571" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D571" s="39" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E571" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572" s="36" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B572" s="37" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C572" s="38" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D572" s="39"/>
+      <c r="E572" s="39">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573" s="36" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B573" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C573" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D573" s="39" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E573" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5">
+      <c r="A574" s="36" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B574" s="37" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C574" s="38" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D574" s="39"/>
+      <c r="E574" s="39">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5">
+      <c r="A575" s="36" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B575" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C575" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D575" s="39" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E575" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5">
+      <c r="A576" s="36" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B576" s="37" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C576" s="38" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D576" s="39" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E576" s="39">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5">
+      <c r="A577" s="36" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B577" s="37" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C577" s="38" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D577" s="39"/>
+      <c r="E577" s="39">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5">
+      <c r="A578" s="36" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B578" s="37" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C578" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D578" s="39" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E578" s="39">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5">
+      <c r="A579" s="36" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B579" s="37" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C579" s="38" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D579" s="39"/>
+      <c r="E579" s="39">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5">
+      <c r="A580" s="36" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B580" s="37" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C580" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D580" s="39" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E580" s="39">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5">
+      <c r="A581" s="36" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B581" s="37" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C581" s="38" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D581" s="39" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E581" s="39">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" ht="18.75">
+      <c r="A582" s="30" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B582" s="31" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C582" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D582" s="34" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E582" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5">
+      <c r="A583" s="30" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B583" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C583" s="32" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D583" s="35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E583" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5">
+      <c r="A584" s="30" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B584" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C584" s="32" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D584" s="35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E584" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5">
+      <c r="A585" s="30" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B585" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C585" s="32" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D585" s="35" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E585" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5">
+      <c r="A586" s="30" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B586" s="32" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C586" s="32" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D586" s="35" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E586" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5">
+      <c r="A587" s="30" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B587" s="31" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C587" s="33" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D587" s="35"/>
+      <c r="E587" s="35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" ht="18.75">
+      <c r="A588" s="30" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B588" s="31" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C588" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D588" s="34" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E588" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" ht="18.75">
+      <c r="A589" s="30" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B589" s="31" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C589" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D589" s="34" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E589" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5">
+      <c r="A590" s="30" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B590" s="31" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C590" s="33" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D590" s="35"/>
+      <c r="E590" s="35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" ht="18.75">
+      <c r="A591" s="30" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B591" s="31" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C591" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D591" s="34" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E591" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" ht="18.75">
+      <c r="A592" s="30" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B592" s="31" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C592" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D592" s="34" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E592" s="35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" ht="18.75">
+      <c r="A593" s="30" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B593" s="31" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C593" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D593" s="34" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E593" s="35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" ht="18.75">
+      <c r="A594" s="30" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B594" s="31" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C594" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D594" s="34" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E594" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" ht="18.75">
+      <c r="A595" s="30" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B595" s="31" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C595" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D595" s="34" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E595" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5">
+      <c r="A596" s="30" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B596" s="31" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C596" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D596" s="35" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E596" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5">
+      <c r="A597" s="30" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B597" s="31" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C597" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D597" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E597" s="35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5">
+      <c r="A598" s="30" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B598" s="32" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C598" s="32" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D598" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E598" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5">
+      <c r="A599" s="30" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B599" s="31" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C599" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D599" s="35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E599" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5">
+      <c r="A600" s="30" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B600" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C600" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D600" s="35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E600" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5">
+      <c r="A601" s="30" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B601" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C601" s="32" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D601" s="35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E601" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5">
+      <c r="A602" s="30" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B602" s="32" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C602" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D602" s="35" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E602" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5">
+      <c r="A603" s="30" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B603" s="32" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C603" s="32" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D603" s="35" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E603" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5">
+      <c r="A604" s="30" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B604" s="31" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C604" s="33" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D604" s="35"/>
+      <c r="E604" s="35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5">
+      <c r="A605" s="30" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B605" s="31" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C605" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D605" s="35" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E605" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5">
+      <c r="A606" s="30" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B606" s="31" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C606" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D606" s="35" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E606" s="35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5">
+      <c r="A607" s="30" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B607" s="31" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C607" s="33" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D607" s="35"/>
+      <c r="E607" s="35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5">
+      <c r="A608" s="30" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B608" s="31" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C608" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D608" s="35" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E608" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5">
+      <c r="A609" s="30" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B609" s="31" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C609" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D609" s="35" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E609" s="35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5">
+      <c r="A610" s="30" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B610" s="31" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C610" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D610" s="35" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E610" s="35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5">
+      <c r="A611" s="30" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B611" s="31" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C611" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D611" s="35" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E611" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5">
+      <c r="A612" s="30" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B612" s="31" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C612" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D612" s="35" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E612" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5">
+      <c r="A613" s="36" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B613" s="37" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C613" s="38" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D613" s="39"/>
+      <c r="E613" s="39">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5">
+      <c r="A614" s="36" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B614" s="37" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C614" s="38" t="s">
+        <v>919</v>
+      </c>
+      <c r="D614" s="39" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E614" s="39">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5">
+      <c r="A615" s="36" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B615" s="38" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C615" s="38" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D615" s="41"/>
+      <c r="E615" s="39">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5">
+      <c r="A616" s="36" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B616" s="38" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C616" s="38" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D616" s="41"/>
+      <c r="E616" s="39">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5">
+      <c r="A617" s="36" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B617" s="37" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C617" s="38" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D617" s="39"/>
+      <c r="E617" s="39">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5">
+      <c r="A618" s="36" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B618" s="37" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C618" s="38" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D618" s="39" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E618" s="39">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5">
+      <c r="A619" s="36" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B619" s="38" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C619" s="38" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D619" s="41"/>
+      <c r="E619" s="39">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5">
+      <c r="A620" s="36" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B620" s="38" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C620" s="38" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D620" s="41"/>
+      <c r="E620" s="39">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5">
+      <c r="A621" s="36" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B621" s="37" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C621" s="38" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D621" s="39"/>
+      <c r="E621" s="39">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" ht="18.75">
+      <c r="A622" s="36" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B622" s="37" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C622" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="D622" s="40" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E622" s="39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5">
+      <c r="A623" s="36" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B623" s="38" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C623" s="38" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D623" s="41"/>
+      <c r="E623" s="39">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5">
+      <c r="A624" s="36" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B624" s="37" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C624" s="38" t="s">
+        <v>919</v>
+      </c>
+      <c r="D624" s="39" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E624" s="39">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" ht="18.75">
+      <c r="A625" s="36" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B625" s="37" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C625" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D625" s="40" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E625" s="39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" ht="18.75">
+      <c r="A626" s="36" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B626" s="37" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C626" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="D626" s="40" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E626" s="39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5">
+      <c r="A627" s="36" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B627" s="37" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C627" s="38" t="s">
+        <v>919</v>
+      </c>
+      <c r="D627" s="39" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E627" s="39">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5">
+      <c r="A628" s="36" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B628" s="37" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C628" s="38" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D628" s="39"/>
+      <c r="E628" s="39">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5">
+      <c r="A629" s="30" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B629" s="31" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C629" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D629" s="35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E629" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5">
+      <c r="A630" s="42" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B630" s="33" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C630" s="33" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D630" s="3"/>
+      <c r="E630" s="43">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5">
+      <c r="A631" s="30" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B631" s="31" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C631" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D631" s="35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E631" s="35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5">
+      <c r="A632" s="30" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B632" s="31" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C632" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D632" s="35" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E632" s="35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5">
+      <c r="A633" s="30" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B633" s="31" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C633" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D633" s="35" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E633" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5">
+      <c r="A634" s="30" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B634" s="31" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C634" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D634" s="35" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E634" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5">
+      <c r="A635" s="30" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B635" s="31" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C635" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D635" s="35" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E635" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" ht="18.75">
+      <c r="A636" s="30" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B636" s="31" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C636" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D636" s="34" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E636" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5">
+      <c r="A637" s="30" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B637" s="31" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C637" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D637" s="35" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E637" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5">
+      <c r="A638" s="30" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B638" s="31" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C638" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D638" s="35" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E638" s="35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5">
+      <c r="A639" s="30" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B639" s="32" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C639" s="32" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D639" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E639" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5">
+      <c r="A640" s="30" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B640" s="32" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C640" s="32" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D640" s="35" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E640" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5">
+      <c r="A641" s="30" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B641" s="32" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C641" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D641" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E641" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5">
+      <c r="A642" s="30" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B642" s="32" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C642" s="32" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D642" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E642" s="35">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5">
+      <c r="A643" s="30" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B643" s="31" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C643" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D643" s="35" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E643" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5">
+      <c r="A644" s="30" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B644" s="31" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C644" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D644" s="35" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E644" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5">
+      <c r="A645" s="30" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B645" s="31" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C645" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D645" s="35" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E645" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5">
+      <c r="A646" s="30" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B646" s="31" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C646" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D646" s="35" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E646" s="35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" ht="18.75">
+      <c r="A647" s="30" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B647" s="31" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C647" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D647" s="34" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E647" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5">
+      <c r="A648" s="30" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B648" s="32" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C648" s="32" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D648" s="35" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E648" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5">
+      <c r="A649" s="30" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B649" s="31" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C649" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D649" s="35" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E649" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5">
+      <c r="A650" s="30" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B650" s="32" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C650" s="32" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D650" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E650" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5">
+      <c r="A651" s="30" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B651" s="31" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C651" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D651" s="35" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E651" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5">
+      <c r="A652" s="30" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B652" s="31" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C652" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D652" s="35" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E652" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5">
+      <c r="A653" s="30" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B653" s="31" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C653" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D653" s="35" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E653" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5">
+      <c r="A654" s="30" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B654" s="31" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C654" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D654" s="35" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E654" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5">
+      <c r="A655" s="30" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B655" s="31" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C655" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D655" s="35" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E655" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5">
+      <c r="A656" s="30" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B656" s="31" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C656" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D656" s="35" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E656" s="35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5">
+      <c r="A657" s="44" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B657" s="45" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C657" s="45" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E657" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5">
+      <c r="A658" s="30" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B658" s="31" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C658" s="32" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D658" s="35" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E658" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5">
+      <c r="A659" s="30" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B659" s="31" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C659" s="32" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D659" s="35" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E659" s="35">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5">
+      <c r="A660" s="30" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B660" s="31" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C660" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="D660" s="35" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E660" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5">
+      <c r="A661" s="30" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B661" s="32" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C661" s="32" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D661" s="35" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E661" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5">
+      <c r="A662" s="30" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B662" s="32" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C662" s="32" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D662" s="35" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E662" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" ht="18.75">
+      <c r="A663" s="30" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B663" s="31" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C663" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D663" s="34" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E663" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" ht="18.75">
+      <c r="A664" s="30" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B664" s="31" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C664" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D664" s="34" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E664" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" ht="18.75">
+      <c r="A665" s="30" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B665" s="31" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C665" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D665" s="34" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E665" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" ht="18.75">
+      <c r="A666" s="30" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B666" s="31" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C666" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D666" s="34" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E666" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" ht="18.75">
+      <c r="A667" s="30" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B667" s="31" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C667" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D667" s="34" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E667" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" ht="18.75">
+      <c r="A668" s="30" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B668" s="31" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C668" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D668" s="34" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E668" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" ht="18.75">
+      <c r="A669" s="30" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B669" s="31" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C669" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D669" s="34" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E669" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" ht="18.75">
+      <c r="A670" s="30" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B670" s="31" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C670" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D670" s="34" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E670" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" ht="18.75">
+      <c r="A671" s="30" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B671" s="31" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C671" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D671" s="34" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E671" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" ht="18.75">
+      <c r="A672" s="30" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B672" s="31" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C672" s="32" t="s">
+        <v>863</v>
+      </c>
+      <c r="D672" s="34" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E672" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" ht="18.75">
+      <c r="A673" s="30" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B673" s="31" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C673" s="32" t="s">
+        <v>861</v>
+      </c>
+      <c r="D673" s="34" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E673" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5">
+      <c r="A674" s="30" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B674" s="32" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C674" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D674" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E674" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5">
+      <c r="A675" s="30" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B675" s="32" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C675" s="32" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D675" s="35" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E675" s="35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5">
+      <c r="A676" s="30" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B676" s="31" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C676" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D676" s="35" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E676" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5">
+      <c r="A677" s="30" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B677" s="31" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C677" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D677" s="35" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E677" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5">
+      <c r="A678" s="30" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B678" s="31" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C678" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D678" s="35" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E678" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5">
+      <c r="A679" s="30" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B679" s="31" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C679" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D679" s="35" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E679" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5">
+      <c r="A680" s="30" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B680" s="31" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C680" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D680" s="35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E680" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5">
+      <c r="A681" s="30" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B681" s="31" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C681" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D681" s="35" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E681" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5">
+      <c r="A682" s="30" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B682" s="31" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C682" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D682" s="35" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E682" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5">
+      <c r="A683" s="30" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B683" s="31" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C683" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D683" s="35" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E683" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5">
+      <c r="A684" s="30" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B684" s="31" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C684" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D684" s="35" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E684" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5">
+      <c r="A685" s="30" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B685" s="31" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C685" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D685" s="35" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E685" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5">
+      <c r="A686" s="30" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B686" s="31" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C686" s="32" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D686" s="35" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E686" s="35">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5">
+      <c r="A687" s="30" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B687" s="31" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C687" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D687" s="35" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E687" s="35">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3E792B-D26C-4BC7-BBA5-E41BD3889685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE525465-1892-4C96-8C88-0933D6A60BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="396" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="396" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6277" uniqueCount="3076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6471" uniqueCount="3209">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -9420,13 +9420,412 @@
   </si>
   <si>
     <t>Dry TR. for Welding Receptacle DB (A80-CSH-PDB-021)</t>
+  </si>
+  <si>
+    <t>MP-1101 B</t>
+  </si>
+  <si>
+    <t>MP-1508 A</t>
+  </si>
+  <si>
+    <t>MP-1901 B</t>
+  </si>
+  <si>
+    <t>MP-1508 B</t>
+  </si>
+  <si>
+    <t>MK-1102 B</t>
+  </si>
+  <si>
+    <t>MP-1501 B</t>
+  </si>
+  <si>
+    <t>MP-1502 B</t>
+  </si>
+  <si>
+    <t>MP-1301 A</t>
+  </si>
+  <si>
+    <t>MP-1401 B</t>
+  </si>
+  <si>
+    <t>MP-1504 A</t>
+  </si>
+  <si>
+    <t>MME-1991</t>
+  </si>
+  <si>
+    <t>MME-1992</t>
+  </si>
+  <si>
+    <t>MME-1993</t>
+  </si>
+  <si>
+    <t>MP-1101 A</t>
+  </si>
+  <si>
+    <t>K-1102A-H1</t>
+  </si>
+  <si>
+    <t>MP-1901A</t>
+  </si>
+  <si>
+    <t>MP-1903A</t>
+  </si>
+  <si>
+    <t>MP-1903B</t>
+  </si>
+  <si>
+    <t>MP-1301 B</t>
+  </si>
+  <si>
+    <t>MP-1401 A</t>
+  </si>
+  <si>
+    <t>MP-1402 B</t>
+  </si>
+  <si>
+    <t>MP-1402 A</t>
+  </si>
+  <si>
+    <t>MP-1505</t>
+  </si>
+  <si>
+    <t>MP-1902 A</t>
+  </si>
+  <si>
+    <t>MP-1902 B</t>
+  </si>
+  <si>
+    <t>K-1102B-H1</t>
+  </si>
+  <si>
+    <t>MP-1501 A</t>
+  </si>
+  <si>
+    <t>MP-1502 A</t>
+  </si>
+  <si>
+    <t>MK-1601</t>
+  </si>
+  <si>
+    <t>K-1601-MP1</t>
+  </si>
+  <si>
+    <t>K-1601-MP2</t>
+  </si>
+  <si>
+    <t>K-1601-MK1</t>
+  </si>
+  <si>
+    <t>К-1601-ЕН1</t>
+  </si>
+  <si>
+    <t>T-1101A-H1</t>
+  </si>
+  <si>
+    <t>T-1101A-H2</t>
+  </si>
+  <si>
+    <t>T-1101A-H3</t>
+  </si>
+  <si>
+    <t>T-1101A-H4</t>
+  </si>
+  <si>
+    <t>T-1101A-H5</t>
+  </si>
+  <si>
+    <t>T-1101A-MK1</t>
+  </si>
+  <si>
+    <t>T-1101A-MK2</t>
+  </si>
+  <si>
+    <t>T-1101A-MK3</t>
+  </si>
+  <si>
+    <t>T-1101A-MK4</t>
+  </si>
+  <si>
+    <t>T-1101A-MP2</t>
+  </si>
+  <si>
+    <t>T-1101A-MP3</t>
+  </si>
+  <si>
+    <t>T-1101A-MP4</t>
+  </si>
+  <si>
+    <t>T-1101B-H1</t>
+  </si>
+  <si>
+    <t>T-1101B-H2</t>
+  </si>
+  <si>
+    <t>T-1101B-H3</t>
+  </si>
+  <si>
+    <t>T-1101B-H4</t>
+  </si>
+  <si>
+    <t>T-1101B-H5</t>
+  </si>
+  <si>
+    <t>T-1101B-MK1</t>
+  </si>
+  <si>
+    <t>T-1101B-MK2</t>
+  </si>
+  <si>
+    <t>T-1101B-MK3</t>
+  </si>
+  <si>
+    <t>T-1101B-MK4</t>
+  </si>
+  <si>
+    <t>T-1101B-MP2</t>
+  </si>
+  <si>
+    <t>T-1101B-MP3</t>
+  </si>
+  <si>
+    <t>T-1101B-MP4</t>
+  </si>
+  <si>
+    <t>T-1303A-H1</t>
+  </si>
+  <si>
+    <t>T-1303A-H2</t>
+  </si>
+  <si>
+    <t>T-1303A-H3</t>
+  </si>
+  <si>
+    <t>T-1303A-H4</t>
+  </si>
+  <si>
+    <t>T-1303A-H5</t>
+  </si>
+  <si>
+    <t>T-1303A-MK1</t>
+  </si>
+  <si>
+    <t>T-1303A-MK2</t>
+  </si>
+  <si>
+    <t>T-1303A-MK3</t>
+  </si>
+  <si>
+    <t>T-1303A-MK4</t>
+  </si>
+  <si>
+    <t>T-1303A-MP2</t>
+  </si>
+  <si>
+    <t>T-1303A-MP3</t>
+  </si>
+  <si>
+    <t>T-1303A-MP4</t>
+  </si>
+  <si>
+    <t>T-1303B-H1</t>
+  </si>
+  <si>
+    <t>T-1303B-H2</t>
+  </si>
+  <si>
+    <t>T-1303B-H3</t>
+  </si>
+  <si>
+    <t>T-1303B-H4</t>
+  </si>
+  <si>
+    <t>T-1303B-H5</t>
+  </si>
+  <si>
+    <t>T-1303B-MK1</t>
+  </si>
+  <si>
+    <t>T-1303B-MK2</t>
+  </si>
+  <si>
+    <t>T-1303B-MK3</t>
+  </si>
+  <si>
+    <t>T-1303B-MK4</t>
+  </si>
+  <si>
+    <t>T-1303B-MP2</t>
+  </si>
+  <si>
+    <t>T-1303B-MP3</t>
+  </si>
+  <si>
+    <t>T-1303B-MP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MK-1102А </t>
+  </si>
+  <si>
+    <t>МК-1102B-МР1</t>
+  </si>
+  <si>
+    <t>MP-1504 B</t>
+  </si>
+  <si>
+    <t>MP-1102</t>
+  </si>
+  <si>
+    <t>МК-1102А-МР1</t>
+  </si>
+  <si>
+    <t>MP-1503 A</t>
+  </si>
+  <si>
+    <t>MP-1506</t>
+  </si>
+  <si>
+    <t>MP-1503 B</t>
+  </si>
+  <si>
+    <t>X-1501-MAG1</t>
+  </si>
+  <si>
+    <t>X-1501-MP1A</t>
+  </si>
+  <si>
+    <t>X-1501-MP1B</t>
+  </si>
+  <si>
+    <t>A10-PC-301</t>
+  </si>
+  <si>
+    <t>A10-PC-302-A</t>
+  </si>
+  <si>
+    <t>A10-PC-301B</t>
+  </si>
+  <si>
+    <t>A10-PC-302</t>
+  </si>
+  <si>
+    <t>A10-PC-301-</t>
+  </si>
+  <si>
+    <t>A10-PC-302-1B</t>
+  </si>
+  <si>
+    <t>A10-PC-302B</t>
+  </si>
+  <si>
+    <t>A10-PC-302A</t>
+  </si>
+  <si>
+    <t>A10-PC-301A</t>
+  </si>
+  <si>
+    <t>A10-PC-301-1A</t>
+  </si>
+  <si>
+    <t>PDB</t>
+  </si>
+  <si>
+    <t>EP-301-1A</t>
+  </si>
+  <si>
+    <t>EP-301</t>
+  </si>
+  <si>
+    <t>A10-PC-302-1A</t>
+  </si>
+  <si>
+    <t>A10-PC-302-</t>
+  </si>
+  <si>
+    <t>FTA-1101A-MCC</t>
+  </si>
+  <si>
+    <t>Panel K-1303B-MCC</t>
+  </si>
+  <si>
+    <t>A10-PC-301-A</t>
+  </si>
+  <si>
+    <t>AR04-7</t>
+  </si>
+  <si>
+    <t>BR02</t>
+  </si>
+  <si>
+    <t>BF01</t>
+  </si>
+  <si>
+    <t>BF02</t>
+  </si>
+  <si>
+    <t>AF02</t>
+  </si>
+  <si>
+    <t>AR03</t>
+  </si>
+  <si>
+    <t>AR02-3</t>
+  </si>
+  <si>
+    <t>AF01</t>
+  </si>
+  <si>
+    <t>402-2</t>
+  </si>
+  <si>
+    <t>ARO01-2</t>
+  </si>
+  <si>
+    <t>AR01</t>
+  </si>
+  <si>
+    <t>AR02-</t>
+  </si>
+  <si>
+    <t>BR01</t>
+  </si>
+  <si>
+    <t>AF03</t>
+  </si>
+  <si>
+    <t>BR04</t>
+  </si>
+  <si>
+    <t>BR02-1</t>
+  </si>
+  <si>
+    <t>AR04</t>
+  </si>
+  <si>
+    <t>BR03</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B1A</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B1E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9538,6 +9937,60 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -9565,7 +10018,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -9640,6 +10093,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -9650,7 +10116,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9793,6 +10259,63 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10110,7 +10633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F1392"/>
+  <dimension ref="A1:F1484"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -34700,6 +35223,1212 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1393" spans="1:6" ht="15.75">
+      <c r="A1393" s="49" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C1393" s="57" t="s">
+        <v>3168</v>
+      </c>
+      <c r="D1393" s="57" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E1393" s="66">
+        <v>5.5</v>
+      </c>
+      <c r="F1393" s="57"/>
+    </row>
+    <row r="1394" spans="1:6" ht="15.75">
+      <c r="A1394" s="49" t="s">
+        <v>3077</v>
+      </c>
+      <c r="C1394" s="57" t="s">
+        <v>3169</v>
+      </c>
+      <c r="D1394" s="57" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E1394" s="66">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F1394" s="57" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:6" ht="15.75">
+      <c r="A1395" s="49" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C1395" s="57" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1395" s="57" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E1395" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1395" s="57" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:6" ht="15.75">
+      <c r="A1396" s="49" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C1396" s="58" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1396" s="57" t="s">
+        <v>3187</v>
+      </c>
+      <c r="E1396" s="64">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F1396" s="57" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:6" ht="15.75">
+      <c r="A1397" s="49" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1397" s="58" t="s">
+        <v>3172</v>
+      </c>
+      <c r="D1397" s="57" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E1397" s="66">
+        <v>120</v>
+      </c>
+      <c r="F1397" s="58"/>
+    </row>
+    <row r="1398" spans="1:6" ht="15.75">
+      <c r="A1398" s="49" t="s">
+        <v>3081</v>
+      </c>
+      <c r="C1398" s="58" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1398" s="57" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E1398" s="64">
+        <v>110</v>
+      </c>
+      <c r="F1398" s="57" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:6" ht="15.75">
+      <c r="A1399" s="49" t="s">
+        <v>3082</v>
+      </c>
+      <c r="C1399" s="58" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1399" s="57" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E1399" s="66">
+        <v>110</v>
+      </c>
+      <c r="F1399" s="57" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:6" ht="15.75">
+      <c r="A1400" s="49" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C1400" s="59" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1400" s="59" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1400" s="64">
+        <v>45</v>
+      </c>
+      <c r="F1400" s="59"/>
+    </row>
+    <row r="1401" spans="1:6" ht="15.75">
+      <c r="A1401" s="49" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C1401" s="57" t="s">
+        <v>3174</v>
+      </c>
+      <c r="D1401" s="57" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E1401" s="66">
+        <v>30</v>
+      </c>
+      <c r="F1401" s="57" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:6" ht="15.75">
+      <c r="A1402" s="50" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C1402" s="60" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1402" s="60" t="s">
+        <v>3191</v>
+      </c>
+      <c r="E1402" s="64">
+        <v>11</v>
+      </c>
+      <c r="F1402" s="60" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:6" ht="15.75">
+      <c r="A1403" s="49" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1403" s="57" t="s">
+        <v>3175</v>
+      </c>
+      <c r="D1403" s="57" t="s">
+        <v>3192</v>
+      </c>
+      <c r="E1403" s="64"/>
+      <c r="F1403" s="57"/>
+    </row>
+    <row r="1404" spans="1:6" ht="15.75">
+      <c r="A1404" s="49" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C1404" s="57" t="s">
+        <v>3176</v>
+      </c>
+      <c r="D1404" s="57" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E1404" s="64"/>
+      <c r="F1404" s="57"/>
+    </row>
+    <row r="1405" spans="1:6" ht="15.75">
+      <c r="A1405" s="51" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C1405" s="57" t="s">
+        <v>3176</v>
+      </c>
+      <c r="D1405" s="57" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E1405" s="64"/>
+      <c r="F1405" s="57"/>
+    </row>
+    <row r="1406" spans="1:6" ht="15.75">
+      <c r="A1406" s="49" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1406" s="58" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D1406" s="58" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1406" s="66">
+        <v>5.5</v>
+      </c>
+      <c r="F1406" s="58"/>
+    </row>
+    <row r="1407" spans="1:6" ht="15.75">
+      <c r="A1407" s="50" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C1407" s="61" t="s">
+        <v>3178</v>
+      </c>
+      <c r="D1407" s="61" t="s">
+        <v>3194</v>
+      </c>
+      <c r="E1407" s="67"/>
+      <c r="F1407" s="61"/>
+    </row>
+    <row r="1408" spans="1:6" ht="15.75">
+      <c r="A1408" s="49" t="s">
+        <v>3091</v>
+      </c>
+      <c r="C1408" s="61" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D1408" s="64" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1408" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1408" s="64"/>
+    </row>
+    <row r="1409" spans="1:6" ht="15.75">
+      <c r="A1409" s="49" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C1409" s="58" t="s">
+        <v>3179</v>
+      </c>
+      <c r="D1409" s="57" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1409" s="64">
+        <v>15</v>
+      </c>
+      <c r="F1409" s="57" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:6" ht="15.75">
+      <c r="A1410" s="52" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C1410" s="61" t="s">
+        <v>3180</v>
+      </c>
+      <c r="D1410" s="64" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1410" s="64">
+        <v>15</v>
+      </c>
+      <c r="F1410" s="64" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:6" ht="15.75">
+      <c r="A1411" s="49" t="s">
+        <v>3094</v>
+      </c>
+      <c r="C1411" s="58" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1411" s="58" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1411" s="64">
+        <v>45</v>
+      </c>
+      <c r="F1411" s="58"/>
+    </row>
+    <row r="1412" spans="1:6" ht="15.75">
+      <c r="A1412" s="49" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C1412" s="58" t="s">
+        <v>3175</v>
+      </c>
+      <c r="D1412" s="64" t="s">
+        <v>3195</v>
+      </c>
+      <c r="E1412" s="64">
+        <v>30</v>
+      </c>
+      <c r="F1412" s="64"/>
+    </row>
+    <row r="1413" spans="1:6" ht="15.75">
+      <c r="A1413" s="49" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C1413" s="58" t="s">
+        <v>3174</v>
+      </c>
+      <c r="D1413" s="58" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E1413" s="67">
+        <v>37</v>
+      </c>
+      <c r="F1413" s="58"/>
+    </row>
+    <row r="1414" spans="1:6" ht="15.75">
+      <c r="A1414" s="49" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C1414" s="57" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D1414" s="57" t="s">
+        <v>3196</v>
+      </c>
+      <c r="E1414" s="66">
+        <v>37</v>
+      </c>
+      <c r="F1414" s="58"/>
+    </row>
+    <row r="1415" spans="1:6" ht="15.75">
+      <c r="A1415" s="49" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C1415" s="57" t="s">
+        <v>3175</v>
+      </c>
+      <c r="D1415" s="57" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E1415" s="64">
+        <v>11</v>
+      </c>
+      <c r="F1415" s="58"/>
+    </row>
+    <row r="1416" spans="1:6" ht="15.75">
+      <c r="A1416" s="49" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C1416" s="57" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D1416" s="57" t="s">
+        <v>3197</v>
+      </c>
+      <c r="E1416" s="64">
+        <v>22</v>
+      </c>
+      <c r="F1416" s="57" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:6" ht="15.75">
+      <c r="A1417" s="49" t="s">
+        <v>3100</v>
+      </c>
+      <c r="C1417" s="57" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1417" s="57" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E1417" s="64">
+        <v>22</v>
+      </c>
+      <c r="F1417" s="58"/>
+    </row>
+    <row r="1418" spans="1:6" ht="15.75">
+      <c r="A1418" s="50" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1418" s="60" t="s">
+        <v>3178</v>
+      </c>
+      <c r="D1418" s="60"/>
+      <c r="E1418" s="66"/>
+      <c r="F1418" s="61"/>
+    </row>
+    <row r="1419" spans="1:6" ht="15.75">
+      <c r="A1419" s="49" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C1419" s="57" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D1419" s="57"/>
+      <c r="E1419" s="66">
+        <v>110</v>
+      </c>
+      <c r="F1419" s="58"/>
+    </row>
+    <row r="1420" spans="1:6" ht="15.75">
+      <c r="A1420" s="49" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1420" s="57" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D1420" s="57" t="s">
+        <v>3199</v>
+      </c>
+      <c r="E1420" s="66">
+        <v>110</v>
+      </c>
+      <c r="F1420" s="58"/>
+    </row>
+    <row r="1421" spans="1:6" ht="15.75">
+      <c r="A1421" s="50" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C1421" s="57"/>
+      <c r="D1421" s="57"/>
+      <c r="E1421" s="64">
+        <v>4200</v>
+      </c>
+      <c r="F1421" s="58"/>
+    </row>
+    <row r="1422" spans="1:6" ht="15.75">
+      <c r="A1422" s="50" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1422" s="57" t="s">
+        <v>3179</v>
+      </c>
+      <c r="D1422" s="57" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1422" s="64">
+        <v>15</v>
+      </c>
+      <c r="F1422" s="58"/>
+    </row>
+    <row r="1423" spans="1:6" ht="15.75">
+      <c r="A1423" s="50" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C1423" s="57" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D1423" s="57" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1423" s="64">
+        <v>15</v>
+      </c>
+      <c r="F1423" s="58"/>
+    </row>
+    <row r="1424" spans="1:6" ht="15.75">
+      <c r="A1424" s="50" t="s">
+        <v>3107</v>
+      </c>
+      <c r="C1424" s="57" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1424" s="57" t="s">
+        <v>3200</v>
+      </c>
+      <c r="E1424" s="64">
+        <v>1</v>
+      </c>
+      <c r="F1424" s="58"/>
+    </row>
+    <row r="1425" spans="1:6" ht="15.75">
+      <c r="A1425" s="53" t="s">
+        <v>3108</v>
+      </c>
+      <c r="C1425" s="57" t="s">
+        <v>3179</v>
+      </c>
+      <c r="D1425" s="57" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1425" s="64">
+        <v>30</v>
+      </c>
+      <c r="F1425" s="58"/>
+    </row>
+    <row r="1426" spans="1:6" ht="15.75">
+      <c r="A1426" s="53" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C1426" s="57"/>
+      <c r="D1426" s="57"/>
+      <c r="E1426" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1426" s="58"/>
+    </row>
+    <row r="1427" spans="1:6" ht="15.75">
+      <c r="A1427" s="53" t="s">
+        <v>3110</v>
+      </c>
+      <c r="C1427" s="62" t="s">
+        <v>3183</v>
+      </c>
+      <c r="D1427" s="57"/>
+      <c r="E1427" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1427" s="58"/>
+    </row>
+    <row r="1428" spans="1:6" ht="15.75">
+      <c r="A1428" s="53" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C1428" s="57"/>
+      <c r="D1428" s="57"/>
+      <c r="E1428" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1428" s="58"/>
+    </row>
+    <row r="1429" spans="1:6" ht="15.75">
+      <c r="A1429" s="53" t="s">
+        <v>3112</v>
+      </c>
+      <c r="C1429" s="57"/>
+      <c r="D1429" s="57"/>
+      <c r="E1429" s="64">
+        <v>63.76</v>
+      </c>
+      <c r="F1429" s="58"/>
+    </row>
+    <row r="1430" spans="1:6" ht="15.75">
+      <c r="A1430" s="53" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1430" s="57"/>
+      <c r="D1430" s="57"/>
+      <c r="E1430" s="64">
+        <v>106.24</v>
+      </c>
+      <c r="F1430" s="58"/>
+    </row>
+    <row r="1431" spans="1:6" ht="15.75">
+      <c r="A1431" s="53" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C1431" s="57"/>
+      <c r="D1431" s="57"/>
+      <c r="E1431" s="64">
+        <v>1.5</v>
+      </c>
+      <c r="F1431" s="58"/>
+    </row>
+    <row r="1432" spans="1:6" ht="15.75">
+      <c r="A1432" s="53" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C1432" s="57"/>
+      <c r="D1432" s="57"/>
+      <c r="E1432" s="64">
+        <v>7.5</v>
+      </c>
+      <c r="F1432" s="58"/>
+    </row>
+    <row r="1433" spans="1:6" ht="15.75">
+      <c r="A1433" s="53" t="s">
+        <v>3116</v>
+      </c>
+      <c r="C1433" s="57"/>
+      <c r="D1433" s="57"/>
+      <c r="E1433" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1433" s="58"/>
+    </row>
+    <row r="1434" spans="1:6" ht="15.75">
+      <c r="A1434" s="53" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1434" s="57"/>
+      <c r="D1434" s="57"/>
+      <c r="E1434" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1434" s="58"/>
+    </row>
+    <row r="1435" spans="1:6" ht="15.75">
+      <c r="A1435" s="53" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C1435" s="57"/>
+      <c r="D1435" s="57"/>
+      <c r="E1435" s="64">
+        <v>12.3</v>
+      </c>
+      <c r="F1435" s="58"/>
+    </row>
+    <row r="1436" spans="1:6" ht="15.75">
+      <c r="A1436" s="53" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1436" s="57"/>
+      <c r="D1436" s="57"/>
+      <c r="E1436" s="64">
+        <v>0.74</v>
+      </c>
+      <c r="F1436" s="58"/>
+    </row>
+    <row r="1437" spans="1:6" ht="15.75">
+      <c r="A1437" s="53" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C1437" s="57"/>
+      <c r="D1437" s="57"/>
+      <c r="E1437" s="64">
+        <v>110</v>
+      </c>
+      <c r="F1437" s="58"/>
+    </row>
+    <row r="1438" spans="1:6" ht="15.75">
+      <c r="A1438" s="53" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1438" s="57"/>
+      <c r="D1438" s="57"/>
+      <c r="E1438" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1438" s="58"/>
+    </row>
+    <row r="1439" spans="1:6" ht="15.75">
+      <c r="A1439" s="53" t="s">
+        <v>3122</v>
+      </c>
+      <c r="C1439" s="57"/>
+      <c r="D1439" s="57"/>
+      <c r="E1439" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1439" s="58"/>
+    </row>
+    <row r="1440" spans="1:6" ht="15.75">
+      <c r="A1440" s="53" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C1440" s="57"/>
+      <c r="D1440" s="57"/>
+      <c r="E1440" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1440" s="58"/>
+    </row>
+    <row r="1441" spans="1:6" ht="15.75">
+      <c r="A1441" s="53" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C1441" s="57"/>
+      <c r="D1441" s="57"/>
+      <c r="E1441" s="64">
+        <v>63.76</v>
+      </c>
+      <c r="F1441" s="58"/>
+    </row>
+    <row r="1442" spans="1:6" ht="15.75">
+      <c r="A1442" s="53" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1442" s="57" t="s">
+        <v>3172</v>
+      </c>
+      <c r="D1442" s="57" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E1442" s="64">
+        <v>106.24</v>
+      </c>
+      <c r="F1442" s="58"/>
+    </row>
+    <row r="1443" spans="1:6" ht="15.75">
+      <c r="A1443" s="53" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C1443" s="57"/>
+      <c r="D1443" s="57"/>
+      <c r="E1443" s="64">
+        <v>1.5</v>
+      </c>
+      <c r="F1443" s="58"/>
+    </row>
+    <row r="1444" spans="1:6" ht="15.75">
+      <c r="A1444" s="54" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C1444" s="57"/>
+      <c r="D1444" s="57"/>
+      <c r="E1444" s="64">
+        <v>7.5</v>
+      </c>
+      <c r="F1444" s="58"/>
+    </row>
+    <row r="1445" spans="1:6" ht="15.75">
+      <c r="A1445" s="54" t="s">
+        <v>3128</v>
+      </c>
+      <c r="C1445" s="57"/>
+      <c r="D1445" s="57"/>
+      <c r="E1445" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1445" s="58"/>
+    </row>
+    <row r="1446" spans="1:6" ht="15.75">
+      <c r="A1446" s="54" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1446" s="57"/>
+      <c r="D1446" s="57"/>
+      <c r="E1446" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1446" s="58"/>
+    </row>
+    <row r="1447" spans="1:6" ht="15.75">
+      <c r="A1447" s="54" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1447" s="57"/>
+      <c r="D1447" s="57"/>
+      <c r="E1447" s="64">
+        <v>12.3</v>
+      </c>
+      <c r="F1447" s="58"/>
+    </row>
+    <row r="1448" spans="1:6" ht="15.75">
+      <c r="A1448" s="53" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C1448" s="57"/>
+      <c r="D1448" s="57"/>
+      <c r="E1448" s="64">
+        <v>0.74</v>
+      </c>
+      <c r="F1448" s="58"/>
+    </row>
+    <row r="1449" spans="1:6" ht="15.75">
+      <c r="A1449" s="54" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1449" s="57"/>
+      <c r="D1449" s="57"/>
+      <c r="E1449" s="64">
+        <v>110</v>
+      </c>
+      <c r="F1449" s="58"/>
+    </row>
+    <row r="1450" spans="1:6" ht="15.75">
+      <c r="A1450" s="53" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1450" s="57"/>
+      <c r="D1450" s="57"/>
+      <c r="E1450" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1450" s="58"/>
+    </row>
+    <row r="1451" spans="1:6" ht="15.75">
+      <c r="A1451" s="53" t="s">
+        <v>3134</v>
+      </c>
+      <c r="C1451" s="57"/>
+      <c r="D1451" s="57"/>
+      <c r="E1451" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1451" s="58"/>
+    </row>
+    <row r="1452" spans="1:6" ht="15.75">
+      <c r="A1452" s="53" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1452" s="57"/>
+      <c r="D1452" s="57"/>
+      <c r="E1452" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1452" s="58"/>
+    </row>
+    <row r="1453" spans="1:6" ht="15.75">
+      <c r="A1453" s="53" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1453" s="57"/>
+      <c r="D1453" s="57"/>
+      <c r="E1453" s="64">
+        <v>63.76</v>
+      </c>
+      <c r="F1453" s="58"/>
+    </row>
+    <row r="1454" spans="1:6" ht="15.75">
+      <c r="A1454" s="53" t="s">
+        <v>3137</v>
+      </c>
+      <c r="C1454" s="57" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D1454" s="57" t="s">
+        <v>3199</v>
+      </c>
+      <c r="E1454" s="64">
+        <v>106.24</v>
+      </c>
+      <c r="F1454" s="58"/>
+    </row>
+    <row r="1455" spans="1:6" ht="15.75">
+      <c r="A1455" s="53" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1455" s="57"/>
+      <c r="D1455" s="57"/>
+      <c r="E1455" s="64">
+        <v>1.5</v>
+      </c>
+      <c r="F1455" s="58"/>
+    </row>
+    <row r="1456" spans="1:6" ht="15.75">
+      <c r="A1456" s="53" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C1456" s="57"/>
+      <c r="D1456" s="57"/>
+      <c r="E1456" s="64">
+        <v>7.5</v>
+      </c>
+      <c r="F1456" s="58"/>
+    </row>
+    <row r="1457" spans="1:6" ht="15.75">
+      <c r="A1457" s="53" t="s">
+        <v>3140</v>
+      </c>
+      <c r="C1457" s="57"/>
+      <c r="D1457" s="57"/>
+      <c r="E1457" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1457" s="58"/>
+    </row>
+    <row r="1458" spans="1:6" ht="15.75">
+      <c r="A1458" s="53" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1458" s="57"/>
+      <c r="D1458" s="57"/>
+      <c r="E1458" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1458" s="58"/>
+    </row>
+    <row r="1459" spans="1:6" ht="15.75">
+      <c r="A1459" s="53" t="s">
+        <v>3142</v>
+      </c>
+      <c r="C1459" s="57"/>
+      <c r="D1459" s="57"/>
+      <c r="E1459" s="64">
+        <v>12.3</v>
+      </c>
+      <c r="F1459" s="58"/>
+    </row>
+    <row r="1460" spans="1:6" ht="15.75">
+      <c r="A1460" s="53" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1460" s="57"/>
+      <c r="D1460" s="57"/>
+      <c r="E1460" s="64">
+        <v>0.74</v>
+      </c>
+      <c r="F1460" s="58"/>
+    </row>
+    <row r="1461" spans="1:6" ht="15.75">
+      <c r="A1461" s="53" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1461" s="57"/>
+      <c r="D1461" s="57"/>
+      <c r="E1461" s="64">
+        <v>110</v>
+      </c>
+      <c r="F1461" s="58"/>
+    </row>
+    <row r="1462" spans="1:6" ht="15.75">
+      <c r="A1462" s="53" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C1462" s="57"/>
+      <c r="D1462" s="57"/>
+      <c r="E1462" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1462" s="58"/>
+    </row>
+    <row r="1463" spans="1:6" ht="15.75">
+      <c r="A1463" s="53" t="s">
+        <v>3146</v>
+      </c>
+      <c r="C1463" s="57"/>
+      <c r="D1463" s="57"/>
+      <c r="E1463" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1463" s="58"/>
+    </row>
+    <row r="1464" spans="1:6" ht="15.75">
+      <c r="A1464" s="53" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1464" s="57"/>
+      <c r="D1464" s="57"/>
+      <c r="E1464" s="64">
+        <v>9</v>
+      </c>
+      <c r="F1464" s="58"/>
+    </row>
+    <row r="1465" spans="1:6" ht="15.75">
+      <c r="A1465" s="53" t="s">
+        <v>3148</v>
+      </c>
+      <c r="C1465" s="57"/>
+      <c r="D1465" s="57"/>
+      <c r="E1465" s="64">
+        <v>63.76</v>
+      </c>
+      <c r="F1465" s="58"/>
+    </row>
+    <row r="1466" spans="1:6" ht="15.75">
+      <c r="A1466" s="53" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C1466" s="57" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1466" s="57" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E1466" s="64">
+        <v>106.24</v>
+      </c>
+      <c r="F1466" s="58"/>
+    </row>
+    <row r="1467" spans="1:6" ht="15.75">
+      <c r="A1467" s="53" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1467" s="57"/>
+      <c r="D1467" s="57"/>
+      <c r="E1467" s="64">
+        <v>1.5</v>
+      </c>
+      <c r="F1467" s="58"/>
+    </row>
+    <row r="1468" spans="1:6" ht="15.75">
+      <c r="A1468" s="53" t="s">
+        <v>3151</v>
+      </c>
+      <c r="C1468" s="57"/>
+      <c r="D1468" s="57"/>
+      <c r="E1468" s="64">
+        <v>7.5</v>
+      </c>
+      <c r="F1468" s="58"/>
+    </row>
+    <row r="1469" spans="1:6" ht="15.75">
+      <c r="A1469" s="54" t="s">
+        <v>3152</v>
+      </c>
+      <c r="C1469" s="62" t="s">
+        <v>3184</v>
+      </c>
+      <c r="D1469" s="57"/>
+      <c r="E1469" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1469" s="58"/>
+    </row>
+    <row r="1470" spans="1:6" ht="15.75">
+      <c r="A1470" s="54" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1470" s="57"/>
+      <c r="D1470" s="57"/>
+      <c r="E1470" s="64">
+        <v>37</v>
+      </c>
+      <c r="F1470" s="58"/>
+    </row>
+    <row r="1471" spans="1:6" ht="15.75">
+      <c r="A1471" s="54" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C1471" s="57"/>
+      <c r="D1471" s="57"/>
+      <c r="E1471" s="64">
+        <v>12.3</v>
+      </c>
+      <c r="F1471" s="58"/>
+    </row>
+    <row r="1472" spans="1:6" ht="15.75">
+      <c r="A1472" s="54" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C1472" s="57"/>
+      <c r="D1472" s="57"/>
+      <c r="E1472" s="64">
+        <v>0.74</v>
+      </c>
+      <c r="F1472" s="58"/>
+    </row>
+    <row r="1473" spans="1:6" ht="15.75">
+      <c r="A1473" s="54" t="s">
+        <v>3156</v>
+      </c>
+      <c r="C1473" s="57"/>
+      <c r="D1473" s="57"/>
+      <c r="E1473" s="64">
+        <v>110</v>
+      </c>
+      <c r="F1473" s="58"/>
+    </row>
+    <row r="1474" spans="1:6" ht="15.75">
+      <c r="A1474" s="49" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1474" s="63" t="s">
+        <v>3185</v>
+      </c>
+      <c r="D1474" s="63" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1474" s="64">
+        <v>120</v>
+      </c>
+      <c r="F1474" s="65"/>
+    </row>
+    <row r="1475" spans="1:6">
+      <c r="A1475" s="55" t="s">
+        <v>3158</v>
+      </c>
+      <c r="C1475" s="57" t="s">
+        <v>3180</v>
+      </c>
+      <c r="D1475" s="57" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1475" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="F1475" s="58"/>
+    </row>
+    <row r="1476" spans="1:6" ht="15.75">
+      <c r="A1476" s="49" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C1476" s="57" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1476" s="57" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E1476" s="64">
+        <v>11</v>
+      </c>
+      <c r="F1476" s="58"/>
+    </row>
+    <row r="1477" spans="1:6" ht="15.75">
+      <c r="A1477" s="49" t="s">
+        <v>3160</v>
+      </c>
+      <c r="C1477" s="61" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1477" s="60" t="s">
+        <v>3201</v>
+      </c>
+      <c r="E1477" s="66">
+        <v>30</v>
+      </c>
+      <c r="F1477" s="61"/>
+    </row>
+    <row r="1478" spans="1:6">
+      <c r="A1478" s="56" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1478" s="61" t="s">
+        <v>3179</v>
+      </c>
+      <c r="D1478" s="60" t="s">
+        <v>3193</v>
+      </c>
+      <c r="E1478" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="F1478" s="61"/>
+    </row>
+    <row r="1479" spans="1:6" ht="15.75">
+      <c r="A1479" s="50" t="s">
+        <v>3162</v>
+      </c>
+      <c r="C1479" s="58" t="s">
+        <v>3175</v>
+      </c>
+      <c r="D1479" s="57" t="s">
+        <v>3192</v>
+      </c>
+      <c r="E1479" s="66">
+        <v>4</v>
+      </c>
+      <c r="F1479" s="58"/>
+    </row>
+    <row r="1480" spans="1:6" ht="15.75">
+      <c r="A1480" s="49" t="s">
+        <v>3163</v>
+      </c>
+      <c r="C1480" s="58" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1480" s="57" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E1480" s="64">
+        <v>7.5</v>
+      </c>
+      <c r="F1480" s="58"/>
+    </row>
+    <row r="1481" spans="1:6" ht="15.75">
+      <c r="A1481" s="49" t="s">
+        <v>3164</v>
+      </c>
+      <c r="C1481" s="57" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D1481" s="57" t="s">
+        <v>3200</v>
+      </c>
+      <c r="E1481" s="66">
+        <v>4</v>
+      </c>
+      <c r="F1481" s="58"/>
+    </row>
+    <row r="1482" spans="1:6" ht="15.75">
+      <c r="A1482" s="49" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1482" s="57" t="s">
+        <v>3177</v>
+      </c>
+      <c r="D1482" s="57" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E1482" s="64">
+        <v>0.75</v>
+      </c>
+      <c r="F1482" s="58"/>
+    </row>
+    <row r="1483" spans="1:6" ht="15.75">
+      <c r="A1483" s="49" t="s">
+        <v>3166</v>
+      </c>
+      <c r="C1483" s="57" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D1483" s="57" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E1483" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="F1483" s="58"/>
+    </row>
+    <row r="1484" spans="1:6" ht="15.75">
+      <c r="A1484" s="49" t="s">
+        <v>3167</v>
+      </c>
+      <c r="C1484" s="57" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1484" s="57" t="s">
+        <v>3203</v>
+      </c>
+      <c r="E1484" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="F1484" s="58"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE525465-1892-4C96-8C88-0933D6A60BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22908F7-BDBB-4C68-9539-292F2D74429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="396" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6471" uniqueCount="3209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7135" uniqueCount="3538">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -9665,39 +9665,6 @@
     <t>T-1303B-MP4</t>
   </si>
   <si>
-    <t xml:space="preserve">MK-1102А </t>
-  </si>
-  <si>
-    <t>МК-1102B-МР1</t>
-  </si>
-  <si>
-    <t>MP-1504 B</t>
-  </si>
-  <si>
-    <t>MP-1102</t>
-  </si>
-  <si>
-    <t>МК-1102А-МР1</t>
-  </si>
-  <si>
-    <t>MP-1503 A</t>
-  </si>
-  <si>
-    <t>MP-1506</t>
-  </si>
-  <si>
-    <t>MP-1503 B</t>
-  </si>
-  <si>
-    <t>X-1501-MAG1</t>
-  </si>
-  <si>
-    <t>X-1501-MP1A</t>
-  </si>
-  <si>
-    <t>X-1501-MP1B</t>
-  </si>
-  <si>
     <t>A10-PC-301</t>
   </si>
   <si>
@@ -9749,9 +9716,6 @@
     <t>Panel K-1303B-MCC</t>
   </si>
   <si>
-    <t>A10-PC-301-A</t>
-  </si>
-  <si>
     <t>AR04-7</t>
   </si>
   <si>
@@ -9797,9 +9761,6 @@
     <t>BR04</t>
   </si>
   <si>
-    <t>BR02-1</t>
-  </si>
-  <si>
     <t>AR04</t>
   </si>
   <si>
@@ -9819,13 +9780,1039 @@
   </si>
   <si>
     <t>B1E</t>
+  </si>
+  <si>
+    <t>MP-5104B</t>
+  </si>
+  <si>
+    <t>MP-5107A</t>
+  </si>
+  <si>
+    <t>MAG-5110B</t>
+  </si>
+  <si>
+    <t>MK-5401</t>
+  </si>
+  <si>
+    <t>MP-5403</t>
+  </si>
+  <si>
+    <t>MK-5403</t>
+  </si>
+  <si>
+    <t>MAG-5401</t>
+  </si>
+  <si>
+    <t>MW-5807</t>
+  </si>
+  <si>
+    <t>MAG-5805</t>
+  </si>
+  <si>
+    <t>MRF-5901B</t>
+  </si>
+  <si>
+    <t>MRF-5901D</t>
+  </si>
+  <si>
+    <t>MRF-5501A</t>
+  </si>
+  <si>
+    <t>MK-5703</t>
+  </si>
+  <si>
+    <t>MK-5801A</t>
+  </si>
+  <si>
+    <t>MK-5802</t>
+  </si>
+  <si>
+    <t>MK-5801A-1(fan)</t>
+  </si>
+  <si>
+    <t>MK-5802-1(fan)</t>
+  </si>
+  <si>
+    <t>MP-5101A</t>
+  </si>
+  <si>
+    <t>MP-5107B</t>
+  </si>
+  <si>
+    <t>MAG-5106B</t>
+  </si>
+  <si>
+    <t>MP-5401B</t>
+  </si>
+  <si>
+    <t>MP-5606A</t>
+  </si>
+  <si>
+    <t>MP-5702</t>
+  </si>
+  <si>
+    <t>MK-5704</t>
+  </si>
+  <si>
+    <t>MP-5802B</t>
+  </si>
+  <si>
+    <t>MP-5805A</t>
+  </si>
+  <si>
+    <t>MRF-5902B</t>
+  </si>
+  <si>
+    <t>MP-5101B</t>
+  </si>
+  <si>
+    <t>MP-5104A</t>
+  </si>
+  <si>
+    <t>MP-5105</t>
+  </si>
+  <si>
+    <t>MP-5112</t>
+  </si>
+  <si>
+    <t>MP-5113B</t>
+  </si>
+  <si>
+    <t>MAG-5106A</t>
+  </si>
+  <si>
+    <t>MP-5303</t>
+  </si>
+  <si>
+    <t>MRF-5501B</t>
+  </si>
+  <si>
+    <t>MP-5802A</t>
+  </si>
+  <si>
+    <t>MK-5902C</t>
+  </si>
+  <si>
+    <t>MP-5106A</t>
+  </si>
+  <si>
+    <t>MP-5113A</t>
+  </si>
+  <si>
+    <t>MP-5302A</t>
+  </si>
+  <si>
+    <t>MP-5608B</t>
+  </si>
+  <si>
+    <t>MK-5702A</t>
+  </si>
+  <si>
+    <t>MP-5804A</t>
+  </si>
+  <si>
+    <t>MRF-5903</t>
+  </si>
+  <si>
+    <t>MRF-5904</t>
+  </si>
+  <si>
+    <t>MRF-5905</t>
+  </si>
+  <si>
+    <t>MP-5102</t>
+  </si>
+  <si>
+    <t>MP-5110</t>
+  </si>
+  <si>
+    <t>MP-5503</t>
+  </si>
+  <si>
+    <t>MK-5602</t>
+  </si>
+  <si>
+    <t>MP-5805B</t>
+  </si>
+  <si>
+    <t>MK-5801B</t>
+  </si>
+  <si>
+    <t>MP-5104C</t>
+  </si>
+  <si>
+    <t>MP-5601A</t>
+  </si>
+  <si>
+    <t>MP-5603B</t>
+  </si>
+  <si>
+    <t>MP-5604B</t>
+  </si>
+  <si>
+    <t>MAG-5804</t>
+  </si>
+  <si>
+    <t>MK-5901A</t>
+  </si>
+  <si>
+    <t>MRF-5901A</t>
+  </si>
+  <si>
+    <t>MRF-5901C</t>
+  </si>
+  <si>
+    <t>MRF-5902A</t>
+  </si>
+  <si>
+    <t>MP-5104D</t>
+  </si>
+  <si>
+    <t>MP-5106B</t>
+  </si>
+  <si>
+    <t>MAG-5110A</t>
+  </si>
+  <si>
+    <t>MP-5502B</t>
+  </si>
+  <si>
+    <t>MP-5604A</t>
+  </si>
+  <si>
+    <t>MP-5610</t>
+  </si>
+  <si>
+    <t>MP-5801B</t>
+  </si>
+  <si>
+    <t>MK-5902B</t>
+  </si>
+  <si>
+    <t>MP-5108A</t>
+  </si>
+  <si>
+    <t>MP-5108B</t>
+  </si>
+  <si>
+    <t>MP-5109</t>
+  </si>
+  <si>
+    <t>MAG-5201</t>
+  </si>
+  <si>
+    <t>MP-5200</t>
+  </si>
+  <si>
+    <t>MP-5201</t>
+  </si>
+  <si>
+    <t>MP-5202</t>
+  </si>
+  <si>
+    <t>MP-5203</t>
+  </si>
+  <si>
+    <t>MP-5204</t>
+  </si>
+  <si>
+    <t>MP-5205A</t>
+  </si>
+  <si>
+    <t>MP-5205B</t>
+  </si>
+  <si>
+    <t>MP-5206A</t>
+  </si>
+  <si>
+    <t>MP-5206B</t>
+  </si>
+  <si>
+    <t>MP-5207A</t>
+  </si>
+  <si>
+    <t>MP-5207B</t>
+  </si>
+  <si>
+    <t>MP-5301A</t>
+  </si>
+  <si>
+    <t>MP-5301B</t>
+  </si>
+  <si>
+    <t>MK-5301</t>
+  </si>
+  <si>
+    <t>MP-5304</t>
+  </si>
+  <si>
+    <t>MP-5305B</t>
+  </si>
+  <si>
+    <t>MAG-5301</t>
+  </si>
+  <si>
+    <t>MK-5501</t>
+  </si>
+  <si>
+    <t>MK-5502A</t>
+  </si>
+  <si>
+    <t>MK-5502B</t>
+  </si>
+  <si>
+    <t>MAG-5501</t>
+  </si>
+  <si>
+    <t>MRF-5502</t>
+  </si>
+  <si>
+    <t>MRF-5503</t>
+  </si>
+  <si>
+    <t>MK-5601</t>
+  </si>
+  <si>
+    <t>MK-5803</t>
+  </si>
+  <si>
+    <t>MK-5804</t>
+  </si>
+  <si>
+    <t>MP-5806</t>
+  </si>
+  <si>
+    <t>MRF-5802A</t>
+  </si>
+  <si>
+    <t>MRF-5802B</t>
+  </si>
+  <si>
+    <t>MRF-5803</t>
+  </si>
+  <si>
+    <t>MRF-5811</t>
+  </si>
+  <si>
+    <t>MM-5803</t>
+  </si>
+  <si>
+    <t>MM-5804</t>
+  </si>
+  <si>
+    <t>MM-5807</t>
+  </si>
+  <si>
+    <t>MK-5903</t>
+  </si>
+  <si>
+    <t>MP-5111A</t>
+  </si>
+  <si>
+    <t>MAG-5105</t>
+  </si>
+  <si>
+    <t>MP-5401A</t>
+  </si>
+  <si>
+    <t>MP-5501B</t>
+  </si>
+  <si>
+    <t>MP-5601B</t>
+  </si>
+  <si>
+    <t>MP-5603A</t>
+  </si>
+  <si>
+    <t>MK-5702B</t>
+  </si>
+  <si>
+    <t>MP-5804B</t>
+  </si>
+  <si>
+    <t>MK-5901B</t>
+  </si>
+  <si>
+    <t>A50-A50-PC-301A</t>
+  </si>
+  <si>
+    <t>A50-PC-301B</t>
+  </si>
+  <si>
+    <t>A50-PC-301A</t>
+  </si>
+  <si>
+    <t>A50-MS-201-6B</t>
+  </si>
+  <si>
+    <t>VSDS</t>
+  </si>
+  <si>
+    <t>A50-PC-302A</t>
+  </si>
+  <si>
+    <t>A50-PC-302B</t>
+  </si>
+  <si>
+    <t>A50-MS-201B</t>
+  </si>
+  <si>
+    <t>A50-PC-301-1A</t>
+  </si>
+  <si>
+    <t>EP-301N</t>
+  </si>
+  <si>
+    <t>A50-PC-302-1A</t>
+  </si>
+  <si>
+    <t>WWT</t>
+  </si>
+  <si>
+    <t>A50-PC-302</t>
+  </si>
+  <si>
+    <t>A50-PC-301-1B</t>
+  </si>
+  <si>
+    <t>A50-MS-201</t>
+  </si>
+  <si>
+    <t>A50-PC-301</t>
+  </si>
+  <si>
+    <t>A50-MS-201A</t>
+  </si>
+  <si>
+    <t>EP-301-E</t>
+  </si>
+  <si>
+    <t>A50-PC-301-B</t>
+  </si>
+  <si>
+    <t>A50-PC-301-A</t>
+  </si>
+  <si>
+    <t>A50-PC-302-A</t>
+  </si>
+  <si>
+    <t>A50-MS-201-B</t>
+  </si>
+  <si>
+    <t>A50-PC-302-B</t>
+  </si>
+  <si>
+    <t>A50-MS-101</t>
+  </si>
+  <si>
+    <t>AR02-8</t>
+  </si>
+  <si>
+    <t>BF-05</t>
+  </si>
+  <si>
+    <t>AF-04</t>
+  </si>
+  <si>
+    <t>BF-02-4</t>
+  </si>
+  <si>
+    <t>BF-02</t>
+  </si>
+  <si>
+    <t>BF04-2</t>
+  </si>
+  <si>
+    <t>BF-07</t>
+  </si>
+  <si>
+    <t>AR06</t>
+  </si>
+  <si>
+    <t>AF-01</t>
+  </si>
+  <si>
+    <t>AR-05</t>
+  </si>
+  <si>
+    <t>AF-06</t>
+  </si>
+  <si>
+    <t>BF02-6</t>
+  </si>
+  <si>
+    <t>AR02-7</t>
+  </si>
+  <si>
+    <t>AF02-6</t>
+  </si>
+  <si>
+    <t>BF01-6</t>
+  </si>
+  <si>
+    <t>AR02</t>
+  </si>
+  <si>
+    <t>BR01-2</t>
+  </si>
+  <si>
+    <t>BR07</t>
+  </si>
+  <si>
+    <t>BF03</t>
+  </si>
+  <si>
+    <t>BR07-7</t>
+  </si>
+  <si>
+    <t>AF05</t>
+  </si>
+  <si>
+    <t>AR05</t>
+  </si>
+  <si>
+    <t>BF04</t>
+  </si>
+  <si>
+    <t>AR-04</t>
+  </si>
+  <si>
+    <t>AR03-8</t>
+  </si>
+  <si>
+    <t>AR05-2</t>
+  </si>
+  <si>
+    <t>AR-01</t>
+  </si>
+  <si>
+    <t>BF07-4</t>
+  </si>
+  <si>
+    <t>BF01-7</t>
+  </si>
+  <si>
+    <t>BF03-5</t>
+  </si>
+  <si>
+    <t>BR-02</t>
+  </si>
+  <si>
+    <t>BR0-2</t>
+  </si>
+  <si>
+    <t>BF05-6</t>
+  </si>
+  <si>
+    <t>BF07-6</t>
+  </si>
+  <si>
+    <t>BF07-7</t>
+  </si>
+  <si>
+    <t>VF1</t>
+  </si>
+  <si>
+    <t>B1C</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>B3C1</t>
+  </si>
+  <si>
+    <t>B2A</t>
+  </si>
+  <si>
+    <t>B1A1</t>
+  </si>
+  <si>
+    <t>B1H</t>
+  </si>
+  <si>
+    <t>B3E</t>
+  </si>
+  <si>
+    <t>VF2</t>
+  </si>
+  <si>
+    <t>B1C1</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>B3A1</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B2B</t>
+  </si>
+  <si>
+    <t>B1F</t>
+  </si>
+  <si>
+    <t>B2F</t>
+  </si>
+  <si>
+    <t>B2A1</t>
+  </si>
+  <si>
+    <t>B2C</t>
+  </si>
+  <si>
+    <t>B1J</t>
+  </si>
+  <si>
+    <t>VF-1</t>
+  </si>
+  <si>
+    <t>B3A</t>
+  </si>
+  <si>
+    <t>B1I</t>
+  </si>
+  <si>
+    <t>V-5105 Agitator motor</t>
+  </si>
+  <si>
+    <t>V-5106A Agitator</t>
+  </si>
+  <si>
+    <t>V-5106B Agitator</t>
+  </si>
+  <si>
+    <t>V-5110 A/B Agitator motor</t>
+  </si>
+  <si>
+    <t>V-5201 Agitator motor</t>
+  </si>
+  <si>
+    <t>Dynamic separator motor</t>
+  </si>
+  <si>
+    <t>R-5401 Scraper motor</t>
+  </si>
+  <si>
+    <t>V-5501 Agitator motor</t>
+  </si>
+  <si>
+    <t>Z-5804Scraper motor</t>
+  </si>
+  <si>
+    <t>Z-5805 Scraper motor</t>
+  </si>
+  <si>
+    <t>ME-5880</t>
+  </si>
+  <si>
+    <t>Elevator for extruder bldg</t>
+  </si>
+  <si>
+    <t>MEX-5801</t>
+  </si>
+  <si>
+    <t>Main motor</t>
+  </si>
+  <si>
+    <t>MEX-5801-1</t>
+  </si>
+  <si>
+    <t>Barring motor</t>
+  </si>
+  <si>
+    <t>MEX-5801-4</t>
+  </si>
+  <si>
+    <t>Underwater pelletizer motor</t>
+  </si>
+  <si>
+    <t>Recycle gas compressor main motor</t>
+  </si>
+  <si>
+    <t>Circuration gas compressor</t>
+  </si>
+  <si>
+    <t>R-5401 Circulation gas blower-lube oil mist fan</t>
+  </si>
+  <si>
+    <t>C-5501 REFLUX PUMP</t>
+  </si>
+  <si>
+    <t>Dryr blower motor</t>
+  </si>
+  <si>
+    <t>MK-5502A-1(fan)</t>
+  </si>
+  <si>
+    <t>Exhaust fan for Mk-5502A</t>
+  </si>
+  <si>
+    <t>MK-5502B-1(fan)</t>
+  </si>
+  <si>
+    <t>Exhaust fan for Mk-5502B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refrigeration unit main motor </t>
+  </si>
+  <si>
+    <t>Drying circuit blower motor</t>
+  </si>
+  <si>
+    <t>MK-5701</t>
+  </si>
+  <si>
+    <t>Ethylene compressor</t>
+  </si>
+  <si>
+    <t>Hydrogen compressor</t>
+  </si>
+  <si>
+    <t>Nitrogen recycle blower-propylene drying pkg</t>
+  </si>
+  <si>
+    <t>Powder transfer blower</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5801A</t>
+  </si>
+  <si>
+    <t>MK-5801A-2(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-2 motor for K-5801A</t>
+  </si>
+  <si>
+    <t>MK-5801B-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5801B</t>
+  </si>
+  <si>
+    <t>MK-5801B-2(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5802</t>
+  </si>
+  <si>
+    <t>Pellet loading blower</t>
+  </si>
+  <si>
+    <t>MK-5802-2(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-2 motor for K-5802</t>
+  </si>
+  <si>
+    <t>Exhaust fan</t>
+  </si>
+  <si>
+    <t>Vacuum blower</t>
+  </si>
+  <si>
+    <t>Pellet silo intake blower</t>
+  </si>
+  <si>
+    <t>MK-5901A-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5901A</t>
+  </si>
+  <si>
+    <t>MK-5901B-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5901B</t>
+  </si>
+  <si>
+    <t>MK-5902A</t>
+  </si>
+  <si>
+    <t>Pellet blend loading blower</t>
+  </si>
+  <si>
+    <t>MK-5902A-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5902A</t>
+  </si>
+  <si>
+    <t>MK-5902B-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5902B</t>
+  </si>
+  <si>
+    <t>MK-5902C-1(fan)</t>
+  </si>
+  <si>
+    <t>Acoustic housing fan-1 motor for K-5902C</t>
+  </si>
+  <si>
+    <t>Vent air blower</t>
+  </si>
+  <si>
+    <t>MK-5904_</t>
+  </si>
+  <si>
+    <t>Polymer stabilizer mixer</t>
+  </si>
+  <si>
+    <t>Pellet vibrating classifier</t>
+  </si>
+  <si>
+    <t>Pellet dryer</t>
+  </si>
+  <si>
+    <t>MME-5804(Mat)</t>
+  </si>
+  <si>
+    <t>Solid stabilizer blender</t>
+  </si>
+  <si>
+    <t>MME-5856(Tall)</t>
+  </si>
+  <si>
+    <t>Hoist for handing bags on 3fl extrusion</t>
+  </si>
+  <si>
+    <t>MME-5857(Tall)</t>
+  </si>
+  <si>
+    <t>Hoist for handing bags on 4fl extrusion</t>
+  </si>
+  <si>
+    <t>MME-5863(Tall)</t>
+  </si>
+  <si>
+    <t>Hoist for extrusion  1fl FLoor</t>
+  </si>
+  <si>
+    <t>С-5501 Reflux pump motor</t>
+  </si>
+  <si>
+    <t>Teal metering pump motor</t>
+  </si>
+  <si>
+    <t>Exhaust oil pump</t>
+  </si>
+  <si>
+    <t>Donor feed pump motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grease loading pump motor </t>
+  </si>
+  <si>
+    <t>Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>Pressurization oil pump motor</t>
+  </si>
+  <si>
+    <t>Motor for catalyst metering pump</t>
+  </si>
+  <si>
+    <t>Cylinders jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>Liquid additive loading pump</t>
+  </si>
+  <si>
+    <t>Liquid additive pump</t>
+  </si>
+  <si>
+    <t>MP-5111B</t>
+  </si>
+  <si>
+    <t>Oil loading pump motor</t>
+  </si>
+  <si>
+    <t>Oil header pump motor</t>
+  </si>
+  <si>
+    <t>R-5200 Pump</t>
+  </si>
+  <si>
+    <t>R-5201</t>
+  </si>
+  <si>
+    <t>R-5202</t>
+  </si>
+  <si>
+    <t>V-5201 Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>R-5200 Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>R-5201 Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>R-5202 Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>Centralized Jacket water  pump</t>
+  </si>
+  <si>
+    <t>Propylene feed pump motor</t>
+  </si>
+  <si>
+    <t>C-5301 Reflux pump motor</t>
+  </si>
+  <si>
+    <t>MP-5302B</t>
+  </si>
+  <si>
+    <t>C-5302 Reflux pump motor</t>
+  </si>
+  <si>
+    <t>Rcycle gas compressor lube oil pump motor</t>
+  </si>
+  <si>
+    <t>R-5401 Jacket water circulation pump</t>
+  </si>
+  <si>
+    <t>MP-5502A</t>
+  </si>
+  <si>
+    <t>C-5502 Reflux pumps motor</t>
+  </si>
+  <si>
+    <t>waste oil pump motor</t>
+  </si>
+  <si>
+    <t>Chilled water pump motor</t>
+  </si>
+  <si>
+    <t>Steam condensate pump motor</t>
+  </si>
+  <si>
+    <t>Waste water final sump pump motor</t>
+  </si>
+  <si>
+    <t>PCW Sump pump motor</t>
+  </si>
+  <si>
+    <t>MP-5606B</t>
+  </si>
+  <si>
+    <t>MP-5608A</t>
+  </si>
+  <si>
+    <t>Oil pump motor</t>
+  </si>
+  <si>
+    <t>Nitrogen compressor-lube oil pump</t>
+  </si>
+  <si>
+    <t>Ethylene compressor-lube oil pump</t>
+  </si>
+  <si>
+    <t>MP-5801A</t>
+  </si>
+  <si>
+    <t>Pcw circulation pump</t>
+  </si>
+  <si>
+    <t>Mixer gear reducer-lube oil pump</t>
+  </si>
+  <si>
+    <t>BCW(barrel cooling water)pump</t>
+  </si>
+  <si>
+    <t>Hot oil pump</t>
+  </si>
+  <si>
+    <t>Hydraulic oil pump</t>
+  </si>
+  <si>
+    <t>V-5502 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>V-5501 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>V-5506 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>M-5502 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5802A Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5802B Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5803 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Pellet discharge rotary feeder</t>
+  </si>
+  <si>
+    <t>Z-5904A Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5904B Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5901C Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5901D Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5902A Rotary Feeder</t>
+  </si>
+  <si>
+    <t>Z-5902B Rotary Feeder</t>
+  </si>
+  <si>
+    <t>M-5904B Rotary Feeder</t>
+  </si>
+  <si>
+    <t>F-5901 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>F-5904 Rotary Feeder</t>
+  </si>
+  <si>
+    <t>MW-5804A</t>
+  </si>
+  <si>
+    <t>Stb metering feeder agitator</t>
+  </si>
+  <si>
+    <t>MW-5804B</t>
+  </si>
+  <si>
+    <t>Solid stabilizer metering feeder</t>
+  </si>
+  <si>
+    <t>MW-5805A</t>
+  </si>
+  <si>
+    <t>MW-5805B</t>
+  </si>
+  <si>
+    <t>Ldpe metering feeder</t>
+  </si>
+  <si>
+    <t>MP-5704-5</t>
+  </si>
+  <si>
+    <t>MME-5104 (Tall)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9951,19 +10938,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -10018,7 +10992,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -10106,6 +11080,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -10116,7 +11101,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10279,7 +11264,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10287,35 +11281,30 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10334,6 +11323,726 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1505</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B689963F-6750-40B4-BF35-2D01EE526224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="7434943"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1483</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AFAB2D8-3DE6-4D12-BB64-F7188342AF70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7362825" y="2952750"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1513</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ED0E2E2-2E1B-4287-BCF4-8E20E8734876}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="8953500"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1513</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BDAE6A6-A986-4406-A577-DC3178690558}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="8953500"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1513</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E018A0FD-E2DC-404A-AE51-C2B30F7F1B9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="8953500"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1513</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F77B1C-C0BA-45DD-B88E-AA342F8594A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="8953500"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1513</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E3EE3A-62AA-4F5C-B65F-378C21D697D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="8953500"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1477</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4D5A89A-3145-45F8-8B44-DDD26706943E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="1752600"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1498</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58F39C35-C988-441D-B0B2-53BE34CC0133}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="5953125"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1499</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EBF0758-679A-44E3-9CDF-48C18D84036B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5943600" y="6153150"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1506</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A42AFC40-167F-4EC1-81D2-D258EBD69BB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="7634968"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1506</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC698B89-C85B-4352-B440-3E81E2A35B66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="7634968"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1474</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6163E8F3-4746-4794-882F-44A891A75016}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4648200" y="1152525"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10633,7 +12342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F1484"/>
+  <dimension ref="A1:F1624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -35227,1211 +36936,3932 @@
       <c r="A1393" s="49" t="s">
         <v>3076</v>
       </c>
-      <c r="C1393" s="57" t="s">
-        <v>3168</v>
-      </c>
-      <c r="D1393" s="57" t="s">
+      <c r="C1393" s="55" t="s">
+        <v>3157</v>
+      </c>
+      <c r="D1393" s="55" t="s">
         <v>1351</v>
       </c>
-      <c r="E1393" s="66">
+      <c r="E1393" s="62">
         <v>5.5</v>
       </c>
-      <c r="F1393" s="57"/>
+      <c r="F1393" s="55"/>
     </row>
     <row r="1394" spans="1:6" ht="15.75">
       <c r="A1394" s="49" t="s">
         <v>3077</v>
       </c>
-      <c r="C1394" s="57" t="s">
-        <v>3169</v>
-      </c>
-      <c r="D1394" s="57" t="s">
-        <v>3186</v>
-      </c>
-      <c r="E1394" s="66">
+      <c r="C1394" s="55" t="s">
+        <v>3158</v>
+      </c>
+      <c r="D1394" s="55" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E1394" s="62">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F1394" s="57" t="s">
-        <v>3204</v>
+      <c r="F1394" s="55" t="s">
+        <v>3191</v>
       </c>
     </row>
     <row r="1395" spans="1:6" ht="15.75">
       <c r="A1395" s="49" t="s">
         <v>3078</v>
       </c>
-      <c r="C1395" s="57" t="s">
-        <v>3170</v>
-      </c>
-      <c r="D1395" s="57" t="s">
+      <c r="C1395" s="55" t="s">
+        <v>3159</v>
+      </c>
+      <c r="D1395" s="55" t="s">
         <v>1255</v>
       </c>
-      <c r="E1395" s="64">
+      <c r="E1395" s="61">
         <v>37</v>
       </c>
-      <c r="F1395" s="57" t="s">
-        <v>3205</v>
+      <c r="F1395" s="55" t="s">
+        <v>3192</v>
       </c>
     </row>
     <row r="1396" spans="1:6" ht="15.75">
       <c r="A1396" s="49" t="s">
         <v>3079</v>
       </c>
-      <c r="C1396" s="58" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1396" s="57" t="s">
-        <v>3187</v>
-      </c>
-      <c r="E1396" s="64">
+      <c r="C1396" s="56" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1396" s="55" t="s">
+        <v>3175</v>
+      </c>
+      <c r="E1396" s="61">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F1396" s="57" t="s">
-        <v>3204</v>
+      <c r="F1396" s="55" t="s">
+        <v>3191</v>
       </c>
     </row>
     <row r="1397" spans="1:6" ht="15.75">
       <c r="A1397" s="49" t="s">
         <v>3080</v>
       </c>
-      <c r="C1397" s="58" t="s">
-        <v>3172</v>
-      </c>
-      <c r="D1397" s="57" t="s">
-        <v>3188</v>
-      </c>
-      <c r="E1397" s="66">
+      <c r="C1397" s="56" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D1397" s="55" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E1397" s="62">
         <v>120</v>
       </c>
-      <c r="F1397" s="58"/>
+      <c r="F1397" s="56"/>
     </row>
     <row r="1398" spans="1:6" ht="15.75">
       <c r="A1398" s="49" t="s">
         <v>3081</v>
       </c>
-      <c r="C1398" s="58" t="s">
-        <v>3173</v>
-      </c>
-      <c r="D1398" s="57" t="s">
-        <v>3188</v>
-      </c>
-      <c r="E1398" s="64">
+      <c r="C1398" s="56" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D1398" s="55" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E1398" s="61">
         <v>110</v>
       </c>
-      <c r="F1398" s="57" t="s">
-        <v>3206</v>
+      <c r="F1398" s="55" t="s">
+        <v>3193</v>
       </c>
     </row>
     <row r="1399" spans="1:6" ht="15.75">
       <c r="A1399" s="49" t="s">
         <v>3082</v>
       </c>
-      <c r="C1399" s="58" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1399" s="57" t="s">
-        <v>3189</v>
-      </c>
-      <c r="E1399" s="66">
+      <c r="C1399" s="56" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1399" s="55" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E1399" s="62">
         <v>110</v>
       </c>
-      <c r="F1399" s="57" t="s">
-        <v>3206</v>
+      <c r="F1399" s="55" t="s">
+        <v>3193</v>
       </c>
     </row>
     <row r="1400" spans="1:6" ht="15.75">
       <c r="A1400" s="49" t="s">
         <v>3083</v>
       </c>
-      <c r="C1400" s="59" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1400" s="59" t="s">
-        <v>3190</v>
-      </c>
-      <c r="E1400" s="64">
+      <c r="C1400" s="57" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1400" s="57" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1400" s="61">
         <v>45</v>
       </c>
-      <c r="F1400" s="59"/>
+      <c r="F1400" s="57"/>
     </row>
     <row r="1401" spans="1:6" ht="15.75">
       <c r="A1401" s="49" t="s">
         <v>3084</v>
       </c>
-      <c r="C1401" s="57" t="s">
-        <v>3174</v>
-      </c>
-      <c r="D1401" s="57" t="s">
+      <c r="C1401" s="55" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D1401" s="55" t="s">
         <v>1197</v>
       </c>
-      <c r="E1401" s="66">
+      <c r="E1401" s="62">
         <v>30</v>
       </c>
-      <c r="F1401" s="57" t="s">
-        <v>3207</v>
+      <c r="F1401" s="55" t="s">
+        <v>3194</v>
       </c>
     </row>
     <row r="1402" spans="1:6" ht="15.75">
       <c r="A1402" s="50" t="s">
         <v>3085</v>
       </c>
-      <c r="C1402" s="60" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1402" s="60" t="s">
-        <v>3191</v>
-      </c>
-      <c r="E1402" s="64">
+      <c r="C1402" s="58" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1402" s="58" t="s">
+        <v>3179</v>
+      </c>
+      <c r="E1402" s="61">
         <v>11</v>
       </c>
-      <c r="F1402" s="60" t="s">
-        <v>3208</v>
+      <c r="F1402" s="58" t="s">
+        <v>3195</v>
       </c>
     </row>
     <row r="1403" spans="1:6" ht="15.75">
       <c r="A1403" s="49" t="s">
         <v>3086</v>
       </c>
-      <c r="C1403" s="57" t="s">
-        <v>3175</v>
-      </c>
-      <c r="D1403" s="57" t="s">
-        <v>3192</v>
-      </c>
-      <c r="E1403" s="64"/>
-      <c r="F1403" s="57"/>
+      <c r="C1403" s="55" t="s">
+        <v>3164</v>
+      </c>
+      <c r="D1403" s="55" t="s">
+        <v>3180</v>
+      </c>
+      <c r="E1403" s="61"/>
+      <c r="F1403" s="55"/>
     </row>
     <row r="1404" spans="1:6" ht="15.75">
       <c r="A1404" s="49" t="s">
         <v>3087</v>
       </c>
-      <c r="C1404" s="57" t="s">
-        <v>3176</v>
-      </c>
-      <c r="D1404" s="57" t="s">
+      <c r="C1404" s="55" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D1404" s="55" t="s">
         <v>1120</v>
       </c>
-      <c r="E1404" s="64"/>
-      <c r="F1404" s="57"/>
+      <c r="E1404" s="61"/>
+      <c r="F1404" s="55"/>
     </row>
     <row r="1405" spans="1:6" ht="15.75">
       <c r="A1405" s="51" t="s">
         <v>3088</v>
       </c>
-      <c r="C1405" s="57" t="s">
-        <v>3176</v>
-      </c>
-      <c r="D1405" s="57" t="s">
+      <c r="C1405" s="55" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D1405" s="55" t="s">
         <v>1171</v>
       </c>
-      <c r="E1405" s="64"/>
-      <c r="F1405" s="57"/>
+      <c r="E1405" s="61"/>
+      <c r="F1405" s="55"/>
     </row>
     <row r="1406" spans="1:6" ht="15.75">
       <c r="A1406" s="49" t="s">
         <v>3089</v>
       </c>
-      <c r="C1406" s="58" t="s">
-        <v>3177</v>
-      </c>
-      <c r="D1406" s="58" t="s">
-        <v>3193</v>
-      </c>
-      <c r="E1406" s="66">
+      <c r="C1406" s="56" t="s">
+        <v>3166</v>
+      </c>
+      <c r="D1406" s="56" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E1406" s="62">
         <v>5.5</v>
       </c>
-      <c r="F1406" s="58"/>
+      <c r="F1406" s="56"/>
     </row>
     <row r="1407" spans="1:6" ht="15.75">
       <c r="A1407" s="50" t="s">
         <v>3090</v>
       </c>
-      <c r="C1407" s="61" t="s">
-        <v>3178</v>
-      </c>
-      <c r="D1407" s="61" t="s">
-        <v>3194</v>
-      </c>
-      <c r="E1407" s="67"/>
-      <c r="F1407" s="61"/>
+      <c r="C1407" s="59" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D1407" s="59" t="s">
+        <v>3182</v>
+      </c>
+      <c r="E1407" s="63"/>
+      <c r="F1407" s="59"/>
     </row>
     <row r="1408" spans="1:6" ht="15.75">
       <c r="A1408" s="49" t="s">
         <v>3091</v>
       </c>
-      <c r="C1408" s="61" t="s">
-        <v>3177</v>
-      </c>
-      <c r="D1408" s="64" t="s">
-        <v>3193</v>
-      </c>
-      <c r="E1408" s="64">
+      <c r="C1408" s="59" t="s">
+        <v>3166</v>
+      </c>
+      <c r="D1408" s="61" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E1408" s="61">
         <v>37</v>
       </c>
-      <c r="F1408" s="64"/>
+      <c r="F1408" s="61"/>
     </row>
     <row r="1409" spans="1:6" ht="15.75">
       <c r="A1409" s="49" t="s">
         <v>3092</v>
       </c>
-      <c r="C1409" s="58" t="s">
-        <v>3179</v>
-      </c>
-      <c r="D1409" s="57" t="s">
-        <v>3193</v>
-      </c>
-      <c r="E1409" s="64">
+      <c r="C1409" s="56" t="s">
+        <v>3168</v>
+      </c>
+      <c r="D1409" s="55" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E1409" s="61">
         <v>15</v>
       </c>
-      <c r="F1409" s="57" t="s">
-        <v>3204</v>
+      <c r="F1409" s="55" t="s">
+        <v>3191</v>
       </c>
     </row>
     <row r="1410" spans="1:6" ht="15.75">
       <c r="A1410" s="52" t="s">
         <v>3093</v>
       </c>
-      <c r="C1410" s="61" t="s">
-        <v>3180</v>
-      </c>
-      <c r="D1410" s="64" t="s">
-        <v>3190</v>
-      </c>
-      <c r="E1410" s="64">
+      <c r="C1410" s="59" t="s">
+        <v>3169</v>
+      </c>
+      <c r="D1410" s="61" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1410" s="61">
         <v>15</v>
       </c>
-      <c r="F1410" s="64" t="s">
-        <v>3204</v>
+      <c r="F1410" s="61" t="s">
+        <v>3191</v>
       </c>
     </row>
     <row r="1411" spans="1:6" ht="15.75">
       <c r="A1411" s="49" t="s">
         <v>3094</v>
       </c>
-      <c r="C1411" s="58" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1411" s="58" t="s">
+      <c r="C1411" s="56" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1411" s="56" t="s">
         <v>1201</v>
       </c>
-      <c r="E1411" s="64">
+      <c r="E1411" s="61">
         <v>45</v>
       </c>
-      <c r="F1411" s="58"/>
+      <c r="F1411" s="56"/>
     </row>
     <row r="1412" spans="1:6" ht="15.75">
       <c r="A1412" s="49" t="s">
         <v>3095</v>
       </c>
-      <c r="C1412" s="58" t="s">
-        <v>3175</v>
-      </c>
-      <c r="D1412" s="64" t="s">
-        <v>3195</v>
-      </c>
-      <c r="E1412" s="64">
+      <c r="C1412" s="56" t="s">
+        <v>3164</v>
+      </c>
+      <c r="D1412" s="61" t="s">
+        <v>3183</v>
+      </c>
+      <c r="E1412" s="61">
         <v>30</v>
       </c>
-      <c r="F1412" s="64"/>
+      <c r="F1412" s="61"/>
     </row>
     <row r="1413" spans="1:6" ht="15.75">
       <c r="A1413" s="49" t="s">
         <v>3096</v>
       </c>
-      <c r="C1413" s="58" t="s">
-        <v>3174</v>
-      </c>
-      <c r="D1413" s="58" t="s">
+      <c r="C1413" s="56" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D1413" s="56" t="s">
         <v>1415</v>
       </c>
-      <c r="E1413" s="67">
+      <c r="E1413" s="63">
         <v>37</v>
       </c>
-      <c r="F1413" s="58"/>
+      <c r="F1413" s="56"/>
     </row>
     <row r="1414" spans="1:6" ht="15.75">
       <c r="A1414" s="49" t="s">
         <v>3097</v>
       </c>
-      <c r="C1414" s="57" t="s">
-        <v>3181</v>
-      </c>
-      <c r="D1414" s="57" t="s">
-        <v>3196</v>
-      </c>
-      <c r="E1414" s="66">
+      <c r="C1414" s="55" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1414" s="55" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1414" s="62">
         <v>37</v>
       </c>
-      <c r="F1414" s="58"/>
+      <c r="F1414" s="56"/>
     </row>
     <row r="1415" spans="1:6" ht="15.75">
       <c r="A1415" s="49" t="s">
         <v>3098</v>
       </c>
-      <c r="C1415" s="57" t="s">
-        <v>3175</v>
-      </c>
-      <c r="D1415" s="57" t="s">
+      <c r="C1415" s="55" t="s">
+        <v>3164</v>
+      </c>
+      <c r="D1415" s="55" t="s">
         <v>1174</v>
       </c>
-      <c r="E1415" s="64">
+      <c r="E1415" s="61">
         <v>11</v>
       </c>
-      <c r="F1415" s="58"/>
+      <c r="F1415" s="56"/>
     </row>
     <row r="1416" spans="1:6" ht="15.75">
       <c r="A1416" s="49" t="s">
         <v>3099</v>
       </c>
-      <c r="C1416" s="57" t="s">
-        <v>3181</v>
-      </c>
-      <c r="D1416" s="57" t="s">
-        <v>3197</v>
-      </c>
-      <c r="E1416" s="64">
+      <c r="C1416" s="55" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1416" s="55" t="s">
+        <v>3185</v>
+      </c>
+      <c r="E1416" s="61">
         <v>22</v>
       </c>
-      <c r="F1416" s="57" t="s">
-        <v>3205</v>
+      <c r="F1416" s="55" t="s">
+        <v>3192</v>
       </c>
     </row>
     <row r="1417" spans="1:6" ht="15.75">
       <c r="A1417" s="49" t="s">
         <v>3100</v>
       </c>
-      <c r="C1417" s="57" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1417" s="57" t="s">
-        <v>3198</v>
-      </c>
-      <c r="E1417" s="64">
+      <c r="C1417" s="55" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D1417" s="55" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E1417" s="61">
         <v>22</v>
       </c>
-      <c r="F1417" s="58"/>
+      <c r="F1417" s="56"/>
     </row>
     <row r="1418" spans="1:6" ht="15.75">
       <c r="A1418" s="50" t="s">
         <v>3101</v>
       </c>
-      <c r="C1418" s="60" t="s">
-        <v>3178</v>
-      </c>
-      <c r="D1418" s="60"/>
-      <c r="E1418" s="66"/>
-      <c r="F1418" s="61"/>
+      <c r="C1418" s="58" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D1418" s="58"/>
+      <c r="E1418" s="62"/>
+      <c r="F1418" s="59"/>
     </row>
     <row r="1419" spans="1:6" ht="15.75">
       <c r="A1419" s="49" t="s">
         <v>3102</v>
       </c>
-      <c r="C1419" s="57" t="s">
-        <v>3182</v>
-      </c>
-      <c r="D1419" s="57"/>
-      <c r="E1419" s="66">
+      <c r="C1419" s="55" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1419" s="55"/>
+      <c r="E1419" s="62">
         <v>110</v>
       </c>
-      <c r="F1419" s="58"/>
+      <c r="F1419" s="56"/>
     </row>
     <row r="1420" spans="1:6" ht="15.75">
       <c r="A1420" s="49" t="s">
         <v>3103</v>
       </c>
-      <c r="C1420" s="57" t="s">
-        <v>3182</v>
-      </c>
-      <c r="D1420" s="57" t="s">
-        <v>3199</v>
-      </c>
-      <c r="E1420" s="66">
+      <c r="C1420" s="55" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D1420" s="55" t="s">
+        <v>3187</v>
+      </c>
+      <c r="E1420" s="62">
         <v>110</v>
       </c>
-      <c r="F1420" s="58"/>
+      <c r="F1420" s="56"/>
     </row>
     <row r="1421" spans="1:6" ht="15.75">
       <c r="A1421" s="50" t="s">
         <v>3104</v>
       </c>
-      <c r="C1421" s="57"/>
-      <c r="D1421" s="57"/>
-      <c r="E1421" s="64">
+      <c r="C1421" s="55"/>
+      <c r="D1421" s="55"/>
+      <c r="E1421" s="61">
         <v>4200</v>
       </c>
-      <c r="F1421" s="58"/>
+      <c r="F1421" s="56"/>
     </row>
     <row r="1422" spans="1:6" ht="15.75">
       <c r="A1422" s="50" t="s">
         <v>3105</v>
       </c>
-      <c r="C1422" s="57" t="s">
-        <v>3179</v>
-      </c>
-      <c r="D1422" s="57" t="s">
-        <v>3193</v>
-      </c>
-      <c r="E1422" s="64">
+      <c r="C1422" s="55" t="s">
+        <v>3168</v>
+      </c>
+      <c r="D1422" s="55" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E1422" s="61">
         <v>15</v>
       </c>
-      <c r="F1422" s="58"/>
+      <c r="F1422" s="56"/>
     </row>
     <row r="1423" spans="1:6" ht="15.75">
       <c r="A1423" s="50" t="s">
         <v>3106</v>
       </c>
-      <c r="C1423" s="57" t="s">
-        <v>3177</v>
-      </c>
-      <c r="D1423" s="57" t="s">
-        <v>3190</v>
-      </c>
-      <c r="E1423" s="64">
+      <c r="C1423" s="55" t="s">
+        <v>3166</v>
+      </c>
+      <c r="D1423" s="55" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1423" s="61">
         <v>15</v>
       </c>
-      <c r="F1423" s="58"/>
+      <c r="F1423" s="56"/>
     </row>
     <row r="1424" spans="1:6" ht="15.75">
       <c r="A1424" s="50" t="s">
         <v>3107</v>
       </c>
-      <c r="C1424" s="57" t="s">
-        <v>3173</v>
-      </c>
-      <c r="D1424" s="57" t="s">
-        <v>3200</v>
-      </c>
-      <c r="E1424" s="64">
+      <c r="C1424" s="55" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D1424" s="55" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E1424" s="61">
         <v>1</v>
       </c>
-      <c r="F1424" s="58"/>
+      <c r="F1424" s="56"/>
     </row>
     <row r="1425" spans="1:6" ht="15.75">
       <c r="A1425" s="53" t="s">
         <v>3108</v>
       </c>
-      <c r="C1425" s="57" t="s">
-        <v>3179</v>
-      </c>
-      <c r="D1425" s="57" t="s">
-        <v>3190</v>
-      </c>
-      <c r="E1425" s="64">
+      <c r="C1425" s="55" t="s">
+        <v>3168</v>
+      </c>
+      <c r="D1425" s="55" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1425" s="61">
         <v>30</v>
       </c>
-      <c r="F1425" s="58"/>
+      <c r="F1425" s="56"/>
     </row>
     <row r="1426" spans="1:6" ht="15.75">
       <c r="A1426" s="53" t="s">
         <v>3109</v>
       </c>
-      <c r="C1426" s="57"/>
-      <c r="D1426" s="57"/>
-      <c r="E1426" s="64">
+      <c r="C1426" s="55"/>
+      <c r="D1426" s="55"/>
+      <c r="E1426" s="61">
         <v>9</v>
       </c>
-      <c r="F1426" s="58"/>
+      <c r="F1426" s="56"/>
     </row>
     <row r="1427" spans="1:6" ht="15.75">
       <c r="A1427" s="53" t="s">
         <v>3110</v>
       </c>
-      <c r="C1427" s="62" t="s">
-        <v>3183</v>
-      </c>
-      <c r="D1427" s="57"/>
-      <c r="E1427" s="64">
+      <c r="C1427" s="60" t="s">
+        <v>3172</v>
+      </c>
+      <c r="D1427" s="55"/>
+      <c r="E1427" s="61">
         <v>9</v>
       </c>
-      <c r="F1427" s="58"/>
+      <c r="F1427" s="56"/>
     </row>
     <row r="1428" spans="1:6" ht="15.75">
       <c r="A1428" s="53" t="s">
         <v>3111</v>
       </c>
-      <c r="C1428" s="57"/>
-      <c r="D1428" s="57"/>
-      <c r="E1428" s="64">
+      <c r="C1428" s="55"/>
+      <c r="D1428" s="55"/>
+      <c r="E1428" s="61">
         <v>9</v>
       </c>
-      <c r="F1428" s="58"/>
+      <c r="F1428" s="56"/>
     </row>
     <row r="1429" spans="1:6" ht="15.75">
       <c r="A1429" s="53" t="s">
         <v>3112</v>
       </c>
-      <c r="C1429" s="57"/>
-      <c r="D1429" s="57"/>
-      <c r="E1429" s="64">
+      <c r="C1429" s="55"/>
+      <c r="D1429" s="55"/>
+      <c r="E1429" s="61">
         <v>63.76</v>
       </c>
-      <c r="F1429" s="58"/>
+      <c r="F1429" s="56"/>
     </row>
     <row r="1430" spans="1:6" ht="15.75">
       <c r="A1430" s="53" t="s">
         <v>3113</v>
       </c>
-      <c r="C1430" s="57"/>
-      <c r="D1430" s="57"/>
-      <c r="E1430" s="64">
+      <c r="C1430" s="55"/>
+      <c r="D1430" s="55"/>
+      <c r="E1430" s="61">
         <v>106.24</v>
       </c>
-      <c r="F1430" s="58"/>
+      <c r="F1430" s="56"/>
     </row>
     <row r="1431" spans="1:6" ht="15.75">
       <c r="A1431" s="53" t="s">
         <v>3114</v>
       </c>
-      <c r="C1431" s="57"/>
-      <c r="D1431" s="57"/>
-      <c r="E1431" s="64">
+      <c r="C1431" s="55"/>
+      <c r="D1431" s="55"/>
+      <c r="E1431" s="61">
         <v>1.5</v>
       </c>
-      <c r="F1431" s="58"/>
+      <c r="F1431" s="56"/>
     </row>
     <row r="1432" spans="1:6" ht="15.75">
       <c r="A1432" s="53" t="s">
         <v>3115</v>
       </c>
-      <c r="C1432" s="57"/>
-      <c r="D1432" s="57"/>
-      <c r="E1432" s="64">
+      <c r="C1432" s="55"/>
+      <c r="D1432" s="55"/>
+      <c r="E1432" s="61">
         <v>7.5</v>
       </c>
-      <c r="F1432" s="58"/>
+      <c r="F1432" s="56"/>
     </row>
     <row r="1433" spans="1:6" ht="15.75">
       <c r="A1433" s="53" t="s">
         <v>3116</v>
       </c>
-      <c r="C1433" s="57"/>
-      <c r="D1433" s="57"/>
-      <c r="E1433" s="64">
+      <c r="C1433" s="55"/>
+      <c r="D1433" s="55"/>
+      <c r="E1433" s="61">
         <v>37</v>
       </c>
-      <c r="F1433" s="58"/>
+      <c r="F1433" s="56"/>
     </row>
     <row r="1434" spans="1:6" ht="15.75">
       <c r="A1434" s="53" t="s">
         <v>3117</v>
       </c>
-      <c r="C1434" s="57"/>
-      <c r="D1434" s="57"/>
-      <c r="E1434" s="64">
+      <c r="C1434" s="55"/>
+      <c r="D1434" s="55"/>
+      <c r="E1434" s="61">
         <v>37</v>
       </c>
-      <c r="F1434" s="58"/>
+      <c r="F1434" s="56"/>
     </row>
     <row r="1435" spans="1:6" ht="15.75">
       <c r="A1435" s="53" t="s">
         <v>3118</v>
       </c>
-      <c r="C1435" s="57"/>
-      <c r="D1435" s="57"/>
-      <c r="E1435" s="64">
+      <c r="C1435" s="55"/>
+      <c r="D1435" s="55"/>
+      <c r="E1435" s="61">
         <v>12.3</v>
       </c>
-      <c r="F1435" s="58"/>
+      <c r="F1435" s="56"/>
     </row>
     <row r="1436" spans="1:6" ht="15.75">
       <c r="A1436" s="53" t="s">
         <v>3119</v>
       </c>
-      <c r="C1436" s="57"/>
-      <c r="D1436" s="57"/>
-      <c r="E1436" s="64">
+      <c r="C1436" s="55"/>
+      <c r="D1436" s="55"/>
+      <c r="E1436" s="61">
         <v>0.74</v>
       </c>
-      <c r="F1436" s="58"/>
+      <c r="F1436" s="56"/>
     </row>
     <row r="1437" spans="1:6" ht="15.75">
       <c r="A1437" s="53" t="s">
         <v>3120</v>
       </c>
-      <c r="C1437" s="57"/>
-      <c r="D1437" s="57"/>
-      <c r="E1437" s="64">
+      <c r="C1437" s="55"/>
+      <c r="D1437" s="55"/>
+      <c r="E1437" s="61">
         <v>110</v>
       </c>
-      <c r="F1437" s="58"/>
+      <c r="F1437" s="56"/>
     </row>
     <row r="1438" spans="1:6" ht="15.75">
       <c r="A1438" s="53" t="s">
         <v>3121</v>
       </c>
-      <c r="C1438" s="57"/>
-      <c r="D1438" s="57"/>
-      <c r="E1438" s="64">
+      <c r="C1438" s="55"/>
+      <c r="D1438" s="55"/>
+      <c r="E1438" s="61">
         <v>9</v>
       </c>
-      <c r="F1438" s="58"/>
+      <c r="F1438" s="56"/>
     </row>
     <row r="1439" spans="1:6" ht="15.75">
       <c r="A1439" s="53" t="s">
         <v>3122</v>
       </c>
-      <c r="C1439" s="57"/>
-      <c r="D1439" s="57"/>
-      <c r="E1439" s="64">
+      <c r="C1439" s="55"/>
+      <c r="D1439" s="55"/>
+      <c r="E1439" s="61">
         <v>9</v>
       </c>
-      <c r="F1439" s="58"/>
+      <c r="F1439" s="56"/>
     </row>
     <row r="1440" spans="1:6" ht="15.75">
       <c r="A1440" s="53" t="s">
         <v>3123</v>
       </c>
-      <c r="C1440" s="57"/>
-      <c r="D1440" s="57"/>
-      <c r="E1440" s="64">
+      <c r="C1440" s="55"/>
+      <c r="D1440" s="55"/>
+      <c r="E1440" s="61">
         <v>9</v>
       </c>
-      <c r="F1440" s="58"/>
+      <c r="F1440" s="56"/>
     </row>
     <row r="1441" spans="1:6" ht="15.75">
       <c r="A1441" s="53" t="s">
         <v>3124</v>
       </c>
-      <c r="C1441" s="57"/>
-      <c r="D1441" s="57"/>
-      <c r="E1441" s="64">
+      <c r="C1441" s="55"/>
+      <c r="D1441" s="55"/>
+      <c r="E1441" s="61">
         <v>63.76</v>
       </c>
-      <c r="F1441" s="58"/>
+      <c r="F1441" s="56"/>
     </row>
     <row r="1442" spans="1:6" ht="15.75">
       <c r="A1442" s="53" t="s">
         <v>3125</v>
       </c>
-      <c r="C1442" s="57" t="s">
-        <v>3172</v>
-      </c>
-      <c r="D1442" s="57" t="s">
-        <v>3189</v>
-      </c>
-      <c r="E1442" s="64">
+      <c r="C1442" s="55" t="s">
+        <v>3161</v>
+      </c>
+      <c r="D1442" s="55" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E1442" s="61">
         <v>106.24</v>
       </c>
-      <c r="F1442" s="58"/>
+      <c r="F1442" s="56"/>
     </row>
     <row r="1443" spans="1:6" ht="15.75">
       <c r="A1443" s="53" t="s">
         <v>3126</v>
       </c>
-      <c r="C1443" s="57"/>
-      <c r="D1443" s="57"/>
-      <c r="E1443" s="64">
+      <c r="C1443" s="55"/>
+      <c r="D1443" s="55"/>
+      <c r="E1443" s="61">
         <v>1.5</v>
       </c>
-      <c r="F1443" s="58"/>
+      <c r="F1443" s="56"/>
     </row>
     <row r="1444" spans="1:6" ht="15.75">
       <c r="A1444" s="54" t="s">
         <v>3127</v>
       </c>
-      <c r="C1444" s="57"/>
-      <c r="D1444" s="57"/>
-      <c r="E1444" s="64">
+      <c r="C1444" s="55"/>
+      <c r="D1444" s="55"/>
+      <c r="E1444" s="61">
         <v>7.5</v>
       </c>
-      <c r="F1444" s="58"/>
+      <c r="F1444" s="56"/>
     </row>
     <row r="1445" spans="1:6" ht="15.75">
       <c r="A1445" s="54" t="s">
         <v>3128</v>
       </c>
-      <c r="C1445" s="57"/>
-      <c r="D1445" s="57"/>
-      <c r="E1445" s="64">
+      <c r="C1445" s="55"/>
+      <c r="D1445" s="55"/>
+      <c r="E1445" s="61">
         <v>37</v>
       </c>
-      <c r="F1445" s="58"/>
+      <c r="F1445" s="56"/>
     </row>
     <row r="1446" spans="1:6" ht="15.75">
       <c r="A1446" s="54" t="s">
         <v>3129</v>
       </c>
-      <c r="C1446" s="57"/>
-      <c r="D1446" s="57"/>
-      <c r="E1446" s="64">
+      <c r="C1446" s="55"/>
+      <c r="D1446" s="55"/>
+      <c r="E1446" s="61">
         <v>37</v>
       </c>
-      <c r="F1446" s="58"/>
+      <c r="F1446" s="56"/>
     </row>
     <row r="1447" spans="1:6" ht="15.75">
       <c r="A1447" s="54" t="s">
         <v>3130</v>
       </c>
-      <c r="C1447" s="57"/>
-      <c r="D1447" s="57"/>
-      <c r="E1447" s="64">
+      <c r="C1447" s="55"/>
+      <c r="D1447" s="55"/>
+      <c r="E1447" s="61">
         <v>12.3</v>
       </c>
-      <c r="F1447" s="58"/>
+      <c r="F1447" s="56"/>
     </row>
     <row r="1448" spans="1:6" ht="15.75">
       <c r="A1448" s="53" t="s">
         <v>3131</v>
       </c>
-      <c r="C1448" s="57"/>
-      <c r="D1448" s="57"/>
-      <c r="E1448" s="64">
+      <c r="C1448" s="55"/>
+      <c r="D1448" s="55"/>
+      <c r="E1448" s="61">
         <v>0.74</v>
       </c>
-      <c r="F1448" s="58"/>
+      <c r="F1448" s="56"/>
     </row>
     <row r="1449" spans="1:6" ht="15.75">
       <c r="A1449" s="54" t="s">
         <v>3132</v>
       </c>
-      <c r="C1449" s="57"/>
-      <c r="D1449" s="57"/>
-      <c r="E1449" s="64">
+      <c r="C1449" s="55"/>
+      <c r="D1449" s="55"/>
+      <c r="E1449" s="61">
         <v>110</v>
       </c>
-      <c r="F1449" s="58"/>
+      <c r="F1449" s="56"/>
     </row>
     <row r="1450" spans="1:6" ht="15.75">
       <c r="A1450" s="53" t="s">
         <v>3133</v>
       </c>
-      <c r="C1450" s="57"/>
-      <c r="D1450" s="57"/>
-      <c r="E1450" s="64">
+      <c r="C1450" s="55"/>
+      <c r="D1450" s="55"/>
+      <c r="E1450" s="61">
         <v>9</v>
       </c>
-      <c r="F1450" s="58"/>
+      <c r="F1450" s="56"/>
     </row>
     <row r="1451" spans="1:6" ht="15.75">
       <c r="A1451" s="53" t="s">
         <v>3134</v>
       </c>
-      <c r="C1451" s="57"/>
-      <c r="D1451" s="57"/>
-      <c r="E1451" s="64">
+      <c r="C1451" s="55"/>
+      <c r="D1451" s="55"/>
+      <c r="E1451" s="61">
         <v>9</v>
       </c>
-      <c r="F1451" s="58"/>
+      <c r="F1451" s="56"/>
     </row>
     <row r="1452" spans="1:6" ht="15.75">
       <c r="A1452" s="53" t="s">
         <v>3135</v>
       </c>
-      <c r="C1452" s="57"/>
-      <c r="D1452" s="57"/>
-      <c r="E1452" s="64">
+      <c r="C1452" s="55"/>
+      <c r="D1452" s="55"/>
+      <c r="E1452" s="61">
         <v>9</v>
       </c>
-      <c r="F1452" s="58"/>
+      <c r="F1452" s="56"/>
     </row>
     <row r="1453" spans="1:6" ht="15.75">
       <c r="A1453" s="53" t="s">
         <v>3136</v>
       </c>
-      <c r="C1453" s="57"/>
-      <c r="D1453" s="57"/>
-      <c r="E1453" s="64">
+      <c r="C1453" s="55"/>
+      <c r="D1453" s="55"/>
+      <c r="E1453" s="61">
         <v>63.76</v>
       </c>
-      <c r="F1453" s="58"/>
+      <c r="F1453" s="56"/>
     </row>
     <row r="1454" spans="1:6" ht="15.75">
       <c r="A1454" s="53" t="s">
         <v>3137</v>
       </c>
-      <c r="C1454" s="57" t="s">
-        <v>3181</v>
-      </c>
-      <c r="D1454" s="57" t="s">
-        <v>3199</v>
-      </c>
-      <c r="E1454" s="64">
+      <c r="C1454" s="55" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D1454" s="55" t="s">
+        <v>3187</v>
+      </c>
+      <c r="E1454" s="61">
         <v>106.24</v>
       </c>
-      <c r="F1454" s="58"/>
+      <c r="F1454" s="56"/>
     </row>
     <row r="1455" spans="1:6" ht="15.75">
       <c r="A1455" s="53" t="s">
         <v>3138</v>
       </c>
-      <c r="C1455" s="57"/>
-      <c r="D1455" s="57"/>
-      <c r="E1455" s="64">
+      <c r="C1455" s="55"/>
+      <c r="D1455" s="55"/>
+      <c r="E1455" s="61">
         <v>1.5</v>
       </c>
-      <c r="F1455" s="58"/>
+      <c r="F1455" s="56"/>
     </row>
     <row r="1456" spans="1:6" ht="15.75">
       <c r="A1456" s="53" t="s">
         <v>3139</v>
       </c>
-      <c r="C1456" s="57"/>
-      <c r="D1456" s="57"/>
-      <c r="E1456" s="64">
+      <c r="C1456" s="55"/>
+      <c r="D1456" s="55"/>
+      <c r="E1456" s="61">
         <v>7.5</v>
       </c>
-      <c r="F1456" s="58"/>
+      <c r="F1456" s="56"/>
     </row>
     <row r="1457" spans="1:6" ht="15.75">
       <c r="A1457" s="53" t="s">
         <v>3140</v>
       </c>
-      <c r="C1457" s="57"/>
-      <c r="D1457" s="57"/>
-      <c r="E1457" s="64">
+      <c r="C1457" s="55"/>
+      <c r="D1457" s="55"/>
+      <c r="E1457" s="61">
         <v>37</v>
       </c>
-      <c r="F1457" s="58"/>
+      <c r="F1457" s="56"/>
     </row>
     <row r="1458" spans="1:6" ht="15.75">
       <c r="A1458" s="53" t="s">
         <v>3141</v>
       </c>
-      <c r="C1458" s="57"/>
-      <c r="D1458" s="57"/>
-      <c r="E1458" s="64">
+      <c r="C1458" s="55"/>
+      <c r="D1458" s="55"/>
+      <c r="E1458" s="61">
         <v>37</v>
       </c>
-      <c r="F1458" s="58"/>
+      <c r="F1458" s="56"/>
     </row>
     <row r="1459" spans="1:6" ht="15.75">
       <c r="A1459" s="53" t="s">
         <v>3142</v>
       </c>
-      <c r="C1459" s="57"/>
-      <c r="D1459" s="57"/>
-      <c r="E1459" s="64">
+      <c r="C1459" s="55"/>
+      <c r="D1459" s="55"/>
+      <c r="E1459" s="61">
         <v>12.3</v>
       </c>
-      <c r="F1459" s="58"/>
+      <c r="F1459" s="56"/>
     </row>
     <row r="1460" spans="1:6" ht="15.75">
       <c r="A1460" s="53" t="s">
         <v>3143</v>
       </c>
-      <c r="C1460" s="57"/>
-      <c r="D1460" s="57"/>
-      <c r="E1460" s="64">
+      <c r="C1460" s="55"/>
+      <c r="D1460" s="55"/>
+      <c r="E1460" s="61">
         <v>0.74</v>
       </c>
-      <c r="F1460" s="58"/>
+      <c r="F1460" s="56"/>
     </row>
     <row r="1461" spans="1:6" ht="15.75">
       <c r="A1461" s="53" t="s">
         <v>3144</v>
       </c>
-      <c r="C1461" s="57"/>
-      <c r="D1461" s="57"/>
-      <c r="E1461" s="64">
+      <c r="C1461" s="55"/>
+      <c r="D1461" s="55"/>
+      <c r="E1461" s="61">
         <v>110</v>
       </c>
-      <c r="F1461" s="58"/>
+      <c r="F1461" s="56"/>
     </row>
     <row r="1462" spans="1:6" ht="15.75">
       <c r="A1462" s="53" t="s">
         <v>3145</v>
       </c>
-      <c r="C1462" s="57"/>
-      <c r="D1462" s="57"/>
-      <c r="E1462" s="64">
+      <c r="C1462" s="55"/>
+      <c r="D1462" s="55"/>
+      <c r="E1462" s="61">
         <v>9</v>
       </c>
-      <c r="F1462" s="58"/>
+      <c r="F1462" s="56"/>
     </row>
     <row r="1463" spans="1:6" ht="15.75">
       <c r="A1463" s="53" t="s">
         <v>3146</v>
       </c>
-      <c r="C1463" s="57"/>
-      <c r="D1463" s="57"/>
-      <c r="E1463" s="64">
+      <c r="C1463" s="55"/>
+      <c r="D1463" s="55"/>
+      <c r="E1463" s="61">
         <v>9</v>
       </c>
-      <c r="F1463" s="58"/>
+      <c r="F1463" s="56"/>
     </row>
     <row r="1464" spans="1:6" ht="15.75">
       <c r="A1464" s="53" t="s">
         <v>3147</v>
       </c>
-      <c r="C1464" s="57"/>
-      <c r="D1464" s="57"/>
-      <c r="E1464" s="64">
+      <c r="C1464" s="55"/>
+      <c r="D1464" s="55"/>
+      <c r="E1464" s="61">
         <v>9</v>
       </c>
-      <c r="F1464" s="58"/>
+      <c r="F1464" s="56"/>
     </row>
     <row r="1465" spans="1:6" ht="15.75">
       <c r="A1465" s="53" t="s">
         <v>3148</v>
       </c>
-      <c r="C1465" s="57"/>
-      <c r="D1465" s="57"/>
-      <c r="E1465" s="64">
+      <c r="C1465" s="55"/>
+      <c r="D1465" s="55"/>
+      <c r="E1465" s="61">
         <v>63.76</v>
       </c>
-      <c r="F1465" s="58"/>
+      <c r="F1465" s="56"/>
     </row>
     <row r="1466" spans="1:6" ht="15.75">
       <c r="A1466" s="53" t="s">
         <v>3149</v>
       </c>
-      <c r="C1466" s="57" t="s">
-        <v>3173</v>
-      </c>
-      <c r="D1466" s="57" t="s">
-        <v>3189</v>
-      </c>
-      <c r="E1466" s="64">
+      <c r="C1466" s="55" t="s">
+        <v>3162</v>
+      </c>
+      <c r="D1466" s="55" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E1466" s="61">
         <v>106.24</v>
       </c>
-      <c r="F1466" s="58"/>
+      <c r="F1466" s="56"/>
     </row>
     <row r="1467" spans="1:6" ht="15.75">
       <c r="A1467" s="53" t="s">
         <v>3150</v>
       </c>
-      <c r="C1467" s="57"/>
-      <c r="D1467" s="57"/>
-      <c r="E1467" s="64">
+      <c r="C1467" s="55"/>
+      <c r="D1467" s="55"/>
+      <c r="E1467" s="61">
         <v>1.5</v>
       </c>
-      <c r="F1467" s="58"/>
+      <c r="F1467" s="56"/>
     </row>
     <row r="1468" spans="1:6" ht="15.75">
       <c r="A1468" s="53" t="s">
         <v>3151</v>
       </c>
-      <c r="C1468" s="57"/>
-      <c r="D1468" s="57"/>
-      <c r="E1468" s="64">
+      <c r="C1468" s="55"/>
+      <c r="D1468" s="55"/>
+      <c r="E1468" s="61">
         <v>7.5</v>
       </c>
-      <c r="F1468" s="58"/>
+      <c r="F1468" s="56"/>
     </row>
     <row r="1469" spans="1:6" ht="15.75">
       <c r="A1469" s="54" t="s">
         <v>3152</v>
       </c>
-      <c r="C1469" s="62" t="s">
-        <v>3184</v>
-      </c>
-      <c r="D1469" s="57"/>
-      <c r="E1469" s="64">
+      <c r="C1469" s="60" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D1469" s="55"/>
+      <c r="E1469" s="61">
         <v>37</v>
       </c>
-      <c r="F1469" s="58"/>
+      <c r="F1469" s="56"/>
     </row>
     <row r="1470" spans="1:6" ht="15.75">
       <c r="A1470" s="54" t="s">
         <v>3153</v>
       </c>
-      <c r="C1470" s="57"/>
-      <c r="D1470" s="57"/>
-      <c r="E1470" s="64">
+      <c r="C1470" s="55"/>
+      <c r="D1470" s="55"/>
+      <c r="E1470" s="61">
         <v>37</v>
       </c>
-      <c r="F1470" s="58"/>
+      <c r="F1470" s="56"/>
     </row>
     <row r="1471" spans="1:6" ht="15.75">
       <c r="A1471" s="54" t="s">
         <v>3154</v>
       </c>
-      <c r="C1471" s="57"/>
-      <c r="D1471" s="57"/>
-      <c r="E1471" s="64">
+      <c r="C1471" s="55"/>
+      <c r="D1471" s="55"/>
+      <c r="E1471" s="61">
         <v>12.3</v>
       </c>
-      <c r="F1471" s="58"/>
+      <c r="F1471" s="56"/>
     </row>
     <row r="1472" spans="1:6" ht="15.75">
       <c r="A1472" s="54" t="s">
         <v>3155</v>
       </c>
-      <c r="C1472" s="57"/>
-      <c r="D1472" s="57"/>
-      <c r="E1472" s="64">
+      <c r="C1472" s="55"/>
+      <c r="D1472" s="55"/>
+      <c r="E1472" s="61">
         <v>0.74</v>
       </c>
-      <c r="F1472" s="58"/>
+      <c r="F1472" s="56"/>
     </row>
     <row r="1473" spans="1:6" ht="15.75">
       <c r="A1473" s="54" t="s">
         <v>3156</v>
       </c>
-      <c r="C1473" s="57"/>
-      <c r="D1473" s="57"/>
-      <c r="E1473" s="64">
+      <c r="C1473" s="55"/>
+      <c r="D1473" s="55"/>
+      <c r="E1473" s="61">
         <v>110</v>
       </c>
-      <c r="F1473" s="58"/>
-    </row>
-    <row r="1474" spans="1:6" ht="15.75">
-      <c r="A1474" s="49" t="s">
-        <v>3157</v>
-      </c>
-      <c r="C1474" s="63" t="s">
-        <v>3185</v>
-      </c>
-      <c r="D1474" s="63" t="s">
+      <c r="F1473" s="56"/>
+    </row>
+    <row r="1474" spans="1:6">
+      <c r="A1474" s="68" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B1474" s="68" t="s">
+        <v>3394</v>
+      </c>
+      <c r="C1474" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1474" s="65" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1474" s="65">
+        <v>3</v>
+      </c>
+      <c r="F1474" s="62" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:6">
+      <c r="A1475" s="68" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B1475" s="68" t="s">
+        <v>3395</v>
+      </c>
+      <c r="C1475" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1475" s="65" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E1475" s="62">
+        <v>4</v>
+      </c>
+      <c r="F1475" s="65" t="s">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:6">
+      <c r="A1476" s="68" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B1476" s="68" t="s">
+        <v>3396</v>
+      </c>
+      <c r="C1476" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1476" s="65" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E1476" s="62">
+        <v>4</v>
+      </c>
+      <c r="F1476" s="65" t="s">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:6">
+      <c r="A1477" s="68" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B1477" s="68" t="s">
+        <v>3397</v>
+      </c>
+      <c r="C1477" s="65" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1477" s="65" t="s">
+        <v>3344</v>
+      </c>
+      <c r="E1477" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1477" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:6">
+      <c r="A1478" s="68" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1478" s="68" t="s">
+        <v>3397</v>
+      </c>
+      <c r="C1478" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1478" s="65"/>
+      <c r="E1478" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1478" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:6">
+      <c r="A1479" s="68" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B1479" s="68" t="s">
+        <v>3398</v>
+      </c>
+      <c r="C1479" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1479" s="65" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E1479" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1479" s="65" t="s">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:6">
+      <c r="A1480" s="68" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B1480" s="68" t="s">
+        <v>3399</v>
+      </c>
+      <c r="C1480" s="65" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1480" s="65" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1480" s="61">
+        <v>22</v>
+      </c>
+      <c r="F1480" s="65"/>
+    </row>
+    <row r="1481" spans="1:6">
+      <c r="A1481" s="68" t="s">
+        <v>3202</v>
+      </c>
+      <c r="B1481" s="68" t="s">
+        <v>3400</v>
+      </c>
+      <c r="C1481" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1481" s="62" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E1481" s="62">
+        <v>4</v>
+      </c>
+      <c r="F1481" s="62" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:6">
+      <c r="A1482" s="68" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B1482" s="68" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C1482" s="62" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1482" s="62" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E1482" s="61">
+        <v>7.5</v>
+      </c>
+      <c r="F1482" s="62"/>
+    </row>
+    <row r="1483" spans="1:6">
+      <c r="A1483" s="68" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B1483" s="68" t="s">
+        <v>3402</v>
+      </c>
+      <c r="C1483" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1483" s="65" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E1483" s="62">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F1483" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:6">
+      <c r="A1484" s="68" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1484" s="68" t="s">
+        <v>3403</v>
+      </c>
+      <c r="C1484" s="65" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D1484" s="65" t="s">
+        <v>3337</v>
+      </c>
+      <c r="E1484" s="62">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F1484" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:6">
+      <c r="A1485" s="68" t="s">
+        <v>3404</v>
+      </c>
+      <c r="B1485" s="68" t="s">
+        <v>3405</v>
+      </c>
+      <c r="C1485" s="65" t="s">
+        <v>3330</v>
+      </c>
+      <c r="D1485" s="65" t="s">
+        <v>3181</v>
+      </c>
+      <c r="E1485" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1485" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:6">
+      <c r="A1486" s="68" t="s">
+        <v>3406</v>
+      </c>
+      <c r="B1486" s="68" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C1486" s="65" t="s">
+        <v>3336</v>
+      </c>
+      <c r="D1486" s="65"/>
+      <c r="E1486" s="61">
+        <v>3600</v>
+      </c>
+      <c r="F1486" s="65"/>
+    </row>
+    <row r="1487" spans="1:6">
+      <c r="A1487" s="68" t="s">
+        <v>3408</v>
+      </c>
+      <c r="B1487" s="68" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C1487" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1487" s="65" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E1487" s="61">
+        <v>55</v>
+      </c>
+      <c r="F1487" s="65" t="s">
         <v>3193</v>
       </c>
-      <c r="E1474" s="64">
-        <v>120</v>
-      </c>
-      <c r="F1474" s="65"/>
-    </row>
-    <row r="1475" spans="1:6">
-      <c r="A1475" s="55" t="s">
-        <v>3158</v>
-      </c>
-      <c r="C1475" s="57" t="s">
-        <v>3180</v>
-      </c>
-      <c r="D1475" s="57" t="s">
+    </row>
+    <row r="1488" spans="1:6">
+      <c r="A1488" s="68" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B1488" s="68" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C1488" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1488" s="65" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E1488" s="61">
+        <v>75</v>
+      </c>
+      <c r="F1488" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:6">
+      <c r="A1489" s="68" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1489" s="68" t="s">
+        <v>3412</v>
+      </c>
+      <c r="C1489" s="65" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D1489" s="65" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1489" s="62">
+        <v>370</v>
+      </c>
+      <c r="F1489" s="65"/>
+    </row>
+    <row r="1490" spans="1:6">
+      <c r="A1490" s="68" t="s">
+        <v>3199</v>
+      </c>
+      <c r="B1490" s="68" t="s">
+        <v>3413</v>
+      </c>
+      <c r="C1490" s="65" t="s">
+        <v>3316</v>
+      </c>
+      <c r="D1490" s="62"/>
+      <c r="E1490" s="62">
+        <v>500</v>
+      </c>
+      <c r="F1490" s="62"/>
+    </row>
+    <row r="1491" spans="1:6">
+      <c r="A1491" s="68" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B1491" s="68" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C1491" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1491" s="62" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E1491" s="62">
+        <v>0.4</v>
+      </c>
+      <c r="F1491" s="62" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:6">
+      <c r="A1492" s="68" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B1492" s="68" t="s">
+        <v>3415</v>
+      </c>
+      <c r="C1492" s="62" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1492" s="62" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E1492" s="61">
+        <v>75</v>
+      </c>
+      <c r="F1492" s="62" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:6">
+      <c r="A1493" s="68" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B1493" s="68" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C1493" s="62" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D1493" s="62" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1493" s="62">
+        <v>185</v>
+      </c>
+      <c r="F1493" s="62"/>
+    </row>
+    <row r="1494" spans="1:6">
+      <c r="A1494" s="68" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B1494" s="68" t="s">
+        <v>3418</v>
+      </c>
+      <c r="C1494" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1494" s="65" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E1494" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1494" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:6">
+      <c r="A1495" s="68" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1495" s="68" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C1495" s="62" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1495" s="62" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1495" s="62">
+        <v>185</v>
+      </c>
+      <c r="F1495" s="62"/>
+    </row>
+    <row r="1496" spans="1:6">
+      <c r="A1496" s="68" t="s">
+        <v>3419</v>
+      </c>
+      <c r="B1496" s="68" t="s">
+        <v>3420</v>
+      </c>
+      <c r="C1496" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1496" s="65" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1496" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1496" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:6">
+      <c r="A1497" s="68" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B1497" s="68" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C1497" s="65" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D1497" s="65" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E1497" s="61">
+        <v>200</v>
+      </c>
+      <c r="F1497" s="65"/>
+    </row>
+    <row r="1498" spans="1:6">
+      <c r="A1498" s="68" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B1498" s="68" t="s">
+        <v>3422</v>
+      </c>
+      <c r="C1498" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1498" s="65" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E1498" s="62">
+        <v>37</v>
+      </c>
+      <c r="F1498" s="65" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:6">
+      <c r="A1499" s="68" t="s">
+        <v>3423</v>
+      </c>
+      <c r="B1499" s="68" t="s">
+        <v>3424</v>
+      </c>
+      <c r="C1499" s="3"/>
+      <c r="D1499" s="3"/>
+      <c r="E1499" s="2"/>
+      <c r="F1499"/>
+    </row>
+    <row r="1500" spans="1:6">
+      <c r="A1500" s="68" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B1500" s="68" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C1500" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1500" s="65" t="s">
+        <v>3351</v>
+      </c>
+      <c r="E1500" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1500" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:6">
+      <c r="A1501" s="68" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B1501" s="68" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C1501" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1501" s="65" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E1501" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1501" s="65" t="s">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:6">
+      <c r="A1502" s="68" t="s">
+        <v>3208</v>
+      </c>
+      <c r="B1502" s="68" t="s">
+        <v>3426</v>
+      </c>
+      <c r="C1502" s="65"/>
+      <c r="D1502" s="65" t="s">
+        <v>3339</v>
+      </c>
+      <c r="E1502" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="F1502" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:6">
+      <c r="A1503" s="68" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B1503" s="68" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C1503" s="65" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1503" s="65" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E1503" s="62">
+        <v>200</v>
+      </c>
+      <c r="F1503" s="65"/>
+    </row>
+    <row r="1504" spans="1:6">
+      <c r="A1504" s="68" t="s">
+        <v>3211</v>
+      </c>
+      <c r="B1504" s="68" t="s">
+        <v>3428</v>
+      </c>
+      <c r="C1504" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1504" s="65" t="s">
+        <v>3340</v>
+      </c>
+      <c r="E1504" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1504" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:6">
+      <c r="A1505" s="68" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B1505" s="68" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C1505" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1505" s="61" t="s">
+        <v>3341</v>
+      </c>
+      <c r="E1505" s="61">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1505" s="61" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:6">
+      <c r="A1506" s="68" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B1506" s="68" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C1506" s="65" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D1506" s="65" t="s">
+        <v>452</v>
+      </c>
+      <c r="E1506" s="62">
+        <v>200</v>
+      </c>
+      <c r="F1506" s="65"/>
+    </row>
+    <row r="1507" spans="1:6">
+      <c r="A1507" s="68" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B1507" s="68" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C1507" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1507" s="65" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1507" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1507" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:6">
+      <c r="A1508" s="68" t="s">
+        <v>3433</v>
+      </c>
+      <c r="B1508" s="68" t="s">
+        <v>3434</v>
+      </c>
+      <c r="C1508" s="3"/>
+      <c r="D1508" s="41"/>
+      <c r="E1508" s="2"/>
+      <c r="F1508"/>
+    </row>
+    <row r="1509" spans="1:6">
+      <c r="A1509" s="68" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B1509" s="68" t="s">
+        <v>3435</v>
+      </c>
+      <c r="C1509" s="65" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1509" s="65" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E1509" s="62">
+        <v>110</v>
+      </c>
+      <c r="F1509" s="65"/>
+    </row>
+    <row r="1510" spans="1:6">
+      <c r="A1510" s="68" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B1510" s="68" t="s">
+        <v>3434</v>
+      </c>
+      <c r="C1510" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1510" s="65" t="s">
+        <v>3341</v>
+      </c>
+      <c r="E1510" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="F1510" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:6">
+      <c r="A1511" s="68" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B1511" s="68" t="s">
+        <v>3437</v>
+      </c>
+      <c r="C1511" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1511" s="61" t="s">
+        <v>3343</v>
+      </c>
+      <c r="E1511" s="61">
+        <v>0.37</v>
+      </c>
+      <c r="F1511" s="61" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:6">
+      <c r="A1512" s="68" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B1512" s="68" t="s">
+        <v>3438</v>
+      </c>
+      <c r="C1512" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1512" s="65" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1512" s="61">
+        <v>5.5</v>
+      </c>
+      <c r="F1512" s="65" t="s">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:6">
+      <c r="A1513" s="68" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B1513" s="68" t="s">
+        <v>3439</v>
+      </c>
+      <c r="C1513" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1513" s="65" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1513" s="61">
+        <v>14</v>
+      </c>
+      <c r="F1513" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:6">
+      <c r="A1514" s="68" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B1514" s="68" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C1514" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1514" s="65" t="s">
+        <v>3356</v>
+      </c>
+      <c r="E1514" s="62">
+        <v>110</v>
+      </c>
+      <c r="F1514" s="65"/>
+    </row>
+    <row r="1515" spans="1:6">
+      <c r="A1515" s="68" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B1515" s="68" t="s">
+        <v>3442</v>
+      </c>
+      <c r="C1515" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1515" s="65" t="s">
+        <v>3370</v>
+      </c>
+      <c r="E1515" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="F1515" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:6">
+      <c r="A1516" s="68" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B1516" s="68" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C1516" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1516" s="65" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E1516" s="62">
+        <v>110</v>
+      </c>
+      <c r="F1516" s="65" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:6">
+      <c r="A1517" s="68" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B1517" s="68" t="s">
+        <v>3444</v>
+      </c>
+      <c r="C1517" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1517" s="65" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E1517" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="F1517" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:6">
+      <c r="A1518" s="68" t="s">
+        <v>3445</v>
+      </c>
+      <c r="B1518" s="68" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C1518" s="3"/>
+      <c r="D1518" s="3"/>
+      <c r="E1518" s="2"/>
+      <c r="F1518"/>
+    </row>
+    <row r="1519" spans="1:6">
+      <c r="A1519" s="68" t="s">
+        <v>3447</v>
+      </c>
+      <c r="B1519" s="68" t="s">
+        <v>3448</v>
+      </c>
+      <c r="C1519" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1519" s="65" t="s">
+        <v>3371</v>
+      </c>
+      <c r="E1519" s="62">
+        <v>0.37</v>
+      </c>
+      <c r="F1519" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:6">
+      <c r="A1520" s="68" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B1520" s="68" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C1520" s="65" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D1520" s="65" t="s">
+        <v>455</v>
+      </c>
+      <c r="E1520" s="62">
+        <v>230</v>
+      </c>
+      <c r="F1520" s="65"/>
+    </row>
+    <row r="1521" spans="1:6">
+      <c r="A1521" s="68" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B1521" s="68" t="s">
+        <v>3450</v>
+      </c>
+      <c r="C1521" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1521" s="65" t="s">
+        <v>3349</v>
+      </c>
+      <c r="E1521" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1521" s="65" t="s">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:6">
+      <c r="A1522" s="68" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B1522" s="68" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C1522" s="65" t="s">
+        <v>3327</v>
+      </c>
+      <c r="D1522" s="65" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E1522" s="62">
+        <v>230</v>
+      </c>
+      <c r="F1522" s="65"/>
+    </row>
+    <row r="1523" spans="1:6">
+      <c r="A1523" s="68" t="s">
+        <v>3451</v>
+      </c>
+      <c r="B1523" s="68" t="s">
+        <v>3452</v>
+      </c>
+      <c r="C1523" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1523" s="65" t="s">
+        <v>3359</v>
+      </c>
+      <c r="E1523" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1523" s="65"/>
+    </row>
+    <row r="1524" spans="1:6">
+      <c r="A1524" s="68" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B1524" s="68" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C1524" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1524" s="65" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1524" s="61">
+        <v>110</v>
+      </c>
+      <c r="F1524" s="65" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:6">
+      <c r="A1525" s="68" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B1525" s="68" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C1525" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1525" s="65" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E1525" s="61">
+        <v>15</v>
+      </c>
+      <c r="F1525" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:6">
+      <c r="A1526" s="68" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1526" s="68" t="s">
+        <v>3455</v>
+      </c>
+      <c r="C1526" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1526" s="65" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E1526" s="61">
+        <v>21.1</v>
+      </c>
+      <c r="F1526" s="65" t="s">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:6">
+      <c r="A1527" s="68" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B1527" s="68" t="s">
+        <v>3456</v>
+      </c>
+      <c r="C1527" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1527" s="65" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E1527" s="61">
+        <v>3.7</v>
+      </c>
+      <c r="F1527" s="65" t="s">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:6">
+      <c r="A1528" s="68" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1528" s="68" t="s">
+        <v>3457</v>
+      </c>
+      <c r="C1528" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1528" s="65" t="s">
+        <v>3365</v>
+      </c>
+      <c r="E1528" s="61">
+        <v>11</v>
+      </c>
+      <c r="F1528" s="65" t="s">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:6">
+      <c r="A1529" s="68" t="s">
+        <v>3458</v>
+      </c>
+      <c r="B1529" s="68" t="s">
+        <v>3459</v>
+      </c>
+      <c r="C1529" s="65" t="s">
+        <v>3333</v>
+      </c>
+      <c r="D1529" s="65" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E1529" s="61">
+        <v>35.5</v>
+      </c>
+      <c r="F1529" s="65" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:6">
+      <c r="A1530" s="68" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B1530" s="68" t="s">
+        <v>3461</v>
+      </c>
+      <c r="C1530" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1530" s="65" t="s">
+        <v>3354</v>
+      </c>
+      <c r="E1530" s="62">
+        <v>4.87</v>
+      </c>
+      <c r="F1530" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:6">
+      <c r="A1531" s="68" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B1531" s="68" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C1531" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1531" s="65" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1531" s="62">
+        <v>3.27</v>
+      </c>
+      <c r="F1531" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:6">
+      <c r="A1532" s="68" t="s">
+        <v>3464</v>
+      </c>
+      <c r="B1532" s="68" t="s">
+        <v>3465</v>
+      </c>
+      <c r="C1532" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1532" s="65" t="s">
+        <v>3355</v>
+      </c>
+      <c r="E1532" s="62">
+        <v>3.27</v>
+      </c>
+      <c r="F1532" s="65" t="s">
+        <v>3382</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:6">
+      <c r="A1533" s="68" t="s">
+        <v>3307</v>
+      </c>
+      <c r="B1533" s="68" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C1533" s="62" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1533" s="62" t="s">
+        <v>3369</v>
+      </c>
+      <c r="E1533" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1533" s="62" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:6">
+      <c r="A1534" s="68" t="s">
+        <v>3213</v>
+      </c>
+      <c r="B1534" s="68" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C1534" s="64" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1534" s="64" t="s">
+        <v>3344</v>
+      </c>
+      <c r="E1534" s="67">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1534" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:6">
+      <c r="A1535" s="68" t="s">
+        <v>3223</v>
+      </c>
+      <c r="B1535" s="68" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C1535" s="64" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1535" s="64" t="s">
+        <v>3348</v>
+      </c>
+      <c r="E1535" s="67">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1535" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:6">
+      <c r="A1536" s="68" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B1536" s="68" t="s">
+        <v>3468</v>
+      </c>
+      <c r="C1536" s="64" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1536" s="64" t="s">
+        <v>3352</v>
+      </c>
+      <c r="E1536" s="67">
+        <v>0.75</v>
+      </c>
+      <c r="F1536" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:6">
+      <c r="A1537" s="68" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B1537" s="68" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C1537" s="65" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1537" s="65" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E1537" s="62">
+        <v>0.4</v>
+      </c>
+      <c r="F1537" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:6">
+      <c r="A1538" s="68" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B1538" s="68" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C1538" s="64" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D1538" s="64" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E1538" s="67">
+        <v>0.4</v>
+      </c>
+      <c r="F1538" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:6">
+      <c r="A1539" s="68" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1539" s="68" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C1539" s="64" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1539" s="64" t="s">
+        <v>3342</v>
+      </c>
+      <c r="E1539" s="67">
+        <v>0.4</v>
+      </c>
+      <c r="F1539" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:6">
+      <c r="A1540" s="68" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B1540" s="68" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C1540" s="64" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1540" s="64" t="s">
+        <v>3352</v>
+      </c>
+      <c r="E1540" s="67">
+        <v>0.4</v>
+      </c>
+      <c r="F1540" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:6">
+      <c r="A1541" s="68" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B1541" s="68" t="s">
+        <v>3470</v>
+      </c>
+      <c r="C1541" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1541" s="65" t="s">
+        <v>3349</v>
+      </c>
+      <c r="E1541" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1541" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:6">
+      <c r="A1542" s="68" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B1542" s="68" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C1542" s="64" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1542" s="64" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E1542" s="67">
+        <v>3.7</v>
+      </c>
+      <c r="F1542" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:6">
+      <c r="A1543" s="68" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B1543" s="68" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C1543" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1543" s="65" t="s">
+        <v>3357</v>
+      </c>
+      <c r="E1543" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1543" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:6">
+      <c r="A1544" s="68" t="s">
+        <v>3197</v>
+      </c>
+      <c r="B1544" s="68" t="s">
+        <v>3472</v>
+      </c>
+      <c r="C1544" s="65" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1544" s="65" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E1544" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1544" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:6">
+      <c r="A1545" s="68" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B1545" s="68" t="s">
+        <v>3472</v>
+      </c>
+      <c r="C1545" s="65" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1545" s="65" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E1545" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1545" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:6">
+      <c r="A1546" s="68" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B1546" s="68" t="s">
+        <v>3473</v>
+      </c>
+      <c r="C1546" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1546" s="65" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E1546" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1546" s="65" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:6">
+      <c r="A1547" s="68" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B1547" s="68" t="s">
+        <v>3473</v>
+      </c>
+      <c r="C1547" s="65" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1547" s="65" t="s">
+        <v>3189</v>
+      </c>
+      <c r="E1547" s="62">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1547" s="65" t="s">
+        <v>3384</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:6">
+      <c r="A1548" s="68" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B1548" s="68" t="s">
+        <v>3474</v>
+      </c>
+      <c r="C1548" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1548" s="65" t="s">
+        <v>3360</v>
+      </c>
+      <c r="E1548" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1548" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:6">
+      <c r="A1549" s="68" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B1549" s="68" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C1549" s="65" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1549" s="65" t="s">
         <v>3190</v>
       </c>
-      <c r="E1475" s="64">
+      <c r="E1549" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1549" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:6">
+      <c r="A1550" s="68" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B1550" s="68" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C1550" s="64" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1550" s="64" t="s">
+        <v>3368</v>
+      </c>
+      <c r="E1550" s="67">
         <v>0.4</v>
       </c>
-      <c r="F1475" s="58"/>
-    </row>
-    <row r="1476" spans="1:6" ht="15.75">
-      <c r="A1476" s="49" t="s">
-        <v>3159</v>
-      </c>
-      <c r="C1476" s="57" t="s">
-        <v>3171</v>
-      </c>
-      <c r="D1476" s="57" t="s">
+      <c r="F1550" s="64" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:6">
+      <c r="A1551" s="68" t="s">
+        <v>3477</v>
+      </c>
+      <c r="B1551" s="68" t="s">
+        <v>3476</v>
+      </c>
+      <c r="C1551" s="3"/>
+      <c r="D1551" s="3"/>
+      <c r="E1551" s="2"/>
+      <c r="F1551"/>
+    </row>
+    <row r="1552" spans="1:6">
+      <c r="A1552" s="68" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B1552" s="68" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C1552" s="65" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1552" s="65" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E1552" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1552" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:6">
+      <c r="A1553" s="68" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B1553" s="68" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C1553" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1553" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E1553" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1553" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:6">
+      <c r="A1554" s="68" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B1554" s="68" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C1554" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1554" s="65" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E1554" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1554" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:6">
+      <c r="A1555" s="68" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B1555" s="68" t="s">
+        <v>3480</v>
+      </c>
+      <c r="C1555" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1555" s="65" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E1555" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1555" s="65" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:6">
+      <c r="A1556" s="68" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B1556" s="68" t="s">
+        <v>3481</v>
+      </c>
+      <c r="C1556" s="65" t="s">
+        <v>3329</v>
+      </c>
+      <c r="D1556" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E1556" s="62">
+        <v>450</v>
+      </c>
+      <c r="F1556" s="65"/>
+    </row>
+    <row r="1557" spans="1:6">
+      <c r="A1557" s="68" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B1557" s="68" t="s">
+        <v>3482</v>
+      </c>
+      <c r="C1557" s="65" t="s">
+        <v>3320</v>
+      </c>
+      <c r="D1557" s="65" t="s">
+        <v>449</v>
+      </c>
+      <c r="E1557" s="62">
+        <v>450</v>
+      </c>
+      <c r="F1557" s="65"/>
+    </row>
+    <row r="1558" spans="1:6">
+      <c r="A1558" s="68" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B1558" s="68" t="s">
+        <v>3483</v>
+      </c>
+      <c r="C1558" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1558" s="65" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E1558" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1558" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:6">
+      <c r="A1559" s="68" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B1559" s="68" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C1559" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1559" s="65" t="s">
+        <v>3361</v>
+      </c>
+      <c r="E1559" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="F1559" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:6">
+      <c r="A1560" s="68" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B1560" s="68" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C1560" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1560" s="65" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E1560" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1560" s="65"/>
+    </row>
+    <row r="1561" spans="1:6">
+      <c r="A1561" s="68" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B1561" s="68" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C1561" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1561" s="65" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1561" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1561" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:6">
+      <c r="A1562" s="68" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B1562" s="68" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C1562" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1562" s="65" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E1562" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1562" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:6">
+      <c r="A1563" s="68" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B1563" s="68" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C1563" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1563" s="65" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1563" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1563" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:6">
+      <c r="A1564" s="68" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B1564" s="68" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C1564" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1564" s="65" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E1564" s="62">
+        <v>75</v>
+      </c>
+      <c r="F1564" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:6">
+      <c r="A1565" s="68" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B1565" s="68" t="s">
+        <v>3487</v>
+      </c>
+      <c r="C1565" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1565" s="65" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E1565" s="62">
+        <v>75</v>
+      </c>
+      <c r="F1565" s="65"/>
+    </row>
+    <row r="1566" spans="1:6">
+      <c r="A1566" s="68" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B1566" s="68" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C1566" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1566" s="65" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E1566" s="62">
+        <v>110</v>
+      </c>
+      <c r="F1566" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:6">
+      <c r="A1567" s="68" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B1567" s="68" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C1567" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1567" s="65" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1567" s="62">
+        <v>110</v>
+      </c>
+      <c r="F1567" s="65" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:6">
+      <c r="A1568" s="68" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B1568" s="68" t="s">
+        <v>3489</v>
+      </c>
+      <c r="C1568" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1568" s="65" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E1568" s="62">
+        <v>18.5</v>
+      </c>
+      <c r="F1568" s="65" t="s">
+        <v>3381</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:6">
+      <c r="A1569" s="68" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B1569" s="68" t="s">
+        <v>3489</v>
+      </c>
+      <c r="C1569" s="3"/>
+      <c r="D1569" s="3"/>
+      <c r="E1569" s="2"/>
+      <c r="F1569"/>
+    </row>
+    <row r="1570" spans="1:6">
+      <c r="A1570" s="68" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B1570" s="68" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C1570" s="65" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1570" s="65" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E1570" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1570" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:6">
+      <c r="A1571" s="68" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B1571" s="68" t="s">
+        <v>3491</v>
+      </c>
+      <c r="C1571" s="65" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1571" s="65" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E1571" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1571" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:6">
+      <c r="A1572" s="68" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B1572" s="68" t="s">
+        <v>3492</v>
+      </c>
+      <c r="C1572" s="65" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1572" s="65" t="s">
+        <v>3362</v>
+      </c>
+      <c r="E1572" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1572" s="65" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:6">
+      <c r="A1573" s="68" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B1573" s="68" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C1573" s="62" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1573" s="62" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E1573" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1573" s="62" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:6">
+      <c r="A1574" s="68" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B1574" s="68" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C1574" s="62" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1574" s="62" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1574" s="62">
+        <v>55</v>
+      </c>
+      <c r="F1574" s="62" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:6">
+      <c r="A1575" s="68" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B1575" s="68" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C1575" s="65" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1575" s="62" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1575" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1575" s="62" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:6">
+      <c r="A1576" s="68" t="s">
+        <v>3494</v>
+      </c>
+      <c r="B1576" s="68" t="s">
+        <v>3495</v>
+      </c>
+      <c r="C1576" s="62" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1576" s="62" t="s">
+        <v>3369</v>
+      </c>
+      <c r="E1576" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1576" s="62" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:6">
+      <c r="A1577" s="68" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B1577" s="68" t="s">
+        <v>3495</v>
+      </c>
+      <c r="C1577" s="62" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1577" s="62" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1577" s="62">
+        <v>7.5</v>
+      </c>
+      <c r="F1577" s="62" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:6">
+      <c r="A1578" s="68" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B1578" s="68" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C1578" s="62" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1578" s="62" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1578" s="62">
+        <v>3.7</v>
+      </c>
+      <c r="F1578" s="62" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:6">
+      <c r="A1579" s="68" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B1579" s="68" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C1579" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1579" s="65" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1579" s="62">
+        <v>37</v>
+      </c>
+      <c r="F1579" s="65" t="s">
+        <v>3383</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:6">
+      <c r="A1580" s="68" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B1580" s="68" t="s">
+        <v>3497</v>
+      </c>
+      <c r="C1580" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1580" s="65" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E1580" s="62">
+        <v>37</v>
+      </c>
+      <c r="F1580" s="65" t="s">
+        <v>3383</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:6">
+      <c r="A1581" s="68" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B1581" s="68" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C1581" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1581" s="65" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E1581" s="62">
+        <v>30</v>
+      </c>
+      <c r="F1581" s="65" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:6">
+      <c r="A1582" s="68" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B1582" s="68" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C1582" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1582" s="65" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E1582" s="62">
+        <v>30</v>
+      </c>
+      <c r="F1582" s="65" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:6">
+      <c r="A1583" s="68" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B1583" s="68" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C1583" s="65" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1583" s="65" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E1583" s="62">
+        <v>15</v>
+      </c>
+      <c r="F1583" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:6">
+      <c r="A1584" s="68" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B1584" s="68" t="s">
+        <v>3499</v>
+      </c>
+      <c r="C1584" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1584" s="65" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E1584" s="62">
+        <v>15</v>
+      </c>
+      <c r="F1584" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:6">
+      <c r="A1585" s="68" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B1585" s="68" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C1585" s="65" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1585" s="65" t="s">
+        <v>3345</v>
+      </c>
+      <c r="E1585" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="F1585" s="65" t="s">
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:6">
+      <c r="A1586" s="68" t="s">
+        <v>3501</v>
+      </c>
+      <c r="B1586" s="68" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C1586" s="3"/>
+      <c r="D1586" s="3"/>
+      <c r="E1586" s="2"/>
+      <c r="F1586"/>
+    </row>
+    <row r="1587" spans="1:6">
+      <c r="A1587" s="68" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B1587" s="68" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C1587" s="3"/>
+      <c r="D1587" s="3"/>
+      <c r="E1587" s="2"/>
+      <c r="F1587"/>
+    </row>
+    <row r="1588" spans="1:6">
+      <c r="A1588" s="68" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B1588" s="68" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C1588" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1588" s="65" t="s">
+        <v>3350</v>
+      </c>
+      <c r="E1588" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="F1588" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:6">
+      <c r="A1589" s="68" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B1589" s="68" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C1589" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1589" s="65" t="s">
+        <v>3358</v>
+      </c>
+      <c r="E1589" s="63">
+        <v>0.75</v>
+      </c>
+      <c r="F1589" s="65" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:6">
+      <c r="A1590" s="68" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B1590" s="68" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C1590" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1590" s="65" t="s">
+        <v>3346</v>
+      </c>
+      <c r="E1590" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1590" s="65" t="s">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:6">
+      <c r="A1591" s="68" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B1591" s="68" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C1591" s="3"/>
+      <c r="D1591" s="3"/>
+      <c r="E1591" s="2"/>
+      <c r="F1591"/>
+    </row>
+    <row r="1592" spans="1:6">
+      <c r="A1592" s="68" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B1592" s="68" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C1592" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1592" s="65" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1592" s="62">
+        <v>45</v>
+      </c>
+      <c r="F1592" s="65" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:6">
+      <c r="A1593" s="68" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B1593" s="68" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C1593" s="65"/>
+      <c r="D1593" s="65" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E1593" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1593" s="65" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:6">
+      <c r="A1594" s="68" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B1594" s="68" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C1594" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1594" s="65" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E1594" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1594" s="65" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:6">
+      <c r="A1595" s="68" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B1595" s="68" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C1595" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1595" s="65"/>
+      <c r="E1595" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1595" s="65" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:6">
+      <c r="A1596" s="68" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B1596" s="68" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C1596" s="65" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D1596" s="65" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E1596" s="62">
+        <v>11</v>
+      </c>
+      <c r="F1596" s="65" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:6">
+      <c r="A1597" s="68" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B1597" s="68" t="s">
+        <v>3510</v>
+      </c>
+      <c r="C1597" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1597" s="65" t="s">
+        <v>3345</v>
+      </c>
+      <c r="E1597" s="62">
+        <v>30</v>
+      </c>
+      <c r="F1597" s="65" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:6">
+      <c r="A1598" s="68" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B1598" s="68" t="s">
+        <v>3510</v>
+      </c>
+      <c r="C1598" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1598" s="65" t="s">
+        <v>3344</v>
+      </c>
+      <c r="E1598" s="62">
+        <v>30</v>
+      </c>
+      <c r="F1598" s="65" t="s">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:6">
+      <c r="A1599" s="68" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B1599" s="68" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C1599" s="65" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1599" s="65" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E1599" s="61">
+        <v>11</v>
+      </c>
+      <c r="F1599" s="65" t="s">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:6">
+      <c r="A1600" s="68" t="s">
+        <v>3207</v>
+      </c>
+      <c r="B1600" s="68" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C1600" s="64" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D1600" s="64" t="s">
+        <v>3338</v>
+      </c>
+      <c r="E1600" s="67">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F1600" s="64" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:6">
+      <c r="A1601" s="68" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B1601" s="68" t="s">
+        <v>3513</v>
+      </c>
+      <c r="C1601" s="65"/>
+      <c r="D1601" s="65" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E1601" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F1601" s="65" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:6">
+      <c r="A1602" s="68" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B1602" s="68" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C1602" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1602" s="65" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E1602" s="61">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1602" s="65" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:6">
+      <c r="A1603" s="68" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B1603" s="68" t="s">
+        <v>3515</v>
+      </c>
+      <c r="C1603" s="65" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1603" s="65" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E1603" s="61">
+        <v>0.25</v>
+      </c>
+      <c r="F1603" s="65" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:6">
+      <c r="A1604" s="68" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B1604" s="68" t="s">
+        <v>3516</v>
+      </c>
+      <c r="C1604" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1604" s="65" t="s">
+        <v>3341</v>
+      </c>
+      <c r="E1604" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1604" s="65" t="s">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:6">
+      <c r="A1605" s="68" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B1605" s="68" t="s">
+        <v>3517</v>
+      </c>
+      <c r="C1605" s="65" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D1605" s="65" t="s">
+        <v>3363</v>
+      </c>
+      <c r="E1605" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1605" s="65" t="s">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:6">
+      <c r="A1606" s="68" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B1606" s="68" t="s">
+        <v>3518</v>
+      </c>
+      <c r="C1606" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1606" s="65" t="s">
+        <v>3355</v>
+      </c>
+      <c r="E1606" s="61">
+        <v>2.1</v>
+      </c>
+      <c r="F1606" s="65" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:6">
+      <c r="A1607" s="68" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B1607" s="68" t="s">
+        <v>3519</v>
+      </c>
+      <c r="C1607" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1607" s="65" t="s">
+        <v>3364</v>
+      </c>
+      <c r="E1607" s="61">
+        <v>0.75</v>
+      </c>
+      <c r="F1607" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:6">
+      <c r="A1608" s="68" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B1608" s="68" t="s">
+        <v>3520</v>
+      </c>
+      <c r="C1608" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1608" s="65" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E1608" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1608" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:6">
+      <c r="A1609" s="68" t="s">
+        <v>3205</v>
+      </c>
+      <c r="B1609" s="68" t="s">
+        <v>3521</v>
+      </c>
+      <c r="C1609" s="65" t="s">
+        <v>3318</v>
+      </c>
+      <c r="D1609" s="65" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E1609" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1609" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:6">
+      <c r="A1610" s="68" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B1610" s="68" t="s">
+        <v>3522</v>
+      </c>
+      <c r="C1610" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1610" s="65" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E1610" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1610" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:6">
+      <c r="A1611" s="68" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B1611" s="68" t="s">
+        <v>3523</v>
+      </c>
+      <c r="C1611" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1611" s="65" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1611" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1611" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:6">
+      <c r="A1612" s="68" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B1612" s="68" t="s">
+        <v>3524</v>
+      </c>
+      <c r="C1612" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1612" s="65" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E1612" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1612" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:6">
+      <c r="A1613" s="68" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B1613" s="68" t="s">
+        <v>3525</v>
+      </c>
+      <c r="C1613" s="65" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D1613" s="65" t="s">
+        <v>3347</v>
+      </c>
+      <c r="E1613" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1613" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:6">
+      <c r="A1614" s="68" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B1614" s="68" t="s">
+        <v>3526</v>
+      </c>
+      <c r="C1614" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1614" s="65" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E1614" s="61">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F1614" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:6">
+      <c r="A1615" s="68" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B1615" s="68" t="s">
+        <v>3527</v>
+      </c>
+      <c r="C1615" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1615" s="65" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1615" s="61">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1615" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:6">
+      <c r="A1616" s="68" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B1616" s="68" t="s">
+        <v>3528</v>
+      </c>
+      <c r="C1616" s="65" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1616" s="65" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E1616" s="61">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F1616" s="65" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:6">
+      <c r="A1617" s="68" t="s">
+        <v>3529</v>
+      </c>
+      <c r="B1617" s="68" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C1617" s="65" t="s">
+        <v>3335</v>
+      </c>
+      <c r="D1617" s="65" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E1617" s="61">
+        <v>0.25</v>
+      </c>
+      <c r="F1617" s="65" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:6">
+      <c r="A1618" s="68" t="s">
+        <v>3531</v>
+      </c>
+      <c r="B1618" s="68" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C1618" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1618" s="65" t="s">
+        <v>3353</v>
+      </c>
+      <c r="E1618" s="63">
+        <v>0.75</v>
+      </c>
+      <c r="F1618" s="65" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:6">
+      <c r="A1619" s="68" t="s">
+        <v>3533</v>
+      </c>
+      <c r="B1619" s="68" t="s">
+        <v>3530</v>
+      </c>
+      <c r="C1619" s="65" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1619" s="65" t="s">
+        <v>3366</v>
+      </c>
+      <c r="E1619" s="62">
+        <v>0.24</v>
+      </c>
+      <c r="F1619" s="65" t="s">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:6">
+      <c r="A1620" s="68" t="s">
+        <v>3534</v>
+      </c>
+      <c r="B1620" s="68" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C1620" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1620" s="65" t="s">
+        <v>3367</v>
+      </c>
+      <c r="E1620" s="62">
+        <v>0.75</v>
+      </c>
+      <c r="F1620" s="65" t="s">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:6">
+      <c r="A1621" s="68" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B1621" s="68" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C1621" s="65" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D1621" s="65" t="s">
         <v>1462</v>
       </c>
-      <c r="E1476" s="64">
-        <v>11</v>
-      </c>
-      <c r="F1476" s="58"/>
-    </row>
-    <row r="1477" spans="1:6" ht="15.75">
-      <c r="A1477" s="49" t="s">
-        <v>3160</v>
-      </c>
-      <c r="C1477" s="61" t="s">
-        <v>3170</v>
-      </c>
-      <c r="D1477" s="60" t="s">
-        <v>3201</v>
-      </c>
-      <c r="E1477" s="66">
-        <v>30</v>
-      </c>
-      <c r="F1477" s="61"/>
-    </row>
-    <row r="1478" spans="1:6">
-      <c r="A1478" s="56" t="s">
-        <v>3161</v>
-      </c>
-      <c r="C1478" s="61" t="s">
-        <v>3179</v>
-      </c>
-      <c r="D1478" s="60" t="s">
-        <v>3193</v>
-      </c>
-      <c r="E1478" s="64">
-        <v>0.4</v>
-      </c>
-      <c r="F1478" s="61"/>
-    </row>
-    <row r="1479" spans="1:6" ht="15.75">
-      <c r="A1479" s="50" t="s">
-        <v>3162</v>
-      </c>
-      <c r="C1479" s="58" t="s">
-        <v>3175</v>
-      </c>
-      <c r="D1479" s="57" t="s">
-        <v>3192</v>
-      </c>
-      <c r="E1479" s="66">
-        <v>4</v>
-      </c>
-      <c r="F1479" s="58"/>
-    </row>
-    <row r="1480" spans="1:6" ht="15.75">
-      <c r="A1480" s="49" t="s">
-        <v>3163</v>
-      </c>
-      <c r="C1480" s="58" t="s">
-        <v>3173</v>
-      </c>
-      <c r="D1480" s="57" t="s">
-        <v>3198</v>
-      </c>
-      <c r="E1480" s="64">
-        <v>7.5</v>
-      </c>
-      <c r="F1480" s="58"/>
-    </row>
-    <row r="1481" spans="1:6" ht="15.75">
-      <c r="A1481" s="49" t="s">
-        <v>3164</v>
-      </c>
-      <c r="C1481" s="57" t="s">
-        <v>3182</v>
-      </c>
-      <c r="D1481" s="57" t="s">
-        <v>3200</v>
-      </c>
-      <c r="E1481" s="66">
-        <v>4</v>
-      </c>
-      <c r="F1481" s="58"/>
-    </row>
-    <row r="1482" spans="1:6" ht="15.75">
-      <c r="A1482" s="49" t="s">
-        <v>3165</v>
-      </c>
-      <c r="C1482" s="57" t="s">
-        <v>3177</v>
-      </c>
-      <c r="D1482" s="57" t="s">
-        <v>3202</v>
-      </c>
-      <c r="E1482" s="64">
-        <v>0.75</v>
-      </c>
-      <c r="F1482" s="58"/>
-    </row>
-    <row r="1483" spans="1:6" ht="15.75">
-      <c r="A1483" s="49" t="s">
-        <v>3166</v>
-      </c>
-      <c r="C1483" s="57" t="s">
-        <v>3181</v>
-      </c>
-      <c r="D1483" s="57" t="s">
-        <v>3202</v>
-      </c>
-      <c r="E1483" s="64">
-        <v>0.4</v>
-      </c>
-      <c r="F1483" s="58"/>
-    </row>
-    <row r="1484" spans="1:6" ht="15.75">
-      <c r="A1484" s="49" t="s">
-        <v>3167</v>
-      </c>
-      <c r="C1484" s="57" t="s">
-        <v>3173</v>
-      </c>
-      <c r="D1484" s="57" t="s">
-        <v>3203</v>
-      </c>
-      <c r="E1484" s="64">
-        <v>0.4</v>
-      </c>
-      <c r="F1484" s="58"/>
+      <c r="E1621" s="62">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F1621" s="65" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:6">
+      <c r="A1622" s="69" t="s">
+        <v>3219</v>
+      </c>
+      <c r="C1622" s="65" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D1622" s="65"/>
+      <c r="E1622" s="62">
+        <v>45</v>
+      </c>
+      <c r="F1622" s="65"/>
+    </row>
+    <row r="1623" spans="1:6">
+      <c r="A1623" s="69" t="s">
+        <v>3536</v>
+      </c>
+      <c r="C1623" s="65" t="s">
+        <v>3324</v>
+      </c>
+      <c r="D1623" s="65"/>
+      <c r="E1623" s="62">
+        <v>1.5</v>
+      </c>
+      <c r="F1623" s="65"/>
+    </row>
+    <row r="1624" spans="1:6">
+      <c r="A1624" s="69" t="s">
+        <v>3537</v>
+      </c>
+      <c r="C1624" s="65" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1624" s="65" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E1624" s="61">
+        <v>2.77</v>
+      </c>
+      <c r="F1624" s="66"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/base.xlsx
+++ b/base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\electrical.foreman\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22908F7-BDBB-4C68-9539-292F2D74429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB0DDD2-34CC-4354-A6F8-79ADCDA7FA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="396" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="396" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="mcc" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7135" uniqueCount="3538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7147" uniqueCount="3549">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -10806,6 +10806,39 @@
   </si>
   <si>
     <t>MME-5104 (Tall)</t>
+  </si>
+  <si>
+    <t>BPD motor space heater</t>
+  </si>
+  <si>
+    <t>Anti-Cond. Heaters For Motors</t>
+  </si>
+  <si>
+    <t>GTGA-QF09</t>
+  </si>
+  <si>
+    <t>GTGA-QF10</t>
+  </si>
+  <si>
+    <t>GTGB-QF15</t>
+  </si>
+  <si>
+    <t>GTGC-QF23</t>
+  </si>
+  <si>
+    <t>A80-MSS-ELP-001</t>
+  </si>
+  <si>
+    <t>Anti-Cond. Heater for cubicles</t>
+  </si>
+  <si>
+    <t>BPD panel space heater</t>
+  </si>
+  <si>
+    <t>GTGB-QF14</t>
+  </si>
+  <si>
+    <t>GTGC-QF24</t>
   </si>
 </sst>
 </file>
@@ -11101,7 +11134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11304,6 +11337,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -12342,7 +12378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F1624"/>
+  <dimension ref="A1:F1626"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -40858,6 +40894,46 @@
       </c>
       <c r="F1624" s="66"/>
     </row>
+    <row r="1625" spans="1:6">
+      <c r="A1625" s="70" t="s">
+        <v>3538</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1625" s="7" t="s">
+        <v>3540</v>
+      </c>
+      <c r="E1625" s="7" t="s">
+        <v>3542</v>
+      </c>
+      <c r="F1625" s="7" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:6">
+      <c r="A1626" s="70" t="s">
+        <v>3546</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1626" s="7" t="s">
+        <v>3541</v>
+      </c>
+      <c r="E1626" s="7" t="s">
+        <v>3547</v>
+      </c>
+      <c r="F1626" s="7" t="s">
+        <v>3548</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
